--- a/input_data/sna_country_data/URY/cei.xlsx
+++ b/input_data/sna_country_data/URY/cei.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39606" uniqueCount="22117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41328" uniqueCount="23776">
   <si>
     <t>code</t>
   </si>
@@ -66349,6 +66349,4983 @@
   </si>
   <si>
     <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
   </si>
   <si>
     <t>Transferencia del BCU al Gobierno</t>
@@ -66420,36 +71397,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22038</v>
+        <v>23223</v>
       </c>
       <c r="B1" t="s">
-        <v>22075</v>
+        <v>23260</v>
       </c>
       <c r="C1" t="s">
-        <v>22111</v>
+        <v>23296</v>
       </c>
       <c r="D1" t="s">
-        <v>22112</v>
+        <v>23297</v>
       </c>
       <c r="E1" t="s">
-        <v>22113</v>
+        <v>23298</v>
       </c>
       <c r="F1" t="s">
-        <v>22114</v>
+        <v>23299</v>
       </c>
       <c r="G1" t="s">
-        <v>22115</v>
+        <v>23300</v>
       </c>
       <c r="H1" t="s">
-        <v>22116</v>
+        <v>23301</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22039</v>
+        <v>23224</v>
       </c>
       <c r="B2" t="s">
-        <v>22076</v>
+        <v>23261</v>
       </c>
       <c r="C2" s="1">
         <v>-35345.263380289784</v>
@@ -66464,10 +71441,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22040</v>
+        <v>23225</v>
       </c>
       <c r="B3" t="s">
-        <v>22077</v>
+        <v>23262</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -66486,10 +71463,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22049</v>
+        <v>23226</v>
       </c>
       <c r="B4" t="s">
-        <v>22085</v>
+        <v>23263</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -66506,10 +71483,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22041</v>
+        <v>23227</v>
       </c>
       <c r="B5" t="s">
-        <v>22078</v>
+        <v>23264</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -66526,10 +71503,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22042</v>
+        <v>23228</v>
       </c>
       <c r="B6" t="s">
-        <v>22079</v>
+        <v>23265</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -66542,10 +71519,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22043</v>
+        <v>23229</v>
       </c>
       <c r="B7" t="s">
-        <v>22080</v>
+        <v>23266</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -66562,10 +71539,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22044</v>
+        <v>23230</v>
       </c>
       <c r="B8" t="s">
-        <v>22081</v>
+        <v>23267</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -66580,10 +71557,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22045</v>
+        <v>23231</v>
       </c>
       <c r="B9" t="s">
-        <v>22081</v>
+        <v>23267</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -66596,10 +71573,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22046</v>
+        <v>23232</v>
       </c>
       <c r="B10" t="s">
-        <v>22082</v>
+        <v>23268</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -66614,10 +71591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22047</v>
+        <v>23233</v>
       </c>
       <c r="B11" t="s">
-        <v>22083</v>
+        <v>23269</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -66632,10 +71609,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22048</v>
+        <v>23234</v>
       </c>
       <c r="B12" t="s">
-        <v>22084</v>
+        <v>23270</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -66654,10 +71631,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22050</v>
+        <v>23235</v>
       </c>
       <c r="B13" t="s">
-        <v>22086</v>
+        <v>23271</v>
       </c>
       <c r="C13" s="1">
         <v>105254.84066842961</v>
@@ -66680,10 +71657,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22051</v>
+        <v>23236</v>
       </c>
       <c r="B14" t="s">
-        <v>22087</v>
+        <v>23272</v>
       </c>
       <c r="C14" s="1">
         <v>20118.629433262511</v>
@@ -66706,10 +71683,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22052</v>
+        <v>23237</v>
       </c>
       <c r="B15" t="s">
-        <v>22088</v>
+        <v>23273</v>
       </c>
       <c r="C15" s="1">
         <v>85136.211235167109</v>
@@ -66732,10 +71709,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22053</v>
+        <v>23238</v>
       </c>
       <c r="B16" t="s">
-        <v>22089</v>
+        <v>23274</v>
       </c>
       <c r="C16" s="1">
         <v>77979.086634604173</v>
@@ -66758,10 +71735,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22055</v>
+        <v>23239</v>
       </c>
       <c r="B17" t="s">
-        <v>22091</v>
+        <v>23275</v>
       </c>
       <c r="C17" s="1">
         <v>708.07373372999996</v>
@@ -66782,10 +71759,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22056</v>
+        <v>23240</v>
       </c>
       <c r="B18" t="s">
-        <v>22092</v>
+        <v>23276</v>
       </c>
       <c r="C18" s="1">
         <v>708.07373372999996</v>
@@ -66802,10 +71779,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22057</v>
+        <v>23241</v>
       </c>
       <c r="B19" t="s">
-        <v>22093</v>
+        <v>23277</v>
       </c>
       <c r="C19" s="1">
         <v>2128.9819248528388</v>
@@ -66828,10 +71805,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22059</v>
+        <v>23242</v>
       </c>
       <c r="B20" t="s">
-        <v>22095</v>
+        <v>23278</v>
       </c>
       <c r="C20" s="1">
         <v>610.943299077402</v>
@@ -66848,10 +71825,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22060</v>
+        <v>23243</v>
       </c>
       <c r="B21" t="s">
-        <v>22096</v>
+        <v>23279</v>
       </c>
       <c r="C21" s="1">
         <v>476.41603700000002</v>
@@ -66870,10 +71847,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22061</v>
+        <v>23244</v>
       </c>
       <c r="B22" t="s">
-        <v>22097</v>
+        <v>23280</v>
       </c>
       <c r="C22" s="1">
         <v>1041.622588775437</v>
@@ -66896,10 +71873,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22054</v>
+        <v>23245</v>
       </c>
       <c r="B23" t="s">
-        <v>22090</v>
+        <v>23281</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -66916,10 +71893,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22058</v>
+        <v>23246</v>
       </c>
       <c r="B24" t="s">
-        <v>22094</v>
+        <v>23282</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -66936,10 +71913,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22062</v>
+        <v>23247</v>
       </c>
       <c r="B25" t="s">
-        <v>22098</v>
+        <v>23283</v>
       </c>
       <c r="C25" s="1">
         <v>75685.254770642801</v>
@@ -66962,10 +71939,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22067</v>
+        <v>23248</v>
       </c>
       <c r="B26" t="s">
-        <v>22103</v>
+        <v>23284</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -66980,18 +71957,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22068</v>
+        <v>23249</v>
       </c>
       <c r="B27" t="s">
-        <v>22104</v>
+        <v>23285</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-3264.8749993161441</v>
+        <v>-3264.8749993161591</v>
       </c>
       <c r="F27" s="1">
-        <v>-3264.8749993161441</v>
+        <v>-3264.8749993161591</v>
       </c>
       <c r="G27" s="1">
         <v>65128.014697722727</v>
@@ -67002,10 +71979,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22065</v>
+        <v>23250</v>
       </c>
       <c r="B28" t="s">
-        <v>22101</v>
+        <v>23286</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -67020,10 +71997,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22066</v>
+        <v>23251</v>
       </c>
       <c r="B29" t="s">
-        <v>22102</v>
+        <v>23287</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -67042,10 +72019,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22067</v>
+        <v>23252</v>
       </c>
       <c r="B30" t="s">
-        <v>22103</v>
+        <v>23288</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -67060,18 +72037,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22068</v>
+        <v>23253</v>
       </c>
       <c r="B31" t="s">
-        <v>22104</v>
+        <v>23289</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-3264.8749993161591</v>
+        <v>-3264.8749993161441</v>
       </c>
       <c r="F31" s="1">
-        <v>-3264.8749993161591</v>
+        <v>-3264.8749993161441</v>
       </c>
       <c r="G31" s="1">
         <v>65128.014697722727</v>
@@ -67082,10 +72059,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>22069</v>
+        <v>23254</v>
       </c>
       <c r="B32" t="s">
-        <v>22105</v>
+        <v>23290</v>
       </c>
       <c r="C32" s="1">
         <v>40339.991390353032</v>
@@ -67100,10 +72077,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>22070</v>
+        <v>23255</v>
       </c>
       <c r="B33" t="s">
-        <v>22027</v>
+        <v>23291</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -67124,10 +72101,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22071</v>
+        <v>23256</v>
       </c>
       <c r="B34" t="s">
-        <v>22107</v>
+        <v>23292</v>
       </c>
       <c r="C34" s="1">
         <v>37886.776197581872</v>
@@ -67142,7 +72119,7 @@
         <v>-25147.551874929632</v>
       </c>
       <c r="G34" s="1">
-        <v>25446.753598644718</v>
+        <v>25446.753598644849</v>
       </c>
       <c r="H34" s="1">
         <v>25446.753598644718</v>
@@ -67150,10 +72127,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>22071</v>
+        <v>23256</v>
       </c>
       <c r="B35" t="s">
-        <v>22107</v>
+        <v>23292</v>
       </c>
       <c r="C35" s="1">
         <v>37886.776197581872</v>
@@ -67168,7 +72145,7 @@
         <v>-25147.551874929632</v>
       </c>
       <c r="G35" s="1">
-        <v>25446.753598644849</v>
+        <v>25446.753598644718</v>
       </c>
       <c r="H35" s="1">
         <v>25446.753598644849</v>
@@ -67176,53 +72153,53 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>22072</v>
+        <v>23257</v>
       </c>
       <c r="B36" t="s">
-        <v>22108</v>
+        <v>23293</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>113976.0975413</v>
+        <v>926.5806651800001</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="1">
-        <v>137582.86030768359</v>
-      </c>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22073</v>
+        <v>23258</v>
       </c>
       <c r="B37" t="s">
-        <v>22109</v>
+        <v>23294</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>79482.446760280014</v>
-      </c>
-      <c r="F37" s="1">
-        <v>79482.446760280014</v>
-      </c>
+        <v>113976.0975413</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="H37" s="1">
+        <v>137582.86030768359</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22074</v>
+        <v>23259</v>
       </c>
       <c r="B38" t="s">
-        <v>22110</v>
+        <v>23295</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>926.5806651800001</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>79482.446760280014</v>
+      </c>
+      <c r="F38" s="1">
+        <v>79482.446760280014</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -67237,36 +72214,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22038</v>
+        <v>23302</v>
       </c>
       <c r="B1" t="s">
-        <v>22075</v>
+        <v>23339</v>
       </c>
       <c r="C1" t="s">
-        <v>22111</v>
+        <v>23375</v>
       </c>
       <c r="D1" t="s">
-        <v>22112</v>
+        <v>23376</v>
       </c>
       <c r="E1" t="s">
-        <v>22113</v>
+        <v>23377</v>
       </c>
       <c r="F1" t="s">
-        <v>22114</v>
+        <v>23378</v>
       </c>
       <c r="G1" t="s">
-        <v>22115</v>
+        <v>23379</v>
       </c>
       <c r="H1" t="s">
-        <v>22116</v>
+        <v>23380</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22039</v>
+        <v>23303</v>
       </c>
       <c r="B2" t="s">
-        <v>22076</v>
+        <v>23340</v>
       </c>
       <c r="C2" s="1">
         <v>-92111.334701685584</v>
@@ -67281,10 +72258,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22040</v>
+        <v>23304</v>
       </c>
       <c r="B3" t="s">
-        <v>22077</v>
+        <v>23341</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -67303,10 +72280,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22049</v>
+        <v>23305</v>
       </c>
       <c r="B4" t="s">
-        <v>22085</v>
+        <v>23342</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -67323,10 +72300,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22041</v>
+        <v>23306</v>
       </c>
       <c r="B5" t="s">
-        <v>22078</v>
+        <v>23343</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -67343,10 +72320,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22042</v>
+        <v>23307</v>
       </c>
       <c r="B6" t="s">
-        <v>22079</v>
+        <v>23344</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -67359,10 +72336,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22043</v>
+        <v>23308</v>
       </c>
       <c r="B7" t="s">
-        <v>22080</v>
+        <v>23345</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -67379,10 +72356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22044</v>
+        <v>23309</v>
       </c>
       <c r="B8" t="s">
-        <v>22081</v>
+        <v>23346</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -67395,10 +72372,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22045</v>
+        <v>23310</v>
       </c>
       <c r="B9" t="s">
-        <v>22081</v>
+        <v>23346</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -67411,10 +72388,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22046</v>
+        <v>23311</v>
       </c>
       <c r="B10" t="s">
-        <v>22082</v>
+        <v>23347</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -67427,10 +72404,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22047</v>
+        <v>23312</v>
       </c>
       <c r="B11" t="s">
-        <v>22083</v>
+        <v>23348</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -67445,10 +72422,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22048</v>
+        <v>23313</v>
       </c>
       <c r="B12" t="s">
-        <v>22084</v>
+        <v>23349</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -67467,10 +72444,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22050</v>
+        <v>23314</v>
       </c>
       <c r="B13" t="s">
-        <v>22086</v>
+        <v>23350</v>
       </c>
       <c r="C13" s="1">
         <v>111912.2883479437</v>
@@ -67493,10 +72470,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22051</v>
+        <v>23315</v>
       </c>
       <c r="B14" t="s">
-        <v>22087</v>
+        <v>23351</v>
       </c>
       <c r="C14" s="1">
         <v>37196.900831416431</v>
@@ -67519,10 +72496,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22052</v>
+        <v>23316</v>
       </c>
       <c r="B15" t="s">
-        <v>22088</v>
+        <v>23352</v>
       </c>
       <c r="C15" s="1">
         <v>74715.387516527291</v>
@@ -67545,10 +72522,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22053</v>
+        <v>23317</v>
       </c>
       <c r="B16" t="s">
-        <v>22089</v>
+        <v>23353</v>
       </c>
       <c r="C16" s="1">
         <v>81203.449470399617</v>
@@ -67571,10 +72548,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22055</v>
+        <v>23318</v>
       </c>
       <c r="B17" t="s">
-        <v>22091</v>
+        <v>23354</v>
       </c>
       <c r="C17" s="1">
         <v>1114.5240200000001</v>
@@ -67595,10 +72572,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22056</v>
+        <v>23319</v>
       </c>
       <c r="B18" t="s">
-        <v>22092</v>
+        <v>23355</v>
       </c>
       <c r="C18" s="1">
         <v>1114.5240200000001</v>
@@ -67617,10 +72594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22057</v>
+        <v>23320</v>
       </c>
       <c r="B19" t="s">
-        <v>22093</v>
+        <v>23356</v>
       </c>
       <c r="C19" s="1">
         <v>17219.038211090661</v>
@@ -67643,10 +72620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22058</v>
+        <v>23321</v>
       </c>
       <c r="B20" t="s">
-        <v>22094</v>
+        <v>23357</v>
       </c>
       <c r="C20" s="1">
         <v>98.619980999999996</v>
@@ -67665,10 +72642,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22059</v>
+        <v>23322</v>
       </c>
       <c r="B21" t="s">
-        <v>22095</v>
+        <v>23358</v>
       </c>
       <c r="C21" s="1">
         <v>1657.9772827899999</v>
@@ -67685,10 +72662,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22060</v>
+        <v>23323</v>
       </c>
       <c r="B22" t="s">
-        <v>22096</v>
+        <v>23359</v>
       </c>
       <c r="C22" s="1">
         <v>1009.104553</v>
@@ -67707,10 +72684,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22061</v>
+        <v>23324</v>
       </c>
       <c r="B23" t="s">
-        <v>22097</v>
+        <v>23360</v>
       </c>
       <c r="C23" s="1">
         <v>14453.336394300661</v>
@@ -67733,10 +72710,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22054</v>
+        <v>23325</v>
       </c>
       <c r="B24" t="s">
-        <v>22090</v>
+        <v>23361</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -67755,10 +72732,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22062</v>
+        <v>23326</v>
       </c>
       <c r="B25" t="s">
-        <v>22098</v>
+        <v>23362</v>
       </c>
       <c r="C25" s="1">
         <v>79087.001794051394</v>
@@ -67781,10 +72758,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22067</v>
+        <v>23327</v>
       </c>
       <c r="B26" t="s">
-        <v>22103</v>
+        <v>23363</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -67799,10 +72776,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22068</v>
+        <v>23328</v>
       </c>
       <c r="B27" t="s">
-        <v>22104</v>
+        <v>23364</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -67810,7 +72787,7 @@
         <v>-10570.434075028639</v>
       </c>
       <c r="F27" s="1">
-        <v>-10570.43407502865</v>
+        <v>-10570.434075028639</v>
       </c>
       <c r="G27" s="1">
         <v>124508.5573505638</v>
@@ -67821,10 +72798,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22065</v>
+        <v>23329</v>
       </c>
       <c r="B28" t="s">
-        <v>22101</v>
+        <v>23365</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -67839,10 +72816,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22066</v>
+        <v>23330</v>
       </c>
       <c r="B29" t="s">
-        <v>22102</v>
+        <v>23366</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -67861,10 +72838,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22067</v>
+        <v>23331</v>
       </c>
       <c r="B30" t="s">
-        <v>22103</v>
+        <v>23367</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -67879,10 +72856,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22068</v>
+        <v>23332</v>
       </c>
       <c r="B31" t="s">
-        <v>22104</v>
+        <v>23368</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -67890,7 +72867,7 @@
         <v>-10570.43407502865</v>
       </c>
       <c r="F31" s="1">
-        <v>-10570.434075028639</v>
+        <v>-10570.43407502865</v>
       </c>
       <c r="G31" s="1">
         <v>124508.5573505638</v>
@@ -67901,10 +72878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>22069</v>
+        <v>23333</v>
       </c>
       <c r="B32" t="s">
-        <v>22105</v>
+        <v>23369</v>
       </c>
       <c r="C32" s="1">
         <v>-13024.332907634191</v>
@@ -67919,10 +72896,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>22070</v>
+        <v>23334</v>
       </c>
       <c r="B33" t="s">
-        <v>22106</v>
+        <v>23370</v>
       </c>
       <c r="C33" s="1">
         <v>181.0641172</v>
@@ -67945,19 +72922,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22071</v>
+        <v>23335</v>
       </c>
       <c r="B34" t="s">
-        <v>22107</v>
+        <v>23371</v>
       </c>
       <c r="C34" s="1">
         <v>-14574.43484844782</v>
       </c>
       <c r="D34" s="1">
-        <v>-14574.434848447811</v>
+        <v>-14574.43484844782</v>
       </c>
       <c r="E34" s="1">
-        <v>-66950.582658753861</v>
+        <v>-66950.582658753847</v>
       </c>
       <c r="F34" s="1">
         <v>-66950.582658753861</v>
@@ -67971,19 +72948,19 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>22071</v>
+        <v>23335</v>
       </c>
       <c r="B35" t="s">
-        <v>22107</v>
+        <v>23371</v>
       </c>
       <c r="C35" s="1">
         <v>-14574.434848447811</v>
       </c>
       <c r="D35" s="1">
-        <v>-14574.43484844782</v>
+        <v>-14574.434848447811</v>
       </c>
       <c r="E35" s="1">
-        <v>-66950.582658753847</v>
+        <v>-66950.582658753861</v>
       </c>
       <c r="F35" s="1">
         <v>-66950.582658753847</v>
@@ -67997,57 +72974,57 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>22074</v>
+        <v>23336</v>
       </c>
       <c r="B36" t="s">
-        <v>22110</v>
+        <v>23372</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>1410.7265588499999</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>147042.35994689999</v>
+      </c>
+      <c r="F36" s="1">
+        <v>147042.21094677999</v>
+      </c>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22073</v>
+        <v>23337</v>
       </c>
       <c r="B37" t="s">
-        <v>22109</v>
+        <v>23373</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>147042.35994689999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>147042.21094677999</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+        <v>181558.9914336357</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>310.92989817709997</v>
+      </c>
+      <c r="H37" s="1">
+        <v>223683.25268700649</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22072</v>
+        <v>23338</v>
       </c>
       <c r="B38" t="s">
-        <v>22108</v>
+        <v>23374</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>181558.9914336357</v>
+        <v>1410.7265588499999</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1">
-        <v>310.92989817709997</v>
-      </c>
-      <c r="H38" s="1">
-        <v>223683.25268700649</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -68060,36 +73037,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22038</v>
+        <v>23381</v>
       </c>
       <c r="B1" t="s">
-        <v>22075</v>
+        <v>23418</v>
       </c>
       <c r="C1" t="s">
-        <v>22111</v>
+        <v>23454</v>
       </c>
       <c r="D1" t="s">
-        <v>22112</v>
+        <v>23455</v>
       </c>
       <c r="E1" t="s">
-        <v>22113</v>
+        <v>23456</v>
       </c>
       <c r="F1" t="s">
-        <v>22114</v>
+        <v>23457</v>
       </c>
       <c r="G1" t="s">
-        <v>22115</v>
+        <v>23458</v>
       </c>
       <c r="H1" t="s">
-        <v>22116</v>
+        <v>23459</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22039</v>
+        <v>23382</v>
       </c>
       <c r="B2" t="s">
-        <v>22076</v>
+        <v>23419</v>
       </c>
       <c r="C2" s="1">
         <v>-102236.23721409201</v>
@@ -68104,10 +73081,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22040</v>
+        <v>23383</v>
       </c>
       <c r="B3" t="s">
-        <v>22077</v>
+        <v>23420</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -68126,10 +73103,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22041</v>
+        <v>23384</v>
       </c>
       <c r="B4" t="s">
-        <v>22078</v>
+        <v>23421</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -68146,10 +73123,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22042</v>
+        <v>23385</v>
       </c>
       <c r="B5" t="s">
-        <v>22079</v>
+        <v>23422</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -68162,10 +73139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22043</v>
+        <v>23386</v>
       </c>
       <c r="B6" t="s">
-        <v>22080</v>
+        <v>23423</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -68182,10 +73159,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22044</v>
+        <v>23387</v>
       </c>
       <c r="B7" t="s">
-        <v>22081</v>
+        <v>23424</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -68198,10 +73175,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22045</v>
+        <v>23388</v>
       </c>
       <c r="B8" t="s">
-        <v>22081</v>
+        <v>23424</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -68214,10 +73191,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22046</v>
+        <v>23389</v>
       </c>
       <c r="B9" t="s">
-        <v>22082</v>
+        <v>23425</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -68230,10 +73207,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22047</v>
+        <v>23390</v>
       </c>
       <c r="B10" t="s">
-        <v>22083</v>
+        <v>23426</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -68248,10 +73225,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22048</v>
+        <v>23391</v>
       </c>
       <c r="B11" t="s">
-        <v>22084</v>
+        <v>23427</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -68270,10 +73247,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22049</v>
+        <v>23392</v>
       </c>
       <c r="B12" t="s">
-        <v>22085</v>
+        <v>23428</v>
       </c>
       <c r="C12" s="1">
         <v>-83.070126027215935</v>
@@ -68292,10 +73269,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22050</v>
+        <v>23393</v>
       </c>
       <c r="B13" t="s">
-        <v>22086</v>
+        <v>23429</v>
       </c>
       <c r="C13" s="1">
         <v>144279.01796396461</v>
@@ -68318,10 +73295,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22051</v>
+        <v>23394</v>
       </c>
       <c r="B14" t="s">
-        <v>22087</v>
+        <v>23430</v>
       </c>
       <c r="C14" s="1">
         <v>32414.538114762661</v>
@@ -68344,10 +73321,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22052</v>
+        <v>23395</v>
       </c>
       <c r="B15" t="s">
-        <v>22088</v>
+        <v>23431</v>
       </c>
       <c r="C15" s="1">
         <v>111864.47984920201</v>
@@ -68368,10 +73345,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22053</v>
+        <v>23396</v>
       </c>
       <c r="B16" t="s">
-        <v>22089</v>
+        <v>23432</v>
       </c>
       <c r="C16" s="1">
         <v>101315.1098362044</v>
@@ -68394,10 +73371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22054</v>
+        <v>23397</v>
       </c>
       <c r="B17" t="s">
-        <v>22090</v>
+        <v>23433</v>
       </c>
       <c r="C17" s="1">
         <v>526.84154559200761</v>
@@ -68418,10 +73395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22055</v>
+        <v>23398</v>
       </c>
       <c r="B18" t="s">
-        <v>22091</v>
+        <v>23434</v>
       </c>
       <c r="C18" s="1">
         <v>1300.503467</v>
@@ -68442,10 +73419,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22056</v>
+        <v>23399</v>
       </c>
       <c r="B19" t="s">
-        <v>22092</v>
+        <v>23435</v>
       </c>
       <c r="C19" s="1">
         <v>1300.503467</v>
@@ -68464,10 +73441,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22057</v>
+        <v>23400</v>
       </c>
       <c r="B20" t="s">
-        <v>22093</v>
+        <v>23436</v>
       </c>
       <c r="C20" s="1">
         <v>16387.63379557012</v>
@@ -68490,10 +73467,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22058</v>
+        <v>23401</v>
       </c>
       <c r="B21" t="s">
-        <v>22094</v>
+        <v>23437</v>
       </c>
       <c r="C21" s="1">
         <v>97.490238000000005</v>
@@ -68512,10 +73489,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22059</v>
+        <v>23402</v>
       </c>
       <c r="B22" t="s">
-        <v>22095</v>
+        <v>23438</v>
       </c>
       <c r="C22" s="1">
         <v>1386.9169386399999</v>
@@ -68532,10 +73509,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22060</v>
+        <v>23403</v>
       </c>
       <c r="B23" t="s">
-        <v>22096</v>
+        <v>23439</v>
       </c>
       <c r="C23" s="1">
         <v>1117.864241</v>
@@ -68554,10 +73531,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22061</v>
+        <v>23404</v>
       </c>
       <c r="B24" t="s">
-        <v>22097</v>
+        <v>23440</v>
       </c>
       <c r="C24" s="1">
         <v>13785.36237793012</v>
@@ -68580,10 +73557,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22062</v>
+        <v>23405</v>
       </c>
       <c r="B25" t="s">
-        <v>22098</v>
+        <v>23441</v>
       </c>
       <c r="C25" s="1">
         <v>98850.343655568271</v>
@@ -68606,10 +73583,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22067</v>
+        <v>23406</v>
       </c>
       <c r="B26" t="s">
-        <v>22103</v>
+        <v>23442</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -68624,18 +73601,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22068</v>
+        <v>23407</v>
       </c>
       <c r="B27" t="s">
-        <v>22104</v>
+        <v>23443</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-25017.38878234318</v>
+        <v>-25017.388782343201</v>
       </c>
       <c r="F27" s="1">
-        <v>-25017.38878234318</v>
+        <v>-25017.388782343201</v>
       </c>
       <c r="G27" s="1">
         <v>118456.4656790759</v>
@@ -68646,10 +73623,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22065</v>
+        <v>23408</v>
       </c>
       <c r="B28" t="s">
-        <v>22101</v>
+        <v>23444</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -68664,10 +73641,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22066</v>
+        <v>23409</v>
       </c>
       <c r="B29" t="s">
-        <v>22102</v>
+        <v>23445</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -68686,10 +73663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22067</v>
+        <v>23410</v>
       </c>
       <c r="B30" t="s">
-        <v>22103</v>
+        <v>23446</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -68704,18 +73681,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22068</v>
+        <v>23411</v>
       </c>
       <c r="B31" t="s">
-        <v>22104</v>
+        <v>23447</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-25017.388782343201</v>
+        <v>-25017.38878234318</v>
       </c>
       <c r="F31" s="1">
-        <v>-25017.388782343201</v>
+        <v>-25017.38878234318</v>
       </c>
       <c r="G31" s="1">
         <v>118456.4656790759</v>
@@ -68726,10 +73703,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>22069</v>
+        <v>23412</v>
       </c>
       <c r="B32" t="s">
-        <v>22105</v>
+        <v>23448</v>
       </c>
       <c r="C32" s="1">
         <v>-3385.8935585237782</v>
@@ -68744,10 +73721,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>22070</v>
+        <v>23413</v>
       </c>
       <c r="B33" t="s">
-        <v>22106</v>
+        <v>23449</v>
       </c>
       <c r="C33" s="1">
         <v>0.27703699999999998</v>
@@ -68770,19 +73747,19 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22071</v>
+        <v>23414</v>
       </c>
       <c r="B34" t="s">
-        <v>22107</v>
+        <v>23450</v>
       </c>
       <c r="C34" s="1">
         <v>-4009.0753441289771</v>
       </c>
       <c r="D34" s="1">
-        <v>-4009.0753441289771</v>
+        <v>-4009.0753441289712</v>
       </c>
       <c r="E34" s="1">
-        <v>-63565.770979082881</v>
+        <v>-63565.818181042087</v>
       </c>
       <c r="F34" s="1">
         <v>-63565.770979082881</v>
@@ -68791,24 +73768,24 @@
         <v>43782.161676834643</v>
       </c>
       <c r="H34" s="1">
-        <v>43782.161676834643</v>
+        <v>43782.161676835007</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>22071</v>
+        <v>23414</v>
       </c>
       <c r="B35" t="s">
-        <v>22107</v>
+        <v>23450</v>
       </c>
       <c r="C35" s="1">
         <v>-4009.0753441289712</v>
       </c>
       <c r="D35" s="1">
-        <v>-4009.0753441289712</v>
+        <v>-4009.0753441289771</v>
       </c>
       <c r="E35" s="1">
-        <v>-63565.818181042087</v>
+        <v>-63565.770979082881</v>
       </c>
       <c r="F35" s="1">
         <v>-63565.818181042087</v>
@@ -68817,53 +73794,53 @@
         <v>43782.161676835007</v>
       </c>
       <c r="H35" s="1">
-        <v>43782.161676835007</v>
+        <v>43782.161676834643</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>22072</v>
+        <v>23415</v>
       </c>
       <c r="B36" t="s">
-        <v>22108</v>
+        <v>23451</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>201604.21968480741</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>337.34758922499998</v>
-      </c>
-      <c r="H36" s="1">
-        <v>253381.7166756459</v>
-      </c>
+        <v>170013.75605207999</v>
+      </c>
+      <c r="F36" s="1">
+        <v>170013.75605207999</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22073</v>
+        <v>23416</v>
       </c>
       <c r="B37" t="s">
-        <v>22109</v>
+        <v>23452</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+        <v>201604.21968480741</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>337.34758922499998</v>
+      </c>
+      <c r="H37" s="1">
+        <v>253381.7166756459</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22074</v>
+        <v>23417</v>
       </c>
       <c r="B38" t="s">
-        <v>22110</v>
+        <v>23453</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -68885,36 +73862,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22038</v>
+        <v>23460</v>
       </c>
       <c r="B1" t="s">
-        <v>22075</v>
+        <v>23497</v>
       </c>
       <c r="C1" t="s">
-        <v>22111</v>
+        <v>23533</v>
       </c>
       <c r="D1" t="s">
-        <v>22112</v>
+        <v>23534</v>
       </c>
       <c r="E1" t="s">
-        <v>22113</v>
+        <v>23535</v>
       </c>
       <c r="F1" t="s">
-        <v>22114</v>
+        <v>23536</v>
       </c>
       <c r="G1" t="s">
-        <v>22115</v>
+        <v>23537</v>
       </c>
       <c r="H1" t="s">
-        <v>22116</v>
+        <v>23538</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22039</v>
+        <v>23461</v>
       </c>
       <c r="B2" t="s">
-        <v>22076</v>
+        <v>23498</v>
       </c>
       <c r="C2" s="1">
         <v>-101427.2938489076</v>
@@ -68929,10 +73906,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22040</v>
+        <v>23462</v>
       </c>
       <c r="B3" t="s">
-        <v>22077</v>
+        <v>23499</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -68951,10 +73928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22041</v>
+        <v>23463</v>
       </c>
       <c r="B4" t="s">
-        <v>22078</v>
+        <v>23500</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -68971,10 +73948,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22042</v>
+        <v>23464</v>
       </c>
       <c r="B5" t="s">
-        <v>22079</v>
+        <v>23501</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -68987,10 +73964,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22043</v>
+        <v>23465</v>
       </c>
       <c r="B6" t="s">
-        <v>22080</v>
+        <v>23502</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -69007,10 +73984,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22044</v>
+        <v>23466</v>
       </c>
       <c r="B7" t="s">
-        <v>22081</v>
+        <v>23503</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -69023,10 +74000,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22045</v>
+        <v>23467</v>
       </c>
       <c r="B8" t="s">
-        <v>22081</v>
+        <v>23503</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -69039,10 +74016,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22046</v>
+        <v>23468</v>
       </c>
       <c r="B9" t="s">
-        <v>22082</v>
+        <v>23504</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -69055,10 +74032,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22047</v>
+        <v>23469</v>
       </c>
       <c r="B10" t="s">
-        <v>22083</v>
+        <v>23505</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -69073,10 +74050,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22048</v>
+        <v>23470</v>
       </c>
       <c r="B11" t="s">
-        <v>22084</v>
+        <v>23506</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -69095,10 +74072,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22049</v>
+        <v>23471</v>
       </c>
       <c r="B12" t="s">
-        <v>22085</v>
+        <v>23507</v>
       </c>
       <c r="C12" s="1">
         <v>-92.934358778526615</v>
@@ -69117,10 +74094,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22050</v>
+        <v>23472</v>
       </c>
       <c r="B13" t="s">
-        <v>22086</v>
+        <v>23508</v>
       </c>
       <c r="C13" s="1">
         <v>162249.8021316196</v>
@@ -69143,10 +74120,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22051</v>
+        <v>23473</v>
       </c>
       <c r="B14" t="s">
-        <v>22087</v>
+        <v>23509</v>
       </c>
       <c r="C14" s="1">
         <v>43179.357846405859</v>
@@ -69169,10 +74146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22052</v>
+        <v>23474</v>
       </c>
       <c r="B15" t="s">
-        <v>22088</v>
+        <v>23510</v>
       </c>
       <c r="C15" s="1">
         <v>119070.4442852137</v>
@@ -69193,10 +74170,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22053</v>
+        <v>23475</v>
       </c>
       <c r="B16" t="s">
-        <v>22089</v>
+        <v>23511</v>
       </c>
       <c r="C16" s="1">
         <v>111072.9372501466</v>
@@ -69219,10 +74196,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22054</v>
+        <v>23476</v>
       </c>
       <c r="B17" t="s">
-        <v>22090</v>
+        <v>23512</v>
       </c>
       <c r="C17" s="1">
         <v>455.25087191519339</v>
@@ -69243,10 +74220,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22055</v>
+        <v>23477</v>
       </c>
       <c r="B18" t="s">
-        <v>22091</v>
+        <v>23513</v>
       </c>
       <c r="C18" s="1">
         <v>1486.8528134281901</v>
@@ -69267,10 +74244,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22056</v>
+        <v>23478</v>
       </c>
       <c r="B19" t="s">
-        <v>22092</v>
+        <v>23514</v>
       </c>
       <c r="C19" s="1">
         <v>1486.8528134281901</v>
@@ -69289,10 +74266,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22057</v>
+        <v>23479</v>
       </c>
       <c r="B20" t="s">
-        <v>22093</v>
+        <v>23515</v>
       </c>
       <c r="C20" s="1">
         <v>19645.88621086465</v>
@@ -69315,10 +74292,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22058</v>
+        <v>23480</v>
       </c>
       <c r="B21" t="s">
-        <v>22094</v>
+        <v>23516</v>
       </c>
       <c r="C21" s="1">
         <v>1.3780870000000001</v>
@@ -69337,10 +74314,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22059</v>
+        <v>23481</v>
       </c>
       <c r="B22" t="s">
-        <v>22095</v>
+        <v>23517</v>
       </c>
       <c r="C22" s="1">
         <v>1680.6084285300001</v>
@@ -69357,10 +74334,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22060</v>
+        <v>23482</v>
       </c>
       <c r="B23" t="s">
-        <v>22096</v>
+        <v>23518</v>
       </c>
       <c r="C23" s="1">
         <v>1167.0419095569939</v>
@@ -69379,10 +74356,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22061</v>
+        <v>23483</v>
       </c>
       <c r="B24" t="s">
-        <v>22097</v>
+        <v>23519</v>
       </c>
       <c r="C24" s="1">
         <v>16796.857785777662</v>
@@ -69405,10 +74382,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22062</v>
+        <v>23484</v>
       </c>
       <c r="B25" t="s">
-        <v>22098</v>
+        <v>23520</v>
       </c>
       <c r="C25" s="1">
         <v>108339.94151571881</v>
@@ -69431,10 +74408,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22067</v>
+        <v>23485</v>
       </c>
       <c r="B26" t="s">
-        <v>22103</v>
+        <v>23521</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -69447,10 +74424,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22068</v>
+        <v>23486</v>
       </c>
       <c r="B27" t="s">
-        <v>22104</v>
+        <v>23522</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -69469,10 +74446,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22065</v>
+        <v>23487</v>
       </c>
       <c r="B28" t="s">
-        <v>22101</v>
+        <v>23523</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -69487,10 +74464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22066</v>
+        <v>23488</v>
       </c>
       <c r="B29" t="s">
-        <v>22102</v>
+        <v>23524</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -69509,10 +74486,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22067</v>
+        <v>23489</v>
       </c>
       <c r="B30" t="s">
-        <v>22103</v>
+        <v>23525</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -69525,10 +74502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22068</v>
+        <v>23490</v>
       </c>
       <c r="B31" t="s">
-        <v>22104</v>
+        <v>23526</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -69547,10 +74524,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>22069</v>
+        <v>23491</v>
       </c>
       <c r="B32" t="s">
-        <v>22105</v>
+        <v>23527</v>
       </c>
       <c r="C32" s="1">
         <v>6912.6476668112009</v>
@@ -69565,10 +74542,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>22070</v>
+        <v>23492</v>
       </c>
       <c r="B33" t="s">
-        <v>22027</v>
+        <v>23528</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -69589,10 +74566,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22071</v>
+        <v>23493</v>
       </c>
       <c r="B34" t="s">
-        <v>22107</v>
+        <v>23529</v>
       </c>
       <c r="C34" s="1">
         <v>5442.5976345336867</v>
@@ -69615,10 +74592,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>22071</v>
+        <v>23493</v>
       </c>
       <c r="B35" t="s">
-        <v>22107</v>
+        <v>23529</v>
       </c>
       <c r="C35" s="1">
         <v>5442.5976345336967</v>
@@ -69641,57 +74618,57 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>22072</v>
+        <v>23494</v>
       </c>
       <c r="B36" t="s">
-        <v>22108</v>
+        <v>23530</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>215925.528549476</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>381.05244255449912</v>
-      </c>
-      <c r="H36" s="1">
-        <v>271956.46735150547</v>
-      </c>
+        <v>207169.67690947151</v>
+      </c>
+      <c r="F36" s="1">
+        <v>207169.67690947151</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22073</v>
+        <v>23495</v>
       </c>
       <c r="B37" t="s">
-        <v>22109</v>
+        <v>23531</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>207169.67690947151</v>
-      </c>
-      <c r="F37" s="1">
-        <v>207169.67690947151</v>
-      </c>
+        <v>1640.019891895929</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22074</v>
+        <v>23496</v>
       </c>
       <c r="B38" t="s">
-        <v>22110</v>
+        <v>23532</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1640.019891895929</v>
+        <v>215925.528549476</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="G38" s="1">
+        <v>381.05244255449912</v>
+      </c>
+      <c r="H38" s="1">
+        <v>271956.46735150547</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -69704,36 +74681,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22038</v>
+        <v>23539</v>
       </c>
       <c r="B1" t="s">
-        <v>22075</v>
+        <v>23576</v>
       </c>
       <c r="C1" t="s">
-        <v>22111</v>
+        <v>23612</v>
       </c>
       <c r="D1" t="s">
-        <v>22112</v>
+        <v>23613</v>
       </c>
       <c r="E1" t="s">
-        <v>22113</v>
+        <v>23614</v>
       </c>
       <c r="F1" t="s">
-        <v>22114</v>
+        <v>23615</v>
       </c>
       <c r="G1" t="s">
-        <v>22115</v>
+        <v>23616</v>
       </c>
       <c r="H1" t="s">
-        <v>22116</v>
+        <v>23617</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22039</v>
+        <v>23540</v>
       </c>
       <c r="B2" t="s">
-        <v>22076</v>
+        <v>23577</v>
       </c>
       <c r="C2" s="1">
         <v>-132325.81806931089</v>
@@ -69748,10 +74725,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22040</v>
+        <v>23541</v>
       </c>
       <c r="B3" t="s">
-        <v>22077</v>
+        <v>23578</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -69770,10 +74747,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22041</v>
+        <v>23542</v>
       </c>
       <c r="B4" t="s">
-        <v>22078</v>
+        <v>23579</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -69790,10 +74767,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22042</v>
+        <v>23543</v>
       </c>
       <c r="B5" t="s">
-        <v>22079</v>
+        <v>23580</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -69806,10 +74783,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22043</v>
+        <v>23544</v>
       </c>
       <c r="B6" t="s">
-        <v>22080</v>
+        <v>23581</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -69826,10 +74803,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22044</v>
+        <v>23545</v>
       </c>
       <c r="B7" t="s">
-        <v>22081</v>
+        <v>23582</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -69842,10 +74819,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22045</v>
+        <v>23546</v>
       </c>
       <c r="B8" t="s">
-        <v>22081</v>
+        <v>23582</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -69858,10 +74835,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22046</v>
+        <v>23547</v>
       </c>
       <c r="B9" t="s">
-        <v>22082</v>
+        <v>23583</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -69874,10 +74851,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22047</v>
+        <v>23548</v>
       </c>
       <c r="B10" t="s">
-        <v>22083</v>
+        <v>23584</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -69892,10 +74869,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22048</v>
+        <v>23549</v>
       </c>
       <c r="B11" t="s">
-        <v>22084</v>
+        <v>23585</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -69914,10 +74891,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22049</v>
+        <v>23550</v>
       </c>
       <c r="B12" t="s">
-        <v>22085</v>
+        <v>23586</v>
       </c>
       <c r="C12" s="1">
         <v>-111.3731775422125</v>
@@ -69936,10 +74913,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22050</v>
+        <v>23551</v>
       </c>
       <c r="B13" t="s">
-        <v>22086</v>
+        <v>23587</v>
       </c>
       <c r="C13" s="1">
         <v>160506.74429795379</v>
@@ -69962,10 +74939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22051</v>
+        <v>23552</v>
       </c>
       <c r="B14" t="s">
-        <v>22087</v>
+        <v>23588</v>
       </c>
       <c r="C14" s="1">
         <v>47266.390163401513</v>
@@ -69988,10 +74965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22052</v>
+        <v>23553</v>
       </c>
       <c r="B15" t="s">
-        <v>22088</v>
+        <v>23589</v>
       </c>
       <c r="C15" s="1">
         <v>113240.3541345523</v>
@@ -70012,10 +74989,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22053</v>
+        <v>23554</v>
       </c>
       <c r="B16" t="s">
-        <v>22089</v>
+        <v>23590</v>
       </c>
       <c r="C16" s="1">
         <v>106078.98298231589</v>
@@ -70038,10 +75015,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22054</v>
+        <v>23555</v>
       </c>
       <c r="B17" t="s">
-        <v>22090</v>
+        <v>23591</v>
       </c>
       <c r="C17" s="1">
         <v>376.90302765656929</v>
@@ -70062,10 +75039,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22055</v>
+        <v>23556</v>
       </c>
       <c r="B18" t="s">
-        <v>22091</v>
+        <v>23592</v>
       </c>
       <c r="C18" s="1">
         <v>1655.657643517555</v>
@@ -70086,10 +75063,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22056</v>
+        <v>23557</v>
       </c>
       <c r="B19" t="s">
-        <v>22092</v>
+        <v>23593</v>
       </c>
       <c r="C19" s="1">
         <v>1655.657643517555</v>
@@ -70108,10 +75085,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22057</v>
+        <v>23558</v>
       </c>
       <c r="B20" t="s">
-        <v>22093</v>
+        <v>23594</v>
       </c>
       <c r="C20" s="1">
         <v>22226.602795191338</v>
@@ -70134,10 +75111,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22058</v>
+        <v>23559</v>
       </c>
       <c r="B21" t="s">
-        <v>22094</v>
+        <v>23595</v>
       </c>
       <c r="C21" s="1">
         <v>2.9676309999999999</v>
@@ -70156,10 +75133,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22059</v>
+        <v>23560</v>
       </c>
       <c r="B22" t="s">
-        <v>22095</v>
+        <v>23596</v>
       </c>
       <c r="C22" s="1">
         <v>2646.0630505200002</v>
@@ -70176,10 +75153,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22060</v>
+        <v>23561</v>
       </c>
       <c r="B23" t="s">
-        <v>22096</v>
+        <v>23597</v>
       </c>
       <c r="C23" s="1">
         <v>1452.5266412882031</v>
@@ -70198,10 +75175,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22061</v>
+        <v>23562</v>
       </c>
       <c r="B24" t="s">
-        <v>22097</v>
+        <v>23598</v>
       </c>
       <c r="C24" s="1">
         <v>18125.045472383139</v>
@@ -70224,10 +75201,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22062</v>
+        <v>23563</v>
       </c>
       <c r="B25" t="s">
-        <v>22098</v>
+        <v>23599</v>
       </c>
       <c r="C25" s="1">
         <v>103687.46021795391</v>
@@ -70250,10 +75227,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22067</v>
+        <v>23564</v>
       </c>
       <c r="B26" t="s">
-        <v>22103</v>
+        <v>23600</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -70266,18 +75243,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22068</v>
+        <v>23565</v>
       </c>
       <c r="B27" t="s">
-        <v>22104</v>
+        <v>23601</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-47487.012322160852</v>
+        <v>-47487.012322160823</v>
       </c>
       <c r="F27" s="1">
-        <v>-47487.012322160852</v>
+        <v>-47487.012322160823</v>
       </c>
       <c r="G27" s="1">
         <v>137422.3722114753</v>
@@ -70288,10 +75265,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22065</v>
+        <v>23566</v>
       </c>
       <c r="B28" t="s">
-        <v>22101</v>
+        <v>23602</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -70306,10 +75283,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22066</v>
+        <v>23567</v>
       </c>
       <c r="B29" t="s">
-        <v>22102</v>
+        <v>23603</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -70328,10 +75305,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22067</v>
+        <v>23568</v>
       </c>
       <c r="B30" t="s">
-        <v>22103</v>
+        <v>23604</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -70344,18 +75321,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22068</v>
+        <v>23569</v>
       </c>
       <c r="B31" t="s">
-        <v>22104</v>
+        <v>23605</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-47487.012322160823</v>
+        <v>-47487.012322160852</v>
       </c>
       <c r="F31" s="1">
-        <v>-47487.012322160823</v>
+        <v>-47487.012322160852</v>
       </c>
       <c r="G31" s="1">
         <v>137422.3722114753</v>
@@ -70366,10 +75343,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>22069</v>
+        <v>23570</v>
       </c>
       <c r="B32" t="s">
-        <v>22105</v>
+        <v>23606</v>
       </c>
       <c r="C32" s="1">
         <v>-28638.357851356981</v>
@@ -70384,10 +75361,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>22070</v>
+        <v>23571</v>
       </c>
       <c r="B33" t="s">
-        <v>22106</v>
+        <v>23607</v>
       </c>
       <c r="C33" s="1">
         <v>13.58729015431644</v>
@@ -70410,10 +75387,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22071</v>
+        <v>23572</v>
       </c>
       <c r="B34" t="s">
-        <v>22107</v>
+        <v>23608</v>
       </c>
       <c r="C34" s="1">
         <v>-14516.140951382629</v>
@@ -70422,24 +75399,24 @@
         <v>-14516.140951382629</v>
       </c>
       <c r="E34" s="1">
-        <v>-63947.039175030113</v>
+        <v>-63947.039175029808</v>
       </c>
       <c r="F34" s="1">
-        <v>-63947.039175030113</v>
+        <v>-63947.039175029808</v>
       </c>
       <c r="G34" s="1">
         <v>39248.472782472993</v>
       </c>
       <c r="H34" s="1">
-        <v>39248.472782472993</v>
+        <v>39248.472782472847</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>22071</v>
+        <v>23572</v>
       </c>
       <c r="B35" t="s">
-        <v>22107</v>
+        <v>23608</v>
       </c>
       <c r="C35" s="1">
         <v>-14516.15048177604</v>
@@ -70448,42 +75425,40 @@
         <v>-14516.15048177604</v>
       </c>
       <c r="E35" s="1">
-        <v>-63947.039175029808</v>
+        <v>-63947.039175030113</v>
       </c>
       <c r="F35" s="1">
-        <v>-63947.039175029808</v>
+        <v>-63947.039175030113</v>
       </c>
       <c r="G35" s="1">
         <v>39248.472782472847</v>
       </c>
       <c r="H35" s="1">
-        <v>39248.472782472847</v>
+        <v>39248.472782472993</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>22073</v>
+        <v>23573</v>
       </c>
       <c r="B36" t="s">
-        <v>22109</v>
+        <v>23609</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>200663.39336498949</v>
-      </c>
-      <c r="F36" s="1">
-        <v>200663.39336498949</v>
-      </c>
+        <v>1691.532447066628</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22072</v>
+        <v>23574</v>
       </c>
       <c r="B37" t="s">
-        <v>22108</v>
+        <v>23610</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -70500,17 +75475,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22074</v>
+        <v>23575</v>
       </c>
       <c r="B38" t="s">
-        <v>22110</v>
+        <v>23611</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1691.532447066628</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>200663.39336498949</v>
+      </c>
+      <c r="F38" s="1">
+        <v>200663.39336498949</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -70525,36 +75502,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22038</v>
+        <v>23618</v>
       </c>
       <c r="B1" t="s">
-        <v>22075</v>
+        <v>23655</v>
       </c>
       <c r="C1" t="s">
-        <v>22111</v>
+        <v>23691</v>
       </c>
       <c r="D1" t="s">
-        <v>22112</v>
+        <v>23692</v>
       </c>
       <c r="E1" t="s">
-        <v>22113</v>
+        <v>23693</v>
       </c>
       <c r="F1" t="s">
-        <v>22114</v>
+        <v>23694</v>
       </c>
       <c r="G1" t="s">
-        <v>22115</v>
+        <v>23695</v>
       </c>
       <c r="H1" t="s">
-        <v>22116</v>
+        <v>23696</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22039</v>
+        <v>23619</v>
       </c>
       <c r="B2" t="s">
-        <v>22076</v>
+        <v>23656</v>
       </c>
       <c r="C2" s="1">
         <v>-104514.67406784389</v>
@@ -70569,10 +75546,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22040</v>
+        <v>23620</v>
       </c>
       <c r="B3" t="s">
-        <v>22077</v>
+        <v>23657</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -70591,10 +75568,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22041</v>
+        <v>23621</v>
       </c>
       <c r="B4" t="s">
-        <v>22078</v>
+        <v>23658</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -70611,10 +75588,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22042</v>
+        <v>23622</v>
       </c>
       <c r="B5" t="s">
-        <v>22079</v>
+        <v>23659</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -70627,10 +75604,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22043</v>
+        <v>23623</v>
       </c>
       <c r="B6" t="s">
-        <v>22080</v>
+        <v>23660</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -70647,10 +75624,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22044</v>
+        <v>23624</v>
       </c>
       <c r="B7" t="s">
-        <v>22081</v>
+        <v>23661</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -70663,10 +75640,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22045</v>
+        <v>23625</v>
       </c>
       <c r="B8" t="s">
-        <v>22081</v>
+        <v>23661</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -70679,10 +75656,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22046</v>
+        <v>23626</v>
       </c>
       <c r="B9" t="s">
-        <v>22082</v>
+        <v>23662</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -70695,10 +75672,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22047</v>
+        <v>23627</v>
       </c>
       <c r="B10" t="s">
-        <v>22083</v>
+        <v>23663</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -70713,10 +75690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22048</v>
+        <v>23628</v>
       </c>
       <c r="B11" t="s">
-        <v>22084</v>
+        <v>23664</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -70735,10 +75712,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22049</v>
+        <v>23629</v>
       </c>
       <c r="B12" t="s">
-        <v>22085</v>
+        <v>23665</v>
       </c>
       <c r="C12" s="1">
         <v>-149.5741136579793</v>
@@ -70757,10 +75734,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22050</v>
+        <v>23630</v>
       </c>
       <c r="B13" t="s">
-        <v>22086</v>
+        <v>23666</v>
       </c>
       <c r="C13" s="1">
         <v>151856.17438438139</v>
@@ -70783,10 +75760,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22051</v>
+        <v>23631</v>
       </c>
       <c r="B14" t="s">
-        <v>22087</v>
+        <v>23667</v>
       </c>
       <c r="C14" s="1">
         <v>54754.723496312057</v>
@@ -70809,10 +75786,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22052</v>
+        <v>23632</v>
       </c>
       <c r="B15" t="s">
-        <v>22088</v>
+        <v>23668</v>
       </c>
       <c r="C15" s="1">
         <v>97101.450888069332</v>
@@ -70831,10 +75808,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22053</v>
+        <v>23633</v>
       </c>
       <c r="B16" t="s">
-        <v>22089</v>
+        <v>23669</v>
       </c>
       <c r="C16" s="1">
         <v>121151.1679762976</v>
@@ -70857,10 +75834,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22054</v>
+        <v>23634</v>
       </c>
       <c r="B17" t="s">
-        <v>22090</v>
+        <v>23670</v>
       </c>
       <c r="C17" s="1">
         <v>829.94672213900139</v>
@@ -70881,10 +75858,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22055</v>
+        <v>23635</v>
       </c>
       <c r="B18" t="s">
-        <v>22091</v>
+        <v>23671</v>
       </c>
       <c r="C18" s="1">
         <v>1851.55709250523</v>
@@ -70905,10 +75882,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22056</v>
+        <v>23636</v>
       </c>
       <c r="B19" t="s">
-        <v>22092</v>
+        <v>23672</v>
       </c>
       <c r="C19" s="1">
         <v>1851.55709250523</v>
@@ -70927,10 +75904,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22057</v>
+        <v>23637</v>
       </c>
       <c r="B20" t="s">
-        <v>22093</v>
+        <v>23673</v>
       </c>
       <c r="C20" s="1">
         <v>13110.58352570426</v>
@@ -70953,10 +75930,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22058</v>
+        <v>23638</v>
       </c>
       <c r="B21" t="s">
-        <v>22094</v>
+        <v>23674</v>
       </c>
       <c r="C21" s="1">
         <v>1.421961</v>
@@ -70975,10 +75952,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22059</v>
+        <v>23639</v>
       </c>
       <c r="B22" t="s">
-        <v>22095</v>
+        <v>23675</v>
       </c>
       <c r="C22" s="1">
         <v>2008.0292188799999</v>
@@ -70995,10 +75972,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22060</v>
+        <v>23640</v>
       </c>
       <c r="B23" t="s">
-        <v>22096</v>
+        <v>23676</v>
       </c>
       <c r="C23" s="1">
         <v>728.95224428820325</v>
@@ -71017,10 +75994,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22061</v>
+        <v>23641</v>
       </c>
       <c r="B24" t="s">
-        <v>22097</v>
+        <v>23677</v>
       </c>
       <c r="C24" s="1">
         <v>10372.18010153606</v>
@@ -71043,10 +76020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22062</v>
+        <v>23642</v>
       </c>
       <c r="B25" t="s">
-        <v>22098</v>
+        <v>23678</v>
       </c>
       <c r="C25" s="1">
         <v>117812.0378742148</v>
@@ -71069,10 +76046,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22067</v>
+        <v>23643</v>
       </c>
       <c r="B26" t="s">
-        <v>22103</v>
+        <v>23679</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -71085,10 +76062,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22068</v>
+        <v>23644</v>
       </c>
       <c r="B27" t="s">
-        <v>22104</v>
+        <v>23680</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -71107,10 +76084,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22065</v>
+        <v>23645</v>
       </c>
       <c r="B28" t="s">
-        <v>22101</v>
+        <v>23681</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -71125,10 +76102,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22066</v>
+        <v>23646</v>
       </c>
       <c r="B29" t="s">
-        <v>22102</v>
+        <v>23682</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -71147,10 +76124,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22067</v>
+        <v>23647</v>
       </c>
       <c r="B30" t="s">
-        <v>22103</v>
+        <v>23683</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -71163,10 +76140,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22068</v>
+        <v>23648</v>
       </c>
       <c r="B31" t="s">
-        <v>22104</v>
+        <v>23684</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -71185,10 +76162,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>22069</v>
+        <v>23649</v>
       </c>
       <c r="B32" t="s">
-        <v>22105</v>
+        <v>23685</v>
       </c>
       <c r="C32" s="1">
         <v>13297.36380637088</v>
@@ -71203,10 +76180,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>22070</v>
+        <v>23650</v>
       </c>
       <c r="B33" t="s">
-        <v>22027</v>
+        <v>23686</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -71227,10 +76204,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22071</v>
+        <v>23651</v>
       </c>
       <c r="B34" t="s">
-        <v>22107</v>
+        <v>23687</v>
       </c>
       <c r="C34" s="1">
         <v>10171.468589380889</v>
@@ -71245,7 +76222,7 @@
         <v>-79545.106801385089</v>
       </c>
       <c r="G34" s="1">
-        <v>66058.729479423899</v>
+        <v>66059.10105946564</v>
       </c>
       <c r="H34" s="1">
         <v>66058.729479423899</v>
@@ -71253,10 +76230,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>22071</v>
+        <v>23651</v>
       </c>
       <c r="B35" t="s">
-        <v>22107</v>
+        <v>23687</v>
       </c>
       <c r="C35" s="1">
         <v>10171.459058987501</v>
@@ -71271,7 +76248,7 @@
         <v>-79545.106801385089</v>
       </c>
       <c r="G35" s="1">
-        <v>66059.10105946564</v>
+        <v>66058.729479423899</v>
       </c>
       <c r="H35" s="1">
         <v>66059.10105946564</v>
@@ -71279,28 +76256,26 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>22073</v>
+        <v>23652</v>
       </c>
       <c r="B36" t="s">
-        <v>22109</v>
+        <v>23688</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>242248.42014405999</v>
-      </c>
-      <c r="F36" s="1">
-        <v>242248.42014405999</v>
-      </c>
+        <v>1625.492093275358</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22072</v>
+        <v>23653</v>
       </c>
       <c r="B37" t="s">
-        <v>22108</v>
+        <v>23689</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -71317,17 +76292,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22074</v>
+        <v>23654</v>
       </c>
       <c r="B38" t="s">
-        <v>22110</v>
+        <v>23690</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1625.492093275358</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>242248.42014405999</v>
+      </c>
+      <c r="F38" s="1">
+        <v>242248.42014405999</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -71342,36 +76319,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>22038</v>
+        <v>23697</v>
       </c>
       <c r="B1" t="s">
-        <v>22075</v>
+        <v>23734</v>
       </c>
       <c r="C1" t="s">
-        <v>22111</v>
+        <v>23770</v>
       </c>
       <c r="D1" t="s">
-        <v>22112</v>
+        <v>23771</v>
       </c>
       <c r="E1" t="s">
-        <v>22113</v>
+        <v>23772</v>
       </c>
       <c r="F1" t="s">
-        <v>22114</v>
+        <v>23773</v>
       </c>
       <c r="G1" t="s">
-        <v>22115</v>
+        <v>23774</v>
       </c>
       <c r="H1" t="s">
-        <v>22116</v>
+        <v>23775</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>22039</v>
+        <v>23698</v>
       </c>
       <c r="B2" t="s">
-        <v>22076</v>
+        <v>23735</v>
       </c>
       <c r="C2" s="1">
         <v>-200371.3593658637</v>
@@ -71386,10 +76363,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>22040</v>
+        <v>23699</v>
       </c>
       <c r="B3" t="s">
-        <v>22077</v>
+        <v>23736</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -71408,10 +76385,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22041</v>
+        <v>23700</v>
       </c>
       <c r="B4" t="s">
-        <v>22078</v>
+        <v>23737</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -71428,10 +76405,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22042</v>
+        <v>23701</v>
       </c>
       <c r="B5" t="s">
-        <v>22079</v>
+        <v>23738</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -71444,10 +76421,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>22043</v>
+        <v>23702</v>
       </c>
       <c r="B6" t="s">
-        <v>22080</v>
+        <v>23739</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -71464,10 +76441,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>22044</v>
+        <v>23703</v>
       </c>
       <c r="B7" t="s">
-        <v>22081</v>
+        <v>23740</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -71480,10 +76457,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22045</v>
+        <v>23704</v>
       </c>
       <c r="B8" t="s">
-        <v>22081</v>
+        <v>23740</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -71496,10 +76473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>22046</v>
+        <v>23705</v>
       </c>
       <c r="B9" t="s">
-        <v>22082</v>
+        <v>23741</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -71512,10 +76489,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>22047</v>
+        <v>23706</v>
       </c>
       <c r="B10" t="s">
-        <v>22083</v>
+        <v>23742</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -71530,10 +76507,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>22048</v>
+        <v>23707</v>
       </c>
       <c r="B11" t="s">
-        <v>22084</v>
+        <v>23743</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -71552,10 +76529,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22049</v>
+        <v>23708</v>
       </c>
       <c r="B12" t="s">
-        <v>22085</v>
+        <v>23744</v>
       </c>
       <c r="C12" s="1">
         <v>-155.06439238415939</v>
@@ -71574,10 +76551,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22050</v>
+        <v>23709</v>
       </c>
       <c r="B13" t="s">
-        <v>22086</v>
+        <v>23745</v>
       </c>
       <c r="C13" s="1">
         <v>314231.27904663578</v>
@@ -71600,10 +76577,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22051</v>
+        <v>23710</v>
       </c>
       <c r="B14" t="s">
-        <v>22087</v>
+        <v>23746</v>
       </c>
       <c r="C14" s="1">
         <v>51456.424245716291</v>
@@ -71626,10 +76603,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>22052</v>
+        <v>23711</v>
       </c>
       <c r="B15" t="s">
-        <v>22088</v>
+        <v>23747</v>
       </c>
       <c r="C15" s="1">
         <v>262774.85480091948</v>
@@ -71648,10 +76625,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22053</v>
+        <v>23712</v>
       </c>
       <c r="B16" t="s">
-        <v>22089</v>
+        <v>23748</v>
       </c>
       <c r="C16" s="1">
         <v>265585.17502668808</v>
@@ -71674,10 +76651,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22054</v>
+        <v>23713</v>
       </c>
       <c r="B17" t="s">
-        <v>22090</v>
+        <v>23749</v>
       </c>
       <c r="C17" s="1">
         <v>1300.758691809164</v>
@@ -71698,10 +76675,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22055</v>
+        <v>23714</v>
       </c>
       <c r="B18" t="s">
-        <v>22091</v>
+        <v>23750</v>
       </c>
       <c r="C18" s="1">
         <v>2035.2769079008131</v>
@@ -71722,10 +76699,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22056</v>
+        <v>23715</v>
       </c>
       <c r="B19" t="s">
-        <v>22092</v>
+        <v>23751</v>
       </c>
       <c r="C19" s="1">
         <v>2035.2769079008131</v>
@@ -71744,10 +76721,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22057</v>
+        <v>23716</v>
       </c>
       <c r="B20" t="s">
-        <v>22093</v>
+        <v>23752</v>
       </c>
       <c r="C20" s="1">
         <v>13142.94333128056</v>
@@ -71770,10 +76747,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22058</v>
+        <v>23717</v>
       </c>
       <c r="B21" t="s">
-        <v>22094</v>
+        <v>23753</v>
       </c>
       <c r="C21" s="1">
         <v>1.218183</v>
@@ -71792,10 +76769,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>22059</v>
+        <v>23718</v>
       </c>
       <c r="B22" t="s">
-        <v>22095</v>
+        <v>23754</v>
       </c>
       <c r="C22" s="1">
         <v>1687.2726680000001</v>
@@ -71812,10 +76789,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>22060</v>
+        <v>23719</v>
       </c>
       <c r="B23" t="s">
-        <v>22096</v>
+        <v>23755</v>
       </c>
       <c r="C23" s="1">
         <v>2336.210388476667</v>
@@ -71834,10 +76811,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>22061</v>
+        <v>23720</v>
       </c>
       <c r="B24" t="s">
-        <v>22097</v>
+        <v>23756</v>
       </c>
       <c r="C24" s="1">
         <v>9118.2420918038915</v>
@@ -71860,10 +76837,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>22062</v>
+        <v>23721</v>
       </c>
       <c r="B25" t="s">
-        <v>22098</v>
+        <v>23757</v>
       </c>
       <c r="C25" s="1">
         <v>262376.75111480377</v>
@@ -71886,10 +76863,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>22067</v>
+        <v>23722</v>
       </c>
       <c r="B26" t="s">
-        <v>22103</v>
+        <v>23758</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -71902,15 +76879,15 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>22068</v>
+        <v>23723</v>
       </c>
       <c r="B27" t="s">
-        <v>22104</v>
+        <v>23759</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-25100.989231280721</v>
+        <v>-25100.98923128075</v>
       </c>
       <c r="F27" s="1">
         <v>-25100.989231280721</v>
@@ -71924,10 +76901,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>22065</v>
+        <v>23724</v>
       </c>
       <c r="B28" t="s">
-        <v>22101</v>
+        <v>23760</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -71942,10 +76919,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>22066</v>
+        <v>23725</v>
       </c>
       <c r="B29" t="s">
-        <v>22102</v>
+        <v>23761</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -71964,10 +76941,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>22067</v>
+        <v>23726</v>
       </c>
       <c r="B30" t="s">
-        <v>22103</v>
+        <v>23762</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -71980,15 +76957,15 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>22068</v>
+        <v>23727</v>
       </c>
       <c r="B31" t="s">
-        <v>22104</v>
+        <v>23763</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-25100.98923128075</v>
+        <v>-25100.989231280721</v>
       </c>
       <c r="F31" s="1">
         <v>-25100.98923128075</v>
@@ -72002,10 +76979,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>22069</v>
+        <v>23728</v>
       </c>
       <c r="B32" t="s">
-        <v>22105</v>
+        <v>23764</v>
       </c>
       <c r="C32" s="1">
         <v>62005.391748940048</v>
@@ -72020,10 +76997,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>22070</v>
+        <v>23729</v>
       </c>
       <c r="B33" t="s">
-        <v>22106</v>
+        <v>23765</v>
       </c>
       <c r="C33" s="1">
         <v>86.331224277060215</v>
@@ -72046,10 +77023,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>22071</v>
+        <v>23730</v>
       </c>
       <c r="B34" t="s">
-        <v>22107</v>
+        <v>23766</v>
       </c>
       <c r="C34" s="1">
         <v>63134.524836636163</v>
@@ -72064,18 +77041,18 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G34" s="1">
+        <v>50492.474199901873</v>
+      </c>
+      <c r="H34" s="1">
         <v>50492.474199902237</v>
-      </c>
-      <c r="H34" s="1">
-        <v>50492.474199901873</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>22071</v>
+        <v>23730</v>
       </c>
       <c r="B35" t="s">
-        <v>22107</v>
+        <v>23766</v>
       </c>
       <c r="C35" s="1">
         <v>63134.515306242713</v>
@@ -72090,18 +77067,18 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G35" s="1">
+        <v>50492.474199902237</v>
+      </c>
+      <c r="H35" s="1">
         <v>50492.474199901873</v>
-      </c>
-      <c r="H35" s="1">
-        <v>50492.474199902237</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>22073</v>
+        <v>23731</v>
       </c>
       <c r="B36" t="s">
-        <v>22109</v>
+        <v>23767</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -72116,10 +77093,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>22072</v>
+        <v>23732</v>
       </c>
       <c r="B37" t="s">
-        <v>22108</v>
+        <v>23768</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -72136,10 +77113,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>22074</v>
+        <v>23733</v>
       </c>
       <c r="B38" t="s">
-        <v>22110</v>
+        <v>23769</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>

--- a/input_data/sna_country_data/URY/cei.xlsx
+++ b/input_data/sna_country_data/URY/cei.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41328" uniqueCount="23776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41902" uniqueCount="24329">
   <si>
     <t>code</t>
   </si>
@@ -71329,6 +71329,1665 @@
   </si>
   <si>
     <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t>Transferencias de capital</t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>row_r</t>
+  </si>
+  <si>
+    <t>row_u</t>
+  </si>
+  <si>
+    <t>gg_r</t>
+  </si>
+  <si>
+    <t>gg_u</t>
+  </si>
+  <si>
+    <t>households_r</t>
+  </si>
+  <si>
+    <t>households_u</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>B.11</t>
+  </si>
+  <si>
+    <t>B.1b</t>
+  </si>
+  <si>
+    <t>D.2</t>
+  </si>
+  <si>
+    <t>D.21</t>
+  </si>
+  <si>
+    <t>D.29</t>
+  </si>
+  <si>
+    <t>(-) D.3</t>
+  </si>
+  <si>
+    <t>(-) D.31</t>
+  </si>
+  <si>
+    <t>(-) D.39</t>
+  </si>
+  <si>
+    <t>B.3b</t>
+  </si>
+  <si>
+    <t>B.2b</t>
+  </si>
+  <si>
+    <t>D.1</t>
+  </si>
+  <si>
+    <t>D.4</t>
+  </si>
+  <si>
+    <t>D.41</t>
+  </si>
+  <si>
+    <t>D.49</t>
+  </si>
+  <si>
+    <t>B.5b</t>
+  </si>
+  <si>
+    <t>D.5</t>
+  </si>
+  <si>
+    <t>D.6</t>
+  </si>
+  <si>
+    <t>D.62</t>
+  </si>
+  <si>
+    <t>D.7</t>
+  </si>
+  <si>
+    <t>D.71</t>
+  </si>
+  <si>
+    <t>D.72</t>
+  </si>
+  <si>
+    <t>D.74</t>
+  </si>
+  <si>
+    <t>D.75</t>
+  </si>
+  <si>
+    <t>B.6b</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>D.63</t>
+  </si>
+  <si>
+    <t>B.07b00</t>
+  </si>
+  <si>
+    <t>D.8</t>
+  </si>
+  <si>
+    <t>B.8B</t>
+  </si>
+  <si>
+    <t>B.12</t>
+  </si>
+  <si>
+    <t>D.9</t>
+  </si>
+  <si>
+    <t>B.9</t>
+  </si>
+  <si>
+    <t>D.76</t>
+  </si>
+  <si>
+    <t>D.61</t>
+  </si>
+  <si>
+    <t>D.73</t>
+  </si>
+  <si>
+    <t>code_long</t>
+  </si>
+  <si>
+    <t>Saldo de bienes y servicios con el exterior</t>
+  </si>
+  <si>
+    <t>Valor agregado bruto / Producto interno bruto</t>
+  </si>
+  <si>
+    <t>Impuestos sobre la producción y las importaciones</t>
+  </si>
+  <si>
+    <t>Impuestos sobre los productos</t>
+  </si>
+  <si>
+    <t>Otros impuestos sobre la producción</t>
+  </si>
+  <si>
+    <t>Subvenciones sobre los productos</t>
+  </si>
+  <si>
+    <t>Otras subvenciones a la producción</t>
+  </si>
+  <si>
+    <t>Ingreso mixto bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excedente de explotación bruto </t>
+  </si>
+  <si>
+    <t>Remuneración de los asalariados</t>
+  </si>
+  <si>
+    <t>Renta de la propiedad</t>
+  </si>
+  <si>
+    <t>Intereses SCN</t>
+  </si>
+  <si>
+    <t>Otras rentas</t>
+  </si>
+  <si>
+    <t>Saldo de ingresos primarios, bruto / ingreso nacional bruto</t>
+  </si>
+  <si>
+    <t>Impuestos corrientes sobre el ingreso, la riqueza, etc.</t>
+  </si>
+  <si>
+    <t>Contribuciones y prestaciones sociales, excepto TSE</t>
+  </si>
+  <si>
+    <t>Prestaciones sociales distintas de las transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Otras transferencias corrientes</t>
+  </si>
+  <si>
+    <t>Primas netas de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Indemnizaciones de seguros no de vida</t>
+  </si>
+  <si>
+    <t>Cooperación internacional corriente</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes diversas</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Transferencias sociales en especie</t>
+  </si>
+  <si>
+    <t>Ingreso disponible bruto ajustado</t>
+  </si>
+  <si>
+    <t>Ajuste por la variación de los derechos de pensión</t>
+  </si>
+  <si>
+    <t>Ahorro bruto</t>
+  </si>
+  <si>
+    <t>Saldo externo corriente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transferencias de capital </t>
+  </si>
+  <si>
+    <t>Préstamo neto (+) / Endeudamiento neto (-)</t>
+  </si>
+  <si>
+    <t>Transferencia del BCU al Gobierno</t>
+  </si>
+  <si>
+    <t>Contribuciones sociales netas</t>
+  </si>
+  <si>
+    <t>Transferencias corrientes dentro del gobierno general</t>
   </si>
   <si>
     <t>row_r</t>
@@ -71397,36 +73056,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23223</v>
+        <v>23776</v>
       </c>
       <c r="B1" t="s">
-        <v>23260</v>
+        <v>23813</v>
       </c>
       <c r="C1" t="s">
-        <v>23296</v>
+        <v>23849</v>
       </c>
       <c r="D1" t="s">
-        <v>23297</v>
+        <v>23850</v>
       </c>
       <c r="E1" t="s">
-        <v>23298</v>
+        <v>23851</v>
       </c>
       <c r="F1" t="s">
-        <v>23299</v>
+        <v>23852</v>
       </c>
       <c r="G1" t="s">
-        <v>23300</v>
+        <v>23853</v>
       </c>
       <c r="H1" t="s">
-        <v>23301</v>
+        <v>23854</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23224</v>
+        <v>23777</v>
       </c>
       <c r="B2" t="s">
-        <v>23261</v>
+        <v>23814</v>
       </c>
       <c r="C2" s="1">
         <v>-35345.263380289784</v>
@@ -71441,10 +73100,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23225</v>
+        <v>23778</v>
       </c>
       <c r="B3" t="s">
-        <v>23262</v>
+        <v>23815</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -71463,10 +73122,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23226</v>
+        <v>23779</v>
       </c>
       <c r="B4" t="s">
-        <v>23263</v>
+        <v>23816</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -71483,10 +73142,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23227</v>
+        <v>23780</v>
       </c>
       <c r="B5" t="s">
-        <v>23264</v>
+        <v>23817</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -71503,10 +73162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23228</v>
+        <v>23781</v>
       </c>
       <c r="B6" t="s">
-        <v>23265</v>
+        <v>23818</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -71519,10 +73178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23229</v>
+        <v>23782</v>
       </c>
       <c r="B7" t="s">
-        <v>23266</v>
+        <v>23819</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -71539,10 +73198,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23230</v>
+        <v>23783</v>
       </c>
       <c r="B8" t="s">
-        <v>23267</v>
+        <v>23820</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -71557,10 +73216,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23231</v>
+        <v>23784</v>
       </c>
       <c r="B9" t="s">
-        <v>23267</v>
+        <v>23820</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -71573,10 +73232,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23232</v>
+        <v>23785</v>
       </c>
       <c r="B10" t="s">
-        <v>23268</v>
+        <v>23821</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -71591,10 +73250,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23233</v>
+        <v>23786</v>
       </c>
       <c r="B11" t="s">
-        <v>23269</v>
+        <v>23822</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -71609,10 +73268,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23234</v>
+        <v>23787</v>
       </c>
       <c r="B12" t="s">
-        <v>23270</v>
+        <v>23823</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -71631,10 +73290,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23235</v>
+        <v>23788</v>
       </c>
       <c r="B13" t="s">
-        <v>23271</v>
+        <v>23824</v>
       </c>
       <c r="C13" s="1">
         <v>105254.84066842961</v>
@@ -71657,10 +73316,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23236</v>
+        <v>23789</v>
       </c>
       <c r="B14" t="s">
-        <v>23272</v>
+        <v>23825</v>
       </c>
       <c r="C14" s="1">
         <v>20118.629433262511</v>
@@ -71683,10 +73342,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23237</v>
+        <v>23790</v>
       </c>
       <c r="B15" t="s">
-        <v>23273</v>
+        <v>23826</v>
       </c>
       <c r="C15" s="1">
         <v>85136.211235167109</v>
@@ -71709,10 +73368,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23238</v>
+        <v>23791</v>
       </c>
       <c r="B16" t="s">
-        <v>23274</v>
+        <v>23827</v>
       </c>
       <c r="C16" s="1">
         <v>77979.086634604173</v>
@@ -71735,10 +73394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23239</v>
+        <v>23792</v>
       </c>
       <c r="B17" t="s">
-        <v>23275</v>
+        <v>23828</v>
       </c>
       <c r="C17" s="1">
         <v>708.07373372999996</v>
@@ -71759,10 +73418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23240</v>
+        <v>23793</v>
       </c>
       <c r="B18" t="s">
-        <v>23276</v>
+        <v>23829</v>
       </c>
       <c r="C18" s="1">
         <v>708.07373372999996</v>
@@ -71779,10 +73438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23241</v>
+        <v>23794</v>
       </c>
       <c r="B19" t="s">
-        <v>23277</v>
+        <v>23830</v>
       </c>
       <c r="C19" s="1">
         <v>2128.9819248528388</v>
@@ -71805,10 +73464,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23242</v>
+        <v>23795</v>
       </c>
       <c r="B20" t="s">
-        <v>23278</v>
+        <v>23831</v>
       </c>
       <c r="C20" s="1">
         <v>610.943299077402</v>
@@ -71825,10 +73484,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23243</v>
+        <v>23796</v>
       </c>
       <c r="B21" t="s">
-        <v>23279</v>
+        <v>23832</v>
       </c>
       <c r="C21" s="1">
         <v>476.41603700000002</v>
@@ -71847,10 +73506,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23244</v>
+        <v>23797</v>
       </c>
       <c r="B22" t="s">
-        <v>23280</v>
+        <v>23833</v>
       </c>
       <c r="C22" s="1">
         <v>1041.622588775437</v>
@@ -71873,10 +73532,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23245</v>
+        <v>23798</v>
       </c>
       <c r="B23" t="s">
-        <v>23281</v>
+        <v>23834</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -71893,10 +73552,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23246</v>
+        <v>23799</v>
       </c>
       <c r="B24" t="s">
-        <v>23282</v>
+        <v>23835</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -71913,10 +73572,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23247</v>
+        <v>23800</v>
       </c>
       <c r="B25" t="s">
-        <v>23283</v>
+        <v>23836</v>
       </c>
       <c r="C25" s="1">
         <v>75685.254770642801</v>
@@ -71939,10 +73598,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23248</v>
+        <v>23801</v>
       </c>
       <c r="B26" t="s">
-        <v>23284</v>
+        <v>23837</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -71957,10 +73616,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23249</v>
+        <v>23802</v>
       </c>
       <c r="B27" t="s">
-        <v>23285</v>
+        <v>23838</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -71968,7 +73627,7 @@
         <v>-3264.8749993161591</v>
       </c>
       <c r="F27" s="1">
-        <v>-3264.8749993161591</v>
+        <v>-3264.8749993161441</v>
       </c>
       <c r="G27" s="1">
         <v>65128.014697722727</v>
@@ -71979,10 +73638,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23250</v>
+        <v>23803</v>
       </c>
       <c r="B28" t="s">
-        <v>23286</v>
+        <v>23839</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -71997,10 +73656,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23251</v>
+        <v>23804</v>
       </c>
       <c r="B29" t="s">
-        <v>23287</v>
+        <v>23840</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -72019,10 +73678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23252</v>
+        <v>23805</v>
       </c>
       <c r="B30" t="s">
-        <v>23288</v>
+        <v>23841</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -72037,10 +73696,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23253</v>
+        <v>23806</v>
       </c>
       <c r="B31" t="s">
-        <v>23289</v>
+        <v>23842</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -72048,7 +73707,7 @@
         <v>-3264.8749993161441</v>
       </c>
       <c r="F31" s="1">
-        <v>-3264.8749993161441</v>
+        <v>-3264.8749993161591</v>
       </c>
       <c r="G31" s="1">
         <v>65128.014697722727</v>
@@ -72059,10 +73718,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23254</v>
+        <v>23807</v>
       </c>
       <c r="B32" t="s">
-        <v>23290</v>
+        <v>23843</v>
       </c>
       <c r="C32" s="1">
         <v>40339.991390353032</v>
@@ -72077,10 +73736,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23255</v>
+        <v>23808</v>
       </c>
       <c r="B33" t="s">
-        <v>23291</v>
+        <v>23844</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -72101,10 +73760,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23256</v>
+        <v>23809</v>
       </c>
       <c r="B34" t="s">
-        <v>23292</v>
+        <v>23845</v>
       </c>
       <c r="C34" s="1">
         <v>37886.776197581872</v>
@@ -72127,10 +73786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23256</v>
+        <v>23809</v>
       </c>
       <c r="B35" t="s">
-        <v>23292</v>
+        <v>23845</v>
       </c>
       <c r="C35" s="1">
         <v>37886.776197581872</v>
@@ -72153,53 +73812,53 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23257</v>
+        <v>23810</v>
       </c>
       <c r="B36" t="s">
-        <v>23293</v>
+        <v>23846</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>926.5806651800001</v>
+        <v>113976.0975413</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="H36" s="1">
+        <v>137582.86030768359</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23258</v>
+        <v>23811</v>
       </c>
       <c r="B37" t="s">
-        <v>23294</v>
+        <v>23847</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>113976.0975413</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>79482.446760280014</v>
+      </c>
+      <c r="F37" s="1">
+        <v>79482.446760280014</v>
+      </c>
       <c r="G37" s="1"/>
-      <c r="H37" s="1">
-        <v>137582.86030768359</v>
-      </c>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23259</v>
+        <v>23812</v>
       </c>
       <c r="B38" t="s">
-        <v>23295</v>
+        <v>23848</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>79482.446760280014</v>
-      </c>
-      <c r="F38" s="1">
-        <v>79482.446760280014</v>
-      </c>
+        <v>926.5806651800001</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -72214,36 +73873,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23302</v>
+        <v>23855</v>
       </c>
       <c r="B1" t="s">
-        <v>23339</v>
+        <v>23892</v>
       </c>
       <c r="C1" t="s">
-        <v>23375</v>
+        <v>23928</v>
       </c>
       <c r="D1" t="s">
-        <v>23376</v>
+        <v>23929</v>
       </c>
       <c r="E1" t="s">
-        <v>23377</v>
+        <v>23930</v>
       </c>
       <c r="F1" t="s">
-        <v>23378</v>
+        <v>23931</v>
       </c>
       <c r="G1" t="s">
-        <v>23379</v>
+        <v>23932</v>
       </c>
       <c r="H1" t="s">
-        <v>23380</v>
+        <v>23933</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23303</v>
+        <v>23856</v>
       </c>
       <c r="B2" t="s">
-        <v>23340</v>
+        <v>23893</v>
       </c>
       <c r="C2" s="1">
         <v>-92111.334701685584</v>
@@ -72258,10 +73917,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23304</v>
+        <v>23857</v>
       </c>
       <c r="B3" t="s">
-        <v>23341</v>
+        <v>23894</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -72280,10 +73939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23305</v>
+        <v>23858</v>
       </c>
       <c r="B4" t="s">
-        <v>23342</v>
+        <v>23895</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -72300,10 +73959,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23306</v>
+        <v>23859</v>
       </c>
       <c r="B5" t="s">
-        <v>23343</v>
+        <v>23896</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -72320,10 +73979,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23307</v>
+        <v>23860</v>
       </c>
       <c r="B6" t="s">
-        <v>23344</v>
+        <v>23897</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -72336,10 +73995,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23308</v>
+        <v>23861</v>
       </c>
       <c r="B7" t="s">
-        <v>23345</v>
+        <v>23898</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -72356,10 +74015,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23309</v>
+        <v>23862</v>
       </c>
       <c r="B8" t="s">
-        <v>23346</v>
+        <v>23899</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -72372,10 +74031,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23310</v>
+        <v>23863</v>
       </c>
       <c r="B9" t="s">
-        <v>23346</v>
+        <v>23899</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -72388,10 +74047,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23311</v>
+        <v>23864</v>
       </c>
       <c r="B10" t="s">
-        <v>23347</v>
+        <v>23900</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -72404,10 +74063,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23312</v>
+        <v>23865</v>
       </c>
       <c r="B11" t="s">
-        <v>23348</v>
+        <v>23901</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -72422,10 +74081,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23313</v>
+        <v>23866</v>
       </c>
       <c r="B12" t="s">
-        <v>23349</v>
+        <v>23902</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -72444,10 +74103,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23314</v>
+        <v>23867</v>
       </c>
       <c r="B13" t="s">
-        <v>23350</v>
+        <v>23903</v>
       </c>
       <c r="C13" s="1">
         <v>111912.2883479437</v>
@@ -72470,10 +74129,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23315</v>
+        <v>23868</v>
       </c>
       <c r="B14" t="s">
-        <v>23351</v>
+        <v>23904</v>
       </c>
       <c r="C14" s="1">
         <v>37196.900831416431</v>
@@ -72496,10 +74155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23316</v>
+        <v>23869</v>
       </c>
       <c r="B15" t="s">
-        <v>23352</v>
+        <v>23905</v>
       </c>
       <c r="C15" s="1">
         <v>74715.387516527291</v>
@@ -72522,10 +74181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23317</v>
+        <v>23870</v>
       </c>
       <c r="B16" t="s">
-        <v>23353</v>
+        <v>23906</v>
       </c>
       <c r="C16" s="1">
         <v>81203.449470399617</v>
@@ -72548,10 +74207,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23318</v>
+        <v>23871</v>
       </c>
       <c r="B17" t="s">
-        <v>23354</v>
+        <v>23907</v>
       </c>
       <c r="C17" s="1">
         <v>1114.5240200000001</v>
@@ -72572,10 +74231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23319</v>
+        <v>23872</v>
       </c>
       <c r="B18" t="s">
-        <v>23355</v>
+        <v>23908</v>
       </c>
       <c r="C18" s="1">
         <v>1114.5240200000001</v>
@@ -72594,10 +74253,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23320</v>
+        <v>23873</v>
       </c>
       <c r="B19" t="s">
-        <v>23356</v>
+        <v>23909</v>
       </c>
       <c r="C19" s="1">
         <v>17219.038211090661</v>
@@ -72620,10 +74279,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23321</v>
+        <v>23874</v>
       </c>
       <c r="B20" t="s">
-        <v>23357</v>
+        <v>23910</v>
       </c>
       <c r="C20" s="1">
         <v>98.619980999999996</v>
@@ -72642,10 +74301,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23322</v>
+        <v>23875</v>
       </c>
       <c r="B21" t="s">
-        <v>23358</v>
+        <v>23911</v>
       </c>
       <c r="C21" s="1">
         <v>1657.9772827899999</v>
@@ -72662,10 +74321,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23323</v>
+        <v>23876</v>
       </c>
       <c r="B22" t="s">
-        <v>23359</v>
+        <v>23912</v>
       </c>
       <c r="C22" s="1">
         <v>1009.104553</v>
@@ -72684,10 +74343,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23324</v>
+        <v>23877</v>
       </c>
       <c r="B23" t="s">
-        <v>23360</v>
+        <v>23913</v>
       </c>
       <c r="C23" s="1">
         <v>14453.336394300661</v>
@@ -72710,10 +74369,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23325</v>
+        <v>23878</v>
       </c>
       <c r="B24" t="s">
-        <v>23361</v>
+        <v>23914</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -72732,10 +74391,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23326</v>
+        <v>23879</v>
       </c>
       <c r="B25" t="s">
-        <v>23362</v>
+        <v>23915</v>
       </c>
       <c r="C25" s="1">
         <v>79087.001794051394</v>
@@ -72758,10 +74417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23327</v>
+        <v>23880</v>
       </c>
       <c r="B26" t="s">
-        <v>23363</v>
+        <v>23916</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -72776,10 +74435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23328</v>
+        <v>23881</v>
       </c>
       <c r="B27" t="s">
-        <v>23364</v>
+        <v>23917</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -72787,7 +74446,7 @@
         <v>-10570.434075028639</v>
       </c>
       <c r="F27" s="1">
-        <v>-10570.434075028639</v>
+        <v>-10570.43407502865</v>
       </c>
       <c r="G27" s="1">
         <v>124508.5573505638</v>
@@ -72798,10 +74457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23329</v>
+        <v>23882</v>
       </c>
       <c r="B28" t="s">
-        <v>23365</v>
+        <v>23918</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -72816,10 +74475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23330</v>
+        <v>23883</v>
       </c>
       <c r="B29" t="s">
-        <v>23366</v>
+        <v>23919</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -72838,10 +74497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23331</v>
+        <v>23884</v>
       </c>
       <c r="B30" t="s">
-        <v>23367</v>
+        <v>23920</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -72856,10 +74515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23332</v>
+        <v>23885</v>
       </c>
       <c r="B31" t="s">
-        <v>23368</v>
+        <v>23921</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -72867,7 +74526,7 @@
         <v>-10570.43407502865</v>
       </c>
       <c r="F31" s="1">
-        <v>-10570.43407502865</v>
+        <v>-10570.434075028639</v>
       </c>
       <c r="G31" s="1">
         <v>124508.5573505638</v>
@@ -72878,10 +74537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23333</v>
+        <v>23886</v>
       </c>
       <c r="B32" t="s">
-        <v>23369</v>
+        <v>23922</v>
       </c>
       <c r="C32" s="1">
         <v>-13024.332907634191</v>
@@ -72896,10 +74555,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23334</v>
+        <v>23887</v>
       </c>
       <c r="B33" t="s">
-        <v>23370</v>
+        <v>23923</v>
       </c>
       <c r="C33" s="1">
         <v>181.0641172</v>
@@ -72922,10 +74581,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23335</v>
+        <v>23888</v>
       </c>
       <c r="B34" t="s">
-        <v>23371</v>
+        <v>23924</v>
       </c>
       <c r="C34" s="1">
         <v>-14574.43484844782</v>
@@ -72937,21 +74596,21 @@
         <v>-66950.582658753847</v>
       </c>
       <c r="F34" s="1">
-        <v>-66950.582658753861</v>
+        <v>-66950.582658753847</v>
       </c>
       <c r="G34" s="1">
         <v>55330.055140544151</v>
       </c>
       <c r="H34" s="1">
-        <v>55330.055140544151</v>
+        <v>55330.055140544697</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23335</v>
+        <v>23888</v>
       </c>
       <c r="B35" t="s">
-        <v>23371</v>
+        <v>23924</v>
       </c>
       <c r="C35" s="1">
         <v>-14574.434848447811</v>
@@ -72963,59 +74622,59 @@
         <v>-66950.582658753861</v>
       </c>
       <c r="F35" s="1">
-        <v>-66950.582658753847</v>
+        <v>-66950.582658753861</v>
       </c>
       <c r="G35" s="1">
         <v>55330.055140544697</v>
       </c>
       <c r="H35" s="1">
-        <v>55330.055140544697</v>
+        <v>55330.055140544151</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23336</v>
+        <v>23889</v>
       </c>
       <c r="B36" t="s">
-        <v>23372</v>
+        <v>23925</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>147042.35994689999</v>
-      </c>
-      <c r="F36" s="1">
-        <v>147042.21094677999</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+        <v>181558.9914336357</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
+        <v>310.92989817709997</v>
+      </c>
+      <c r="H36" s="1">
+        <v>223683.25268700649</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23337</v>
+        <v>23890</v>
       </c>
       <c r="B37" t="s">
-        <v>23373</v>
+        <v>23926</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>181558.9914336357</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1">
-        <v>310.92989817709997</v>
-      </c>
-      <c r="H37" s="1">
-        <v>223683.25268700649</v>
-      </c>
+        <v>147042.35994689999</v>
+      </c>
+      <c r="F37" s="1">
+        <v>147042.21094677999</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23338</v>
+        <v>23891</v>
       </c>
       <c r="B38" t="s">
-        <v>23374</v>
+        <v>23927</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -73037,36 +74696,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23381</v>
+        <v>23934</v>
       </c>
       <c r="B1" t="s">
-        <v>23418</v>
+        <v>23971</v>
       </c>
       <c r="C1" t="s">
-        <v>23454</v>
+        <v>24007</v>
       </c>
       <c r="D1" t="s">
-        <v>23455</v>
+        <v>24008</v>
       </c>
       <c r="E1" t="s">
-        <v>23456</v>
+        <v>24009</v>
       </c>
       <c r="F1" t="s">
-        <v>23457</v>
+        <v>24010</v>
       </c>
       <c r="G1" t="s">
-        <v>23458</v>
+        <v>24011</v>
       </c>
       <c r="H1" t="s">
-        <v>23459</v>
+        <v>24012</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23382</v>
+        <v>23935</v>
       </c>
       <c r="B2" t="s">
-        <v>23419</v>
+        <v>23972</v>
       </c>
       <c r="C2" s="1">
         <v>-102236.23721409201</v>
@@ -73081,10 +74740,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23383</v>
+        <v>23936</v>
       </c>
       <c r="B3" t="s">
-        <v>23420</v>
+        <v>23973</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -73103,10 +74762,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23384</v>
+        <v>23937</v>
       </c>
       <c r="B4" t="s">
-        <v>23421</v>
+        <v>23974</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -73123,10 +74782,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23385</v>
+        <v>23938</v>
       </c>
       <c r="B5" t="s">
-        <v>23422</v>
+        <v>23975</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -73139,10 +74798,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23386</v>
+        <v>23939</v>
       </c>
       <c r="B6" t="s">
-        <v>23423</v>
+        <v>23976</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -73159,10 +74818,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23387</v>
+        <v>23940</v>
       </c>
       <c r="B7" t="s">
-        <v>23424</v>
+        <v>23977</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -73175,10 +74834,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23388</v>
+        <v>23941</v>
       </c>
       <c r="B8" t="s">
-        <v>23424</v>
+        <v>23977</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -73191,10 +74850,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23389</v>
+        <v>23942</v>
       </c>
       <c r="B9" t="s">
-        <v>23425</v>
+        <v>23978</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -73207,10 +74866,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23390</v>
+        <v>23943</v>
       </c>
       <c r="B10" t="s">
-        <v>23426</v>
+        <v>23979</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -73225,10 +74884,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23391</v>
+        <v>23944</v>
       </c>
       <c r="B11" t="s">
-        <v>23427</v>
+        <v>23980</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -73247,10 +74906,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23392</v>
+        <v>23945</v>
       </c>
       <c r="B12" t="s">
-        <v>23428</v>
+        <v>23981</v>
       </c>
       <c r="C12" s="1">
         <v>-83.070126027215935</v>
@@ -73269,10 +74928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23393</v>
+        <v>23946</v>
       </c>
       <c r="B13" t="s">
-        <v>23429</v>
+        <v>23982</v>
       </c>
       <c r="C13" s="1">
         <v>144279.01796396461</v>
@@ -73295,10 +74954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23394</v>
+        <v>23947</v>
       </c>
       <c r="B14" t="s">
-        <v>23430</v>
+        <v>23983</v>
       </c>
       <c r="C14" s="1">
         <v>32414.538114762661</v>
@@ -73321,10 +74980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23395</v>
+        <v>23948</v>
       </c>
       <c r="B15" t="s">
-        <v>23431</v>
+        <v>23984</v>
       </c>
       <c r="C15" s="1">
         <v>111864.47984920201</v>
@@ -73345,10 +75004,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23396</v>
+        <v>23949</v>
       </c>
       <c r="B16" t="s">
-        <v>23432</v>
+        <v>23985</v>
       </c>
       <c r="C16" s="1">
         <v>101315.1098362044</v>
@@ -73371,10 +75030,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23397</v>
+        <v>23950</v>
       </c>
       <c r="B17" t="s">
-        <v>23433</v>
+        <v>23986</v>
       </c>
       <c r="C17" s="1">
         <v>526.84154559200761</v>
@@ -73395,10 +75054,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23398</v>
+        <v>23951</v>
       </c>
       <c r="B18" t="s">
-        <v>23434</v>
+        <v>23987</v>
       </c>
       <c r="C18" s="1">
         <v>1300.503467</v>
@@ -73419,10 +75078,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23399</v>
+        <v>23952</v>
       </c>
       <c r="B19" t="s">
-        <v>23435</v>
+        <v>23988</v>
       </c>
       <c r="C19" s="1">
         <v>1300.503467</v>
@@ -73441,10 +75100,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23400</v>
+        <v>23953</v>
       </c>
       <c r="B20" t="s">
-        <v>23436</v>
+        <v>23989</v>
       </c>
       <c r="C20" s="1">
         <v>16387.63379557012</v>
@@ -73467,10 +75126,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23401</v>
+        <v>23954</v>
       </c>
       <c r="B21" t="s">
-        <v>23437</v>
+        <v>23990</v>
       </c>
       <c r="C21" s="1">
         <v>97.490238000000005</v>
@@ -73489,10 +75148,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23402</v>
+        <v>23955</v>
       </c>
       <c r="B22" t="s">
-        <v>23438</v>
+        <v>23991</v>
       </c>
       <c r="C22" s="1">
         <v>1386.9169386399999</v>
@@ -73509,10 +75168,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23403</v>
+        <v>23956</v>
       </c>
       <c r="B23" t="s">
-        <v>23439</v>
+        <v>23992</v>
       </c>
       <c r="C23" s="1">
         <v>1117.864241</v>
@@ -73531,10 +75190,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23404</v>
+        <v>23957</v>
       </c>
       <c r="B24" t="s">
-        <v>23440</v>
+        <v>23993</v>
       </c>
       <c r="C24" s="1">
         <v>13785.36237793012</v>
@@ -73557,10 +75216,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23405</v>
+        <v>23958</v>
       </c>
       <c r="B25" t="s">
-        <v>23441</v>
+        <v>23994</v>
       </c>
       <c r="C25" s="1">
         <v>98850.343655568271</v>
@@ -73583,10 +75242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23406</v>
+        <v>23959</v>
       </c>
       <c r="B26" t="s">
-        <v>23442</v>
+        <v>23995</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -73601,15 +75260,15 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23407</v>
+        <v>23960</v>
       </c>
       <c r="B27" t="s">
-        <v>23443</v>
+        <v>23996</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-25017.388782343201</v>
+        <v>-25017.38878234318</v>
       </c>
       <c r="F27" s="1">
         <v>-25017.388782343201</v>
@@ -73623,10 +75282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23408</v>
+        <v>23961</v>
       </c>
       <c r="B28" t="s">
-        <v>23444</v>
+        <v>23997</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -73641,10 +75300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23409</v>
+        <v>23962</v>
       </c>
       <c r="B29" t="s">
-        <v>23445</v>
+        <v>23998</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -73663,10 +75322,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23410</v>
+        <v>23963</v>
       </c>
       <c r="B30" t="s">
-        <v>23446</v>
+        <v>23999</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -73681,15 +75340,15 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23411</v>
+        <v>23964</v>
       </c>
       <c r="B31" t="s">
-        <v>23447</v>
+        <v>24000</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-25017.38878234318</v>
+        <v>-25017.388782343201</v>
       </c>
       <c r="F31" s="1">
         <v>-25017.38878234318</v>
@@ -73703,10 +75362,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23412</v>
+        <v>23965</v>
       </c>
       <c r="B32" t="s">
-        <v>23448</v>
+        <v>24001</v>
       </c>
       <c r="C32" s="1">
         <v>-3385.8935585237782</v>
@@ -73721,10 +75380,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23413</v>
+        <v>23966</v>
       </c>
       <c r="B33" t="s">
-        <v>23449</v>
+        <v>24002</v>
       </c>
       <c r="C33" s="1">
         <v>0.27703699999999998</v>
@@ -73747,10 +75406,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23414</v>
+        <v>23967</v>
       </c>
       <c r="B34" t="s">
-        <v>23450</v>
+        <v>24003</v>
       </c>
       <c r="C34" s="1">
         <v>-4009.0753441289771</v>
@@ -73762,7 +75421,7 @@
         <v>-63565.818181042087</v>
       </c>
       <c r="F34" s="1">
-        <v>-63565.770979082881</v>
+        <v>-63565.818181042087</v>
       </c>
       <c r="G34" s="1">
         <v>43782.161676834643</v>
@@ -73773,10 +75432,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23414</v>
+        <v>23967</v>
       </c>
       <c r="B35" t="s">
-        <v>23450</v>
+        <v>24003</v>
       </c>
       <c r="C35" s="1">
         <v>-4009.0753441289712</v>
@@ -73788,7 +75447,7 @@
         <v>-63565.770979082881</v>
       </c>
       <c r="F35" s="1">
-        <v>-63565.818181042087</v>
+        <v>-63565.770979082881</v>
       </c>
       <c r="G35" s="1">
         <v>43782.161676835007</v>
@@ -73799,10 +75458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23415</v>
+        <v>23968</v>
       </c>
       <c r="B36" t="s">
-        <v>23451</v>
+        <v>24004</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -73817,10 +75476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23416</v>
+        <v>23969</v>
       </c>
       <c r="B37" t="s">
-        <v>23452</v>
+        <v>24005</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -73837,10 +75496,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23417</v>
+        <v>23970</v>
       </c>
       <c r="B38" t="s">
-        <v>23453</v>
+        <v>24006</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -73862,36 +75521,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23460</v>
+        <v>24013</v>
       </c>
       <c r="B1" t="s">
-        <v>23497</v>
+        <v>24050</v>
       </c>
       <c r="C1" t="s">
-        <v>23533</v>
+        <v>24086</v>
       </c>
       <c r="D1" t="s">
-        <v>23534</v>
+        <v>24087</v>
       </c>
       <c r="E1" t="s">
-        <v>23535</v>
+        <v>24088</v>
       </c>
       <c r="F1" t="s">
-        <v>23536</v>
+        <v>24089</v>
       </c>
       <c r="G1" t="s">
-        <v>23537</v>
+        <v>24090</v>
       </c>
       <c r="H1" t="s">
-        <v>23538</v>
+        <v>24091</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23461</v>
+        <v>24014</v>
       </c>
       <c r="B2" t="s">
-        <v>23498</v>
+        <v>24051</v>
       </c>
       <c r="C2" s="1">
         <v>-101427.2938489076</v>
@@ -73906,10 +75565,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23462</v>
+        <v>24015</v>
       </c>
       <c r="B3" t="s">
-        <v>23499</v>
+        <v>24052</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -73928,10 +75587,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23463</v>
+        <v>24016</v>
       </c>
       <c r="B4" t="s">
-        <v>23500</v>
+        <v>24053</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -73948,10 +75607,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23464</v>
+        <v>24017</v>
       </c>
       <c r="B5" t="s">
-        <v>23501</v>
+        <v>24054</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -73964,10 +75623,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23465</v>
+        <v>24018</v>
       </c>
       <c r="B6" t="s">
-        <v>23502</v>
+        <v>24055</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -73984,10 +75643,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23466</v>
+        <v>24019</v>
       </c>
       <c r="B7" t="s">
-        <v>23503</v>
+        <v>24056</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -74000,10 +75659,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23467</v>
+        <v>24020</v>
       </c>
       <c r="B8" t="s">
-        <v>23503</v>
+        <v>24056</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -74016,10 +75675,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23468</v>
+        <v>24021</v>
       </c>
       <c r="B9" t="s">
-        <v>23504</v>
+        <v>24057</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -74032,10 +75691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23469</v>
+        <v>24022</v>
       </c>
       <c r="B10" t="s">
-        <v>23505</v>
+        <v>24058</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -74050,10 +75709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23470</v>
+        <v>24023</v>
       </c>
       <c r="B11" t="s">
-        <v>23506</v>
+        <v>24059</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -74072,10 +75731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23471</v>
+        <v>24024</v>
       </c>
       <c r="B12" t="s">
-        <v>23507</v>
+        <v>24060</v>
       </c>
       <c r="C12" s="1">
         <v>-92.934358778526615</v>
@@ -74094,10 +75753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23472</v>
+        <v>24025</v>
       </c>
       <c r="B13" t="s">
-        <v>23508</v>
+        <v>24061</v>
       </c>
       <c r="C13" s="1">
         <v>162249.8021316196</v>
@@ -74120,10 +75779,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23473</v>
+        <v>24026</v>
       </c>
       <c r="B14" t="s">
-        <v>23509</v>
+        <v>24062</v>
       </c>
       <c r="C14" s="1">
         <v>43179.357846405859</v>
@@ -74146,10 +75805,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23474</v>
+        <v>24027</v>
       </c>
       <c r="B15" t="s">
-        <v>23510</v>
+        <v>24063</v>
       </c>
       <c r="C15" s="1">
         <v>119070.4442852137</v>
@@ -74170,10 +75829,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23475</v>
+        <v>24028</v>
       </c>
       <c r="B16" t="s">
-        <v>23511</v>
+        <v>24064</v>
       </c>
       <c r="C16" s="1">
         <v>111072.9372501466</v>
@@ -74196,10 +75855,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23476</v>
+        <v>24029</v>
       </c>
       <c r="B17" t="s">
-        <v>23512</v>
+        <v>24065</v>
       </c>
       <c r="C17" s="1">
         <v>455.25087191519339</v>
@@ -74220,10 +75879,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23477</v>
+        <v>24030</v>
       </c>
       <c r="B18" t="s">
-        <v>23513</v>
+        <v>24066</v>
       </c>
       <c r="C18" s="1">
         <v>1486.8528134281901</v>
@@ -74244,10 +75903,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23478</v>
+        <v>24031</v>
       </c>
       <c r="B19" t="s">
-        <v>23514</v>
+        <v>24067</v>
       </c>
       <c r="C19" s="1">
         <v>1486.8528134281901</v>
@@ -74266,10 +75925,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23479</v>
+        <v>24032</v>
       </c>
       <c r="B20" t="s">
-        <v>23515</v>
+        <v>24068</v>
       </c>
       <c r="C20" s="1">
         <v>19645.88621086465</v>
@@ -74292,10 +75951,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23480</v>
+        <v>24033</v>
       </c>
       <c r="B21" t="s">
-        <v>23516</v>
+        <v>24069</v>
       </c>
       <c r="C21" s="1">
         <v>1.3780870000000001</v>
@@ -74314,10 +75973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23481</v>
+        <v>24034</v>
       </c>
       <c r="B22" t="s">
-        <v>23517</v>
+        <v>24070</v>
       </c>
       <c r="C22" s="1">
         <v>1680.6084285300001</v>
@@ -74334,10 +75993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23482</v>
+        <v>24035</v>
       </c>
       <c r="B23" t="s">
-        <v>23518</v>
+        <v>24071</v>
       </c>
       <c r="C23" s="1">
         <v>1167.0419095569939</v>
@@ -74356,10 +76015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23483</v>
+        <v>24036</v>
       </c>
       <c r="B24" t="s">
-        <v>23519</v>
+        <v>24072</v>
       </c>
       <c r="C24" s="1">
         <v>16796.857785777662</v>
@@ -74382,10 +76041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23484</v>
+        <v>24037</v>
       </c>
       <c r="B25" t="s">
-        <v>23520</v>
+        <v>24073</v>
       </c>
       <c r="C25" s="1">
         <v>108339.94151571881</v>
@@ -74408,10 +76067,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23485</v>
+        <v>24038</v>
       </c>
       <c r="B26" t="s">
-        <v>23521</v>
+        <v>24074</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -74424,10 +76083,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23486</v>
+        <v>24039</v>
       </c>
       <c r="B27" t="s">
-        <v>23522</v>
+        <v>24075</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -74446,10 +76105,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23487</v>
+        <v>24040</v>
       </c>
       <c r="B28" t="s">
-        <v>23523</v>
+        <v>24076</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -74464,10 +76123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23488</v>
+        <v>24041</v>
       </c>
       <c r="B29" t="s">
-        <v>23524</v>
+        <v>24077</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -74486,10 +76145,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23489</v>
+        <v>24042</v>
       </c>
       <c r="B30" t="s">
-        <v>23525</v>
+        <v>24078</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -74502,10 +76161,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23490</v>
+        <v>24043</v>
       </c>
       <c r="B31" t="s">
-        <v>23526</v>
+        <v>24079</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -74524,10 +76183,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23491</v>
+        <v>24044</v>
       </c>
       <c r="B32" t="s">
-        <v>23527</v>
+        <v>24080</v>
       </c>
       <c r="C32" s="1">
         <v>6912.6476668112009</v>
@@ -74542,10 +76201,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23492</v>
+        <v>24045</v>
       </c>
       <c r="B33" t="s">
-        <v>23528</v>
+        <v>24081</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -74566,10 +76225,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23493</v>
+        <v>24046</v>
       </c>
       <c r="B34" t="s">
-        <v>23529</v>
+        <v>24082</v>
       </c>
       <c r="C34" s="1">
         <v>5442.5976345336867</v>
@@ -74578,24 +76237,24 @@
         <v>5442.5976345336967</v>
       </c>
       <c r="E34" s="1">
-        <v>-49773.892247343349</v>
+        <v>-49773.892247342999</v>
       </c>
       <c r="F34" s="1">
         <v>-49773.892247342999</v>
       </c>
       <c r="G34" s="1">
+        <v>33283.712597372112</v>
+      </c>
+      <c r="H34" s="1">
         <v>33283.712597372418</v>
-      </c>
-      <c r="H34" s="1">
-        <v>33283.712597372112</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23493</v>
+        <v>24046</v>
       </c>
       <c r="B35" t="s">
-        <v>23529</v>
+        <v>24082</v>
       </c>
       <c r="C35" s="1">
         <v>5442.5976345336967</v>
@@ -74604,42 +76263,44 @@
         <v>5442.5976345336867</v>
       </c>
       <c r="E35" s="1">
-        <v>-49773.892247342999</v>
+        <v>-49773.892247343349</v>
       </c>
       <c r="F35" s="1">
         <v>-49773.892247343349</v>
       </c>
       <c r="G35" s="1">
+        <v>33283.712597372418</v>
+      </c>
+      <c r="H35" s="1">
         <v>33283.712597372112</v>
-      </c>
-      <c r="H35" s="1">
-        <v>33283.712597372418</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23494</v>
+        <v>24047</v>
       </c>
       <c r="B36" t="s">
-        <v>23530</v>
+        <v>24083</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>207169.67690947151</v>
-      </c>
-      <c r="F36" s="1">
-        <v>207169.67690947151</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+        <v>215925.528549476</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
+        <v>381.05244255449912</v>
+      </c>
+      <c r="H36" s="1">
+        <v>271956.46735150547</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23495</v>
+        <v>24048</v>
       </c>
       <c r="B37" t="s">
-        <v>23531</v>
+        <v>24084</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -74652,23 +76313,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23496</v>
+        <v>24049</v>
       </c>
       <c r="B38" t="s">
-        <v>23532</v>
+        <v>24085</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>215925.528549476</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1">
-        <v>381.05244255449912</v>
-      </c>
-      <c r="H38" s="1">
-        <v>271956.46735150547</v>
-      </c>
+        <v>207169.67690947151</v>
+      </c>
+      <c r="F38" s="1">
+        <v>207169.67690947151</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -74681,36 +76340,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23539</v>
+        <v>24092</v>
       </c>
       <c r="B1" t="s">
-        <v>23576</v>
+        <v>24129</v>
       </c>
       <c r="C1" t="s">
-        <v>23612</v>
+        <v>24165</v>
       </c>
       <c r="D1" t="s">
-        <v>23613</v>
+        <v>24166</v>
       </c>
       <c r="E1" t="s">
-        <v>23614</v>
+        <v>24167</v>
       </c>
       <c r="F1" t="s">
-        <v>23615</v>
+        <v>24168</v>
       </c>
       <c r="G1" t="s">
-        <v>23616</v>
+        <v>24169</v>
       </c>
       <c r="H1" t="s">
-        <v>23617</v>
+        <v>24170</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23540</v>
+        <v>24093</v>
       </c>
       <c r="B2" t="s">
-        <v>23577</v>
+        <v>24130</v>
       </c>
       <c r="C2" s="1">
         <v>-132325.81806931089</v>
@@ -74725,10 +76384,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23541</v>
+        <v>24094</v>
       </c>
       <c r="B3" t="s">
-        <v>23578</v>
+        <v>24131</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -74747,10 +76406,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23542</v>
+        <v>24095</v>
       </c>
       <c r="B4" t="s">
-        <v>23579</v>
+        <v>24132</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -74767,10 +76426,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23543</v>
+        <v>24096</v>
       </c>
       <c r="B5" t="s">
-        <v>23580</v>
+        <v>24133</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -74783,10 +76442,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23544</v>
+        <v>24097</v>
       </c>
       <c r="B6" t="s">
-        <v>23581</v>
+        <v>24134</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -74803,10 +76462,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23545</v>
+        <v>24098</v>
       </c>
       <c r="B7" t="s">
-        <v>23582</v>
+        <v>24135</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -74819,10 +76478,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23546</v>
+        <v>24099</v>
       </c>
       <c r="B8" t="s">
-        <v>23582</v>
+        <v>24135</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -74835,10 +76494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23547</v>
+        <v>24100</v>
       </c>
       <c r="B9" t="s">
-        <v>23583</v>
+        <v>24136</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -74851,10 +76510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23548</v>
+        <v>24101</v>
       </c>
       <c r="B10" t="s">
-        <v>23584</v>
+        <v>24137</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -74869,10 +76528,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23549</v>
+        <v>24102</v>
       </c>
       <c r="B11" t="s">
-        <v>23585</v>
+        <v>24138</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -74891,10 +76550,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23550</v>
+        <v>24103</v>
       </c>
       <c r="B12" t="s">
-        <v>23586</v>
+        <v>24139</v>
       </c>
       <c r="C12" s="1">
         <v>-111.3731775422125</v>
@@ -74913,10 +76572,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23551</v>
+        <v>24104</v>
       </c>
       <c r="B13" t="s">
-        <v>23587</v>
+        <v>24140</v>
       </c>
       <c r="C13" s="1">
         <v>160506.74429795379</v>
@@ -74939,10 +76598,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23552</v>
+        <v>24105</v>
       </c>
       <c r="B14" t="s">
-        <v>23588</v>
+        <v>24141</v>
       </c>
       <c r="C14" s="1">
         <v>47266.390163401513</v>
@@ -74965,10 +76624,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23553</v>
+        <v>24106</v>
       </c>
       <c r="B15" t="s">
-        <v>23589</v>
+        <v>24142</v>
       </c>
       <c r="C15" s="1">
         <v>113240.3541345523</v>
@@ -74989,10 +76648,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23554</v>
+        <v>24107</v>
       </c>
       <c r="B16" t="s">
-        <v>23590</v>
+        <v>24143</v>
       </c>
       <c r="C16" s="1">
         <v>106078.98298231589</v>
@@ -75015,10 +76674,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23555</v>
+        <v>24108</v>
       </c>
       <c r="B17" t="s">
-        <v>23591</v>
+        <v>24144</v>
       </c>
       <c r="C17" s="1">
         <v>376.90302765656929</v>
@@ -75039,10 +76698,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23556</v>
+        <v>24109</v>
       </c>
       <c r="B18" t="s">
-        <v>23592</v>
+        <v>24145</v>
       </c>
       <c r="C18" s="1">
         <v>1655.657643517555</v>
@@ -75063,10 +76722,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23557</v>
+        <v>24110</v>
       </c>
       <c r="B19" t="s">
-        <v>23593</v>
+        <v>24146</v>
       </c>
       <c r="C19" s="1">
         <v>1655.657643517555</v>
@@ -75085,10 +76744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23558</v>
+        <v>24111</v>
       </c>
       <c r="B20" t="s">
-        <v>23594</v>
+        <v>24147</v>
       </c>
       <c r="C20" s="1">
         <v>22226.602795191338</v>
@@ -75111,10 +76770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23559</v>
+        <v>24112</v>
       </c>
       <c r="B21" t="s">
-        <v>23595</v>
+        <v>24148</v>
       </c>
       <c r="C21" s="1">
         <v>2.9676309999999999</v>
@@ -75133,10 +76792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23560</v>
+        <v>24113</v>
       </c>
       <c r="B22" t="s">
-        <v>23596</v>
+        <v>24149</v>
       </c>
       <c r="C22" s="1">
         <v>2646.0630505200002</v>
@@ -75153,10 +76812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23561</v>
+        <v>24114</v>
       </c>
       <c r="B23" t="s">
-        <v>23597</v>
+        <v>24150</v>
       </c>
       <c r="C23" s="1">
         <v>1452.5266412882031</v>
@@ -75175,10 +76834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23562</v>
+        <v>24115</v>
       </c>
       <c r="B24" t="s">
-        <v>23598</v>
+        <v>24151</v>
       </c>
       <c r="C24" s="1">
         <v>18125.045472383139</v>
@@ -75201,10 +76860,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23563</v>
+        <v>24116</v>
       </c>
       <c r="B25" t="s">
-        <v>23599</v>
+        <v>24152</v>
       </c>
       <c r="C25" s="1">
         <v>103687.46021795391</v>
@@ -75227,10 +76886,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23564</v>
+        <v>24117</v>
       </c>
       <c r="B26" t="s">
-        <v>23600</v>
+        <v>24153</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -75243,15 +76902,15 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23565</v>
+        <v>24118</v>
       </c>
       <c r="B27" t="s">
-        <v>23601</v>
+        <v>24154</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-47487.012322160823</v>
+        <v>-47487.012322160852</v>
       </c>
       <c r="F27" s="1">
         <v>-47487.012322160823</v>
@@ -75265,10 +76924,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23566</v>
+        <v>24119</v>
       </c>
       <c r="B28" t="s">
-        <v>23602</v>
+        <v>24155</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -75283,10 +76942,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23567</v>
+        <v>24120</v>
       </c>
       <c r="B29" t="s">
-        <v>23603</v>
+        <v>24156</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -75305,10 +76964,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23568</v>
+        <v>24121</v>
       </c>
       <c r="B30" t="s">
-        <v>23604</v>
+        <v>24157</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -75321,15 +76980,15 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23569</v>
+        <v>24122</v>
       </c>
       <c r="B31" t="s">
-        <v>23605</v>
+        <v>24158</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-47487.012322160852</v>
+        <v>-47487.012322160823</v>
       </c>
       <c r="F31" s="1">
         <v>-47487.012322160852</v>
@@ -75343,10 +77002,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23570</v>
+        <v>24123</v>
       </c>
       <c r="B32" t="s">
-        <v>23606</v>
+        <v>24159</v>
       </c>
       <c r="C32" s="1">
         <v>-28638.357851356981</v>
@@ -75361,10 +77020,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23571</v>
+        <v>24124</v>
       </c>
       <c r="B33" t="s">
-        <v>23607</v>
+        <v>24160</v>
       </c>
       <c r="C33" s="1">
         <v>13.58729015431644</v>
@@ -75387,10 +77046,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23572</v>
+        <v>24125</v>
       </c>
       <c r="B34" t="s">
-        <v>23608</v>
+        <v>24161</v>
       </c>
       <c r="C34" s="1">
         <v>-14516.140951382629</v>
@@ -75408,15 +77067,15 @@
         <v>39248.472782472993</v>
       </c>
       <c r="H34" s="1">
-        <v>39248.472782472847</v>
+        <v>39248.472782472993</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23572</v>
+        <v>24125</v>
       </c>
       <c r="B35" t="s">
-        <v>23608</v>
+        <v>24161</v>
       </c>
       <c r="C35" s="1">
         <v>-14516.15048177604</v>
@@ -75434,51 +77093,51 @@
         <v>39248.472782472847</v>
       </c>
       <c r="H35" s="1">
-        <v>39248.472782472993</v>
+        <v>39248.472782472847</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23573</v>
+        <v>24126</v>
       </c>
       <c r="B36" t="s">
-        <v>23609</v>
+        <v>24162</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>1691.532447066628</v>
+        <v>239376.743428952</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="G36" s="1">
+        <v>402.67289956090139</v>
+      </c>
+      <c r="H36" s="1">
+        <v>298520.24294644757</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23574</v>
+        <v>24127</v>
       </c>
       <c r="B37" t="s">
-        <v>23610</v>
+        <v>24163</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>239376.743428952</v>
+        <v>1691.532447066628</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1">
-        <v>402.67289956090139</v>
-      </c>
-      <c r="H37" s="1">
-        <v>298520.24294644757</v>
-      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23575</v>
+        <v>24128</v>
       </c>
       <c r="B38" t="s">
-        <v>23611</v>
+        <v>24164</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -75502,36 +77161,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23618</v>
+        <v>24171</v>
       </c>
       <c r="B1" t="s">
-        <v>23655</v>
+        <v>24208</v>
       </c>
       <c r="C1" t="s">
-        <v>23691</v>
+        <v>24244</v>
       </c>
       <c r="D1" t="s">
-        <v>23692</v>
+        <v>24245</v>
       </c>
       <c r="E1" t="s">
-        <v>23693</v>
+        <v>24246</v>
       </c>
       <c r="F1" t="s">
-        <v>23694</v>
+        <v>24247</v>
       </c>
       <c r="G1" t="s">
-        <v>23695</v>
+        <v>24248</v>
       </c>
       <c r="H1" t="s">
-        <v>23696</v>
+        <v>24249</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23619</v>
+        <v>24172</v>
       </c>
       <c r="B2" t="s">
-        <v>23656</v>
+        <v>24209</v>
       </c>
       <c r="C2" s="1">
         <v>-104514.67406784389</v>
@@ -75546,10 +77205,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23620</v>
+        <v>24173</v>
       </c>
       <c r="B3" t="s">
-        <v>23657</v>
+        <v>24210</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -75568,10 +77227,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23621</v>
+        <v>24174</v>
       </c>
       <c r="B4" t="s">
-        <v>23658</v>
+        <v>24211</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -75588,10 +77247,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23622</v>
+        <v>24175</v>
       </c>
       <c r="B5" t="s">
-        <v>23659</v>
+        <v>24212</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -75604,10 +77263,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23623</v>
+        <v>24176</v>
       </c>
       <c r="B6" t="s">
-        <v>23660</v>
+        <v>24213</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -75624,10 +77283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23624</v>
+        <v>24177</v>
       </c>
       <c r="B7" t="s">
-        <v>23661</v>
+        <v>24214</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -75640,10 +77299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23625</v>
+        <v>24178</v>
       </c>
       <c r="B8" t="s">
-        <v>23661</v>
+        <v>24214</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -75656,10 +77315,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23626</v>
+        <v>24179</v>
       </c>
       <c r="B9" t="s">
-        <v>23662</v>
+        <v>24215</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -75672,10 +77331,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23627</v>
+        <v>24180</v>
       </c>
       <c r="B10" t="s">
-        <v>23663</v>
+        <v>24216</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -75690,10 +77349,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23628</v>
+        <v>24181</v>
       </c>
       <c r="B11" t="s">
-        <v>23664</v>
+        <v>24217</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -75712,10 +77371,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23629</v>
+        <v>24182</v>
       </c>
       <c r="B12" t="s">
-        <v>23665</v>
+        <v>24218</v>
       </c>
       <c r="C12" s="1">
         <v>-149.5741136579793</v>
@@ -75734,10 +77393,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23630</v>
+        <v>24183</v>
       </c>
       <c r="B13" t="s">
-        <v>23666</v>
+        <v>24219</v>
       </c>
       <c r="C13" s="1">
         <v>151856.17438438139</v>
@@ -75760,10 +77419,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23631</v>
+        <v>24184</v>
       </c>
       <c r="B14" t="s">
-        <v>23667</v>
+        <v>24220</v>
       </c>
       <c r="C14" s="1">
         <v>54754.723496312057</v>
@@ -75786,10 +77445,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23632</v>
+        <v>24185</v>
       </c>
       <c r="B15" t="s">
-        <v>23668</v>
+        <v>24221</v>
       </c>
       <c r="C15" s="1">
         <v>97101.450888069332</v>
@@ -75808,10 +77467,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23633</v>
+        <v>24186</v>
       </c>
       <c r="B16" t="s">
-        <v>23669</v>
+        <v>24222</v>
       </c>
       <c r="C16" s="1">
         <v>121151.1679762976</v>
@@ -75834,10 +77493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23634</v>
+        <v>24187</v>
       </c>
       <c r="B17" t="s">
-        <v>23670</v>
+        <v>24223</v>
       </c>
       <c r="C17" s="1">
         <v>829.94672213900139</v>
@@ -75858,10 +77517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23635</v>
+        <v>24188</v>
       </c>
       <c r="B18" t="s">
-        <v>23671</v>
+        <v>24224</v>
       </c>
       <c r="C18" s="1">
         <v>1851.55709250523</v>
@@ -75882,10 +77541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23636</v>
+        <v>24189</v>
       </c>
       <c r="B19" t="s">
-        <v>23672</v>
+        <v>24225</v>
       </c>
       <c r="C19" s="1">
         <v>1851.55709250523</v>
@@ -75904,10 +77563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23637</v>
+        <v>24190</v>
       </c>
       <c r="B20" t="s">
-        <v>23673</v>
+        <v>24226</v>
       </c>
       <c r="C20" s="1">
         <v>13110.58352570426</v>
@@ -75930,10 +77589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23638</v>
+        <v>24191</v>
       </c>
       <c r="B21" t="s">
-        <v>23674</v>
+        <v>24227</v>
       </c>
       <c r="C21" s="1">
         <v>1.421961</v>
@@ -75952,10 +77611,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23639</v>
+        <v>24192</v>
       </c>
       <c r="B22" t="s">
-        <v>23675</v>
+        <v>24228</v>
       </c>
       <c r="C22" s="1">
         <v>2008.0292188799999</v>
@@ -75972,10 +77631,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23640</v>
+        <v>24193</v>
       </c>
       <c r="B23" t="s">
-        <v>23676</v>
+        <v>24229</v>
       </c>
       <c r="C23" s="1">
         <v>728.95224428820325</v>
@@ -75994,10 +77653,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23641</v>
+        <v>24194</v>
       </c>
       <c r="B24" t="s">
-        <v>23677</v>
+        <v>24230</v>
       </c>
       <c r="C24" s="1">
         <v>10372.18010153606</v>
@@ -76020,10 +77679,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23642</v>
+        <v>24195</v>
       </c>
       <c r="B25" t="s">
-        <v>23678</v>
+        <v>24231</v>
       </c>
       <c r="C25" s="1">
         <v>117812.0378742148</v>
@@ -76046,10 +77705,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23643</v>
+        <v>24196</v>
       </c>
       <c r="B26" t="s">
-        <v>23679</v>
+        <v>24232</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -76062,10 +77721,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23644</v>
+        <v>24197</v>
       </c>
       <c r="B27" t="s">
-        <v>23680</v>
+        <v>24233</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -76084,10 +77743,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23645</v>
+        <v>24198</v>
       </c>
       <c r="B28" t="s">
-        <v>23681</v>
+        <v>24234</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -76102,10 +77761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23646</v>
+        <v>24199</v>
       </c>
       <c r="B29" t="s">
-        <v>23682</v>
+        <v>24235</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -76124,10 +77783,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23647</v>
+        <v>24200</v>
       </c>
       <c r="B30" t="s">
-        <v>23683</v>
+        <v>24236</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -76140,10 +77799,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23648</v>
+        <v>24201</v>
       </c>
       <c r="B31" t="s">
-        <v>23684</v>
+        <v>24237</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -76162,10 +77821,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23649</v>
+        <v>24202</v>
       </c>
       <c r="B32" t="s">
-        <v>23685</v>
+        <v>24238</v>
       </c>
       <c r="C32" s="1">
         <v>13297.36380637088</v>
@@ -76180,10 +77839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23650</v>
+        <v>24203</v>
       </c>
       <c r="B33" t="s">
-        <v>23686</v>
+        <v>24239</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -76204,16 +77863,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23651</v>
+        <v>24204</v>
       </c>
       <c r="B34" t="s">
-        <v>23687</v>
+        <v>24240</v>
       </c>
       <c r="C34" s="1">
         <v>10171.468589380889</v>
       </c>
       <c r="D34" s="1">
-        <v>10171.459058987501</v>
+        <v>10171.468589380889</v>
       </c>
       <c r="E34" s="1">
         <v>-79545.106801385089</v>
@@ -76225,21 +77884,21 @@
         <v>66059.10105946564</v>
       </c>
       <c r="H34" s="1">
-        <v>66058.729479423899</v>
+        <v>66059.10105946564</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23651</v>
+        <v>24204</v>
       </c>
       <c r="B35" t="s">
-        <v>23687</v>
+        <v>24240</v>
       </c>
       <c r="C35" s="1">
         <v>10171.459058987501</v>
       </c>
       <c r="D35" s="1">
-        <v>10171.468589380889</v>
+        <v>10171.459058987501</v>
       </c>
       <c r="E35" s="1">
         <v>-79545.106801385089</v>
@@ -76251,60 +77910,60 @@
         <v>66058.729479423899</v>
       </c>
       <c r="H35" s="1">
-        <v>66059.10105946564</v>
+        <v>66058.729479423899</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23652</v>
+        <v>24205</v>
       </c>
       <c r="B36" t="s">
-        <v>23688</v>
+        <v>24241</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>1625.492093275358</v>
+        <v>250754.8245620098</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="G36" s="1">
+        <v>442.30808405340002</v>
+      </c>
+      <c r="H36" s="1">
+        <v>313181.58741649322</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23653</v>
+        <v>24206</v>
       </c>
       <c r="B37" t="s">
-        <v>23689</v>
+        <v>24242</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>250754.8245620098</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1">
-        <v>442.30808405340002</v>
-      </c>
-      <c r="H37" s="1">
-        <v>313181.58741649322</v>
-      </c>
+        <v>242248.42014405999</v>
+      </c>
+      <c r="F37" s="1">
+        <v>242248.42014405999</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23654</v>
+        <v>24207</v>
       </c>
       <c r="B38" t="s">
-        <v>23690</v>
+        <v>24243</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>242248.42014405999</v>
-      </c>
-      <c r="F38" s="1">
-        <v>242248.42014405999</v>
-      </c>
+        <v>1625.492093275358</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -76319,36 +77978,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23697</v>
+        <v>24250</v>
       </c>
       <c r="B1" t="s">
-        <v>23734</v>
+        <v>24287</v>
       </c>
       <c r="C1" t="s">
-        <v>23770</v>
+        <v>24323</v>
       </c>
       <c r="D1" t="s">
-        <v>23771</v>
+        <v>24324</v>
       </c>
       <c r="E1" t="s">
-        <v>23772</v>
+        <v>24325</v>
       </c>
       <c r="F1" t="s">
-        <v>23773</v>
+        <v>24326</v>
       </c>
       <c r="G1" t="s">
-        <v>23774</v>
+        <v>24327</v>
       </c>
       <c r="H1" t="s">
-        <v>23775</v>
+        <v>24328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23698</v>
+        <v>24251</v>
       </c>
       <c r="B2" t="s">
-        <v>23735</v>
+        <v>24288</v>
       </c>
       <c r="C2" s="1">
         <v>-200371.3593658637</v>
@@ -76363,10 +78022,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23699</v>
+        <v>24252</v>
       </c>
       <c r="B3" t="s">
-        <v>23736</v>
+        <v>24289</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -76385,10 +78044,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23700</v>
+        <v>24253</v>
       </c>
       <c r="B4" t="s">
-        <v>23737</v>
+        <v>24290</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -76405,10 +78064,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23701</v>
+        <v>24254</v>
       </c>
       <c r="B5" t="s">
-        <v>23738</v>
+        <v>24291</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -76421,10 +78080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23702</v>
+        <v>24255</v>
       </c>
       <c r="B6" t="s">
-        <v>23739</v>
+        <v>24292</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -76441,10 +78100,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23703</v>
+        <v>24256</v>
       </c>
       <c r="B7" t="s">
-        <v>23740</v>
+        <v>24293</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -76457,10 +78116,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23704</v>
+        <v>24257</v>
       </c>
       <c r="B8" t="s">
-        <v>23740</v>
+        <v>24293</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -76473,10 +78132,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23705</v>
+        <v>24258</v>
       </c>
       <c r="B9" t="s">
-        <v>23741</v>
+        <v>24294</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -76489,10 +78148,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23706</v>
+        <v>24259</v>
       </c>
       <c r="B10" t="s">
-        <v>23742</v>
+        <v>24295</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -76507,10 +78166,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23707</v>
+        <v>24260</v>
       </c>
       <c r="B11" t="s">
-        <v>23743</v>
+        <v>24296</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -76529,10 +78188,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23708</v>
+        <v>24261</v>
       </c>
       <c r="B12" t="s">
-        <v>23744</v>
+        <v>24297</v>
       </c>
       <c r="C12" s="1">
         <v>-155.06439238415939</v>
@@ -76551,10 +78210,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23709</v>
+        <v>24262</v>
       </c>
       <c r="B13" t="s">
-        <v>23745</v>
+        <v>24298</v>
       </c>
       <c r="C13" s="1">
         <v>314231.27904663578</v>
@@ -76577,10 +78236,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23710</v>
+        <v>24263</v>
       </c>
       <c r="B14" t="s">
-        <v>23746</v>
+        <v>24299</v>
       </c>
       <c r="C14" s="1">
         <v>51456.424245716291</v>
@@ -76603,10 +78262,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23711</v>
+        <v>24264</v>
       </c>
       <c r="B15" t="s">
-        <v>23747</v>
+        <v>24300</v>
       </c>
       <c r="C15" s="1">
         <v>262774.85480091948</v>
@@ -76625,10 +78284,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23712</v>
+        <v>24265</v>
       </c>
       <c r="B16" t="s">
-        <v>23748</v>
+        <v>24301</v>
       </c>
       <c r="C16" s="1">
         <v>265585.17502668808</v>
@@ -76651,10 +78310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23713</v>
+        <v>24266</v>
       </c>
       <c r="B17" t="s">
-        <v>23749</v>
+        <v>24302</v>
       </c>
       <c r="C17" s="1">
         <v>1300.758691809164</v>
@@ -76675,10 +78334,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23714</v>
+        <v>24267</v>
       </c>
       <c r="B18" t="s">
-        <v>23750</v>
+        <v>24303</v>
       </c>
       <c r="C18" s="1">
         <v>2035.2769079008131</v>
@@ -76699,10 +78358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23715</v>
+        <v>24268</v>
       </c>
       <c r="B19" t="s">
-        <v>23751</v>
+        <v>24304</v>
       </c>
       <c r="C19" s="1">
         <v>2035.2769079008131</v>
@@ -76721,10 +78380,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23716</v>
+        <v>24269</v>
       </c>
       <c r="B20" t="s">
-        <v>23752</v>
+        <v>24305</v>
       </c>
       <c r="C20" s="1">
         <v>13142.94333128056</v>
@@ -76747,10 +78406,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23717</v>
+        <v>24270</v>
       </c>
       <c r="B21" t="s">
-        <v>23753</v>
+        <v>24306</v>
       </c>
       <c r="C21" s="1">
         <v>1.218183</v>
@@ -76769,10 +78428,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23718</v>
+        <v>24271</v>
       </c>
       <c r="B22" t="s">
-        <v>23754</v>
+        <v>24307</v>
       </c>
       <c r="C22" s="1">
         <v>1687.2726680000001</v>
@@ -76789,10 +78448,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23719</v>
+        <v>24272</v>
       </c>
       <c r="B23" t="s">
-        <v>23755</v>
+        <v>24308</v>
       </c>
       <c r="C23" s="1">
         <v>2336.210388476667</v>
@@ -76811,10 +78470,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23720</v>
+        <v>24273</v>
       </c>
       <c r="B24" t="s">
-        <v>23756</v>
+        <v>24309</v>
       </c>
       <c r="C24" s="1">
         <v>9118.2420918038915</v>
@@ -76837,10 +78496,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23721</v>
+        <v>24274</v>
       </c>
       <c r="B25" t="s">
-        <v>23757</v>
+        <v>24310</v>
       </c>
       <c r="C25" s="1">
         <v>262376.75111480377</v>
@@ -76863,10 +78522,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23722</v>
+        <v>24275</v>
       </c>
       <c r="B26" t="s">
-        <v>23758</v>
+        <v>24311</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -76879,10 +78538,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23723</v>
+        <v>24276</v>
       </c>
       <c r="B27" t="s">
-        <v>23759</v>
+        <v>24312</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -76901,10 +78560,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23724</v>
+        <v>24277</v>
       </c>
       <c r="B28" t="s">
-        <v>23760</v>
+        <v>24313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -76919,10 +78578,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23725</v>
+        <v>24278</v>
       </c>
       <c r="B29" t="s">
-        <v>23761</v>
+        <v>24314</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -76941,10 +78600,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23726</v>
+        <v>24279</v>
       </c>
       <c r="B30" t="s">
-        <v>23762</v>
+        <v>24315</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -76957,10 +78616,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23727</v>
+        <v>24280</v>
       </c>
       <c r="B31" t="s">
-        <v>23763</v>
+        <v>24316</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -76979,10 +78638,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23728</v>
+        <v>24281</v>
       </c>
       <c r="B32" t="s">
-        <v>23764</v>
+        <v>24317</v>
       </c>
       <c r="C32" s="1">
         <v>62005.391748940048</v>
@@ -76997,10 +78656,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23729</v>
+        <v>24282</v>
       </c>
       <c r="B33" t="s">
-        <v>23765</v>
+        <v>24318</v>
       </c>
       <c r="C33" s="1">
         <v>86.331224277060215</v>
@@ -77023,10 +78682,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23730</v>
+        <v>24283</v>
       </c>
       <c r="B34" t="s">
-        <v>23766</v>
+        <v>24319</v>
       </c>
       <c r="C34" s="1">
         <v>63134.524836636163</v>
@@ -77041,18 +78700,18 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G34" s="1">
+        <v>50492.474199902237</v>
+      </c>
+      <c r="H34" s="1">
         <v>50492.474199901873</v>
-      </c>
-      <c r="H34" s="1">
-        <v>50492.474199902237</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23730</v>
+        <v>24283</v>
       </c>
       <c r="B35" t="s">
-        <v>23766</v>
+        <v>24319</v>
       </c>
       <c r="C35" s="1">
         <v>63134.515306242713</v>
@@ -77067,36 +78726,34 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G35" s="1">
+        <v>50492.474199901873</v>
+      </c>
+      <c r="H35" s="1">
         <v>50492.474199902237</v>
-      </c>
-      <c r="H35" s="1">
-        <v>50492.474199901873</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23731</v>
+        <v>24284</v>
       </c>
       <c r="B36" t="s">
-        <v>23767</v>
+        <v>24320</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>264574.52162751998</v>
-      </c>
-      <c r="F36" s="1">
-        <v>264574.52162751998</v>
-      </c>
+        <v>1891.473003789004</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23732</v>
+        <v>24285</v>
       </c>
       <c r="B37" t="s">
-        <v>23768</v>
+        <v>24321</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -77113,17 +78770,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23733</v>
+        <v>24286</v>
       </c>
       <c r="B38" t="s">
-        <v>23769</v>
+        <v>24322</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1891.473003789004</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>264574.52162751998</v>
+      </c>
+      <c r="F38" s="1">
+        <v>264574.52162751998</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>

--- a/input_data/sna_country_data/URY/cei.xlsx
+++ b/input_data/sna_country_data/URY/cei.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41902" uniqueCount="24329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42476" uniqueCount="24329">
   <si>
     <t>code</t>
   </si>
@@ -73056,36 +73056,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23776</v>
+        <v>24250</v>
       </c>
       <c r="B1" t="s">
-        <v>23813</v>
+        <v>24287</v>
       </c>
       <c r="C1" t="s">
-        <v>23849</v>
+        <v>24323</v>
       </c>
       <c r="D1" t="s">
-        <v>23850</v>
+        <v>24324</v>
       </c>
       <c r="E1" t="s">
-        <v>23851</v>
+        <v>24325</v>
       </c>
       <c r="F1" t="s">
-        <v>23852</v>
+        <v>24326</v>
       </c>
       <c r="G1" t="s">
-        <v>23853</v>
+        <v>24327</v>
       </c>
       <c r="H1" t="s">
-        <v>23854</v>
+        <v>24328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23777</v>
+        <v>24251</v>
       </c>
       <c r="B2" t="s">
-        <v>23814</v>
+        <v>24288</v>
       </c>
       <c r="C2" s="1">
         <v>-35345.263380289784</v>
@@ -73100,10 +73100,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23778</v>
+        <v>24252</v>
       </c>
       <c r="B3" t="s">
-        <v>23815</v>
+        <v>24289</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -73122,10 +73122,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23779</v>
+        <v>24261</v>
       </c>
       <c r="B4" t="s">
-        <v>23816</v>
+        <v>24297</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -73142,10 +73142,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23780</v>
+        <v>24253</v>
       </c>
       <c r="B5" t="s">
-        <v>23817</v>
+        <v>24290</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -73162,10 +73162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23781</v>
+        <v>24254</v>
       </c>
       <c r="B6" t="s">
-        <v>23818</v>
+        <v>24291</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -73178,10 +73178,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23782</v>
+        <v>24255</v>
       </c>
       <c r="B7" t="s">
-        <v>23819</v>
+        <v>24292</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -73198,10 +73198,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23783</v>
+        <v>24256</v>
       </c>
       <c r="B8" t="s">
-        <v>23820</v>
+        <v>24293</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -73216,10 +73216,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23784</v>
+        <v>24257</v>
       </c>
       <c r="B9" t="s">
-        <v>23820</v>
+        <v>24293</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -73232,10 +73232,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23785</v>
+        <v>24258</v>
       </c>
       <c r="B10" t="s">
-        <v>23821</v>
+        <v>24294</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -73250,10 +73250,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23786</v>
+        <v>24259</v>
       </c>
       <c r="B11" t="s">
-        <v>23822</v>
+        <v>24295</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -73268,10 +73268,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23787</v>
+        <v>24260</v>
       </c>
       <c r="B12" t="s">
-        <v>23823</v>
+        <v>24296</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -73290,10 +73290,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23788</v>
+        <v>24262</v>
       </c>
       <c r="B13" t="s">
-        <v>23824</v>
+        <v>24298</v>
       </c>
       <c r="C13" s="1">
         <v>105254.84066842961</v>
@@ -73316,10 +73316,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23789</v>
+        <v>24263</v>
       </c>
       <c r="B14" t="s">
-        <v>23825</v>
+        <v>24299</v>
       </c>
       <c r="C14" s="1">
         <v>20118.629433262511</v>
@@ -73342,10 +73342,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23790</v>
+        <v>24264</v>
       </c>
       <c r="B15" t="s">
-        <v>23826</v>
+        <v>24300</v>
       </c>
       <c r="C15" s="1">
         <v>85136.211235167109</v>
@@ -73368,10 +73368,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23791</v>
+        <v>24265</v>
       </c>
       <c r="B16" t="s">
-        <v>23827</v>
+        <v>24301</v>
       </c>
       <c r="C16" s="1">
         <v>77979.086634604173</v>
@@ -73394,10 +73394,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23792</v>
+        <v>24267</v>
       </c>
       <c r="B17" t="s">
-        <v>23828</v>
+        <v>24303</v>
       </c>
       <c r="C17" s="1">
         <v>708.07373372999996</v>
@@ -73418,10 +73418,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23793</v>
+        <v>24268</v>
       </c>
       <c r="B18" t="s">
-        <v>23829</v>
+        <v>24304</v>
       </c>
       <c r="C18" s="1">
         <v>708.07373372999996</v>
@@ -73438,10 +73438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23794</v>
+        <v>24269</v>
       </c>
       <c r="B19" t="s">
-        <v>23830</v>
+        <v>24305</v>
       </c>
       <c r="C19" s="1">
         <v>2128.9819248528388</v>
@@ -73464,10 +73464,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23795</v>
+        <v>24271</v>
       </c>
       <c r="B20" t="s">
-        <v>23831</v>
+        <v>24307</v>
       </c>
       <c r="C20" s="1">
         <v>610.943299077402</v>
@@ -73484,10 +73484,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23796</v>
+        <v>24272</v>
       </c>
       <c r="B21" t="s">
-        <v>23832</v>
+        <v>24308</v>
       </c>
       <c r="C21" s="1">
         <v>476.41603700000002</v>
@@ -73506,10 +73506,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23797</v>
+        <v>24273</v>
       </c>
       <c r="B22" t="s">
-        <v>23833</v>
+        <v>24309</v>
       </c>
       <c r="C22" s="1">
         <v>1041.622588775437</v>
@@ -73532,10 +73532,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23798</v>
+        <v>24266</v>
       </c>
       <c r="B23" t="s">
-        <v>23834</v>
+        <v>24302</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
@@ -73552,10 +73552,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23799</v>
+        <v>24270</v>
       </c>
       <c r="B24" t="s">
-        <v>23835</v>
+        <v>24306</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -73572,10 +73572,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23800</v>
+        <v>24274</v>
       </c>
       <c r="B25" t="s">
-        <v>23836</v>
+        <v>24310</v>
       </c>
       <c r="C25" s="1">
         <v>75685.254770642801</v>
@@ -73598,10 +73598,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23801</v>
+        <v>24279</v>
       </c>
       <c r="B26" t="s">
-        <v>23837</v>
+        <v>24315</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -73616,15 +73616,15 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23802</v>
+        <v>24280</v>
       </c>
       <c r="B27" t="s">
-        <v>23838</v>
+        <v>24316</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-3264.8749993161591</v>
+        <v>-3264.8749993161441</v>
       </c>
       <c r="F27" s="1">
         <v>-3264.8749993161441</v>
@@ -73638,10 +73638,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23803</v>
+        <v>24277</v>
       </c>
       <c r="B28" t="s">
-        <v>23839</v>
+        <v>24313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -73656,10 +73656,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23804</v>
+        <v>24278</v>
       </c>
       <c r="B29" t="s">
-        <v>23840</v>
+        <v>24314</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -73678,10 +73678,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23805</v>
+        <v>24279</v>
       </c>
       <c r="B30" t="s">
-        <v>23841</v>
+        <v>24315</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -73696,15 +73696,15 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23806</v>
+        <v>24280</v>
       </c>
       <c r="B31" t="s">
-        <v>23842</v>
+        <v>24316</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-3264.8749993161441</v>
+        <v>-3264.8749993161591</v>
       </c>
       <c r="F31" s="1">
         <v>-3264.8749993161591</v>
@@ -73718,10 +73718,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23807</v>
+        <v>24281</v>
       </c>
       <c r="B32" t="s">
-        <v>23843</v>
+        <v>24317</v>
       </c>
       <c r="C32" s="1">
         <v>40339.991390353032</v>
@@ -73736,10 +73736,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23808</v>
+        <v>24282</v>
       </c>
       <c r="B33" t="s">
-        <v>23844</v>
+        <v>24239</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -73760,10 +73760,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23809</v>
+        <v>24283</v>
       </c>
       <c r="B34" t="s">
-        <v>23845</v>
+        <v>24319</v>
       </c>
       <c r="C34" s="1">
         <v>37886.776197581872</v>
@@ -73786,10 +73786,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23809</v>
+        <v>24283</v>
       </c>
       <c r="B35" t="s">
-        <v>23845</v>
+        <v>24319</v>
       </c>
       <c r="C35" s="1">
         <v>37886.776197581872</v>
@@ -73812,46 +73812,46 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23810</v>
+        <v>24286</v>
       </c>
       <c r="B36" t="s">
-        <v>23846</v>
+        <v>24322</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>113976.0975413</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>79482.446760280014</v>
+      </c>
+      <c r="F36" s="1">
+        <v>79482.446760280014</v>
+      </c>
       <c r="G36" s="1"/>
-      <c r="H36" s="1">
-        <v>137582.86030768359</v>
-      </c>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23811</v>
+        <v>24285</v>
       </c>
       <c r="B37" t="s">
-        <v>23847</v>
+        <v>24321</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>79482.446760280014</v>
-      </c>
-      <c r="F37" s="1">
-        <v>79482.446760280014</v>
-      </c>
+        <v>113976.0975413</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="H37" s="1">
+        <v>137582.86030768359</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23812</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>23848</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -73873,36 +73873,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23855</v>
+        <v>24250</v>
       </c>
       <c r="B1" t="s">
-        <v>23892</v>
+        <v>24287</v>
       </c>
       <c r="C1" t="s">
-        <v>23928</v>
+        <v>24323</v>
       </c>
       <c r="D1" t="s">
-        <v>23929</v>
+        <v>24324</v>
       </c>
       <c r="E1" t="s">
-        <v>23930</v>
+        <v>24325</v>
       </c>
       <c r="F1" t="s">
-        <v>23931</v>
+        <v>24326</v>
       </c>
       <c r="G1" t="s">
-        <v>23932</v>
+        <v>24327</v>
       </c>
       <c r="H1" t="s">
-        <v>23933</v>
+        <v>24328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23856</v>
+        <v>24251</v>
       </c>
       <c r="B2" t="s">
-        <v>23893</v>
+        <v>24288</v>
       </c>
       <c r="C2" s="1">
         <v>-92111.334701685584</v>
@@ -73917,10 +73917,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23857</v>
+        <v>24252</v>
       </c>
       <c r="B3" t="s">
-        <v>23894</v>
+        <v>24289</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -73939,10 +73939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23858</v>
+        <v>24261</v>
       </c>
       <c r="B4" t="s">
-        <v>23895</v>
+        <v>24297</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -73959,10 +73959,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23859</v>
+        <v>24253</v>
       </c>
       <c r="B5" t="s">
-        <v>23896</v>
+        <v>24290</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -73979,10 +73979,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23860</v>
+        <v>24254</v>
       </c>
       <c r="B6" t="s">
-        <v>23897</v>
+        <v>24291</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -73995,10 +73995,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23861</v>
+        <v>24255</v>
       </c>
       <c r="B7" t="s">
-        <v>23898</v>
+        <v>24292</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -74015,10 +74015,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23862</v>
+        <v>24256</v>
       </c>
       <c r="B8" t="s">
-        <v>23899</v>
+        <v>24293</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -74031,10 +74031,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23863</v>
+        <v>24257</v>
       </c>
       <c r="B9" t="s">
-        <v>23899</v>
+        <v>24293</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -74047,10 +74047,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23864</v>
+        <v>24258</v>
       </c>
       <c r="B10" t="s">
-        <v>23900</v>
+        <v>24294</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -74063,10 +74063,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23865</v>
+        <v>24259</v>
       </c>
       <c r="B11" t="s">
-        <v>23901</v>
+        <v>24295</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -74081,10 +74081,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23866</v>
+        <v>24260</v>
       </c>
       <c r="B12" t="s">
-        <v>23902</v>
+        <v>24296</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -74103,10 +74103,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23867</v>
+        <v>24262</v>
       </c>
       <c r="B13" t="s">
-        <v>23903</v>
+        <v>24298</v>
       </c>
       <c r="C13" s="1">
         <v>111912.2883479437</v>
@@ -74129,10 +74129,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23868</v>
+        <v>24263</v>
       </c>
       <c r="B14" t="s">
-        <v>23904</v>
+        <v>24299</v>
       </c>
       <c r="C14" s="1">
         <v>37196.900831416431</v>
@@ -74155,10 +74155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23869</v>
+        <v>24264</v>
       </c>
       <c r="B15" t="s">
-        <v>23905</v>
+        <v>24300</v>
       </c>
       <c r="C15" s="1">
         <v>74715.387516527291</v>
@@ -74181,10 +74181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23870</v>
+        <v>24265</v>
       </c>
       <c r="B16" t="s">
-        <v>23906</v>
+        <v>24301</v>
       </c>
       <c r="C16" s="1">
         <v>81203.449470399617</v>
@@ -74207,10 +74207,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23871</v>
+        <v>24267</v>
       </c>
       <c r="B17" t="s">
-        <v>23907</v>
+        <v>24303</v>
       </c>
       <c r="C17" s="1">
         <v>1114.5240200000001</v>
@@ -74231,10 +74231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23872</v>
+        <v>24268</v>
       </c>
       <c r="B18" t="s">
-        <v>23908</v>
+        <v>24304</v>
       </c>
       <c r="C18" s="1">
         <v>1114.5240200000001</v>
@@ -74253,10 +74253,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23873</v>
+        <v>24269</v>
       </c>
       <c r="B19" t="s">
-        <v>23909</v>
+        <v>24305</v>
       </c>
       <c r="C19" s="1">
         <v>17219.038211090661</v>
@@ -74279,10 +74279,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23874</v>
+        <v>24270</v>
       </c>
       <c r="B20" t="s">
-        <v>23910</v>
+        <v>24306</v>
       </c>
       <c r="C20" s="1">
         <v>98.619980999999996</v>
@@ -74301,10 +74301,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23875</v>
+        <v>24271</v>
       </c>
       <c r="B21" t="s">
-        <v>23911</v>
+        <v>24307</v>
       </c>
       <c r="C21" s="1">
         <v>1657.9772827899999</v>
@@ -74321,10 +74321,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23876</v>
+        <v>24272</v>
       </c>
       <c r="B22" t="s">
-        <v>23912</v>
+        <v>24308</v>
       </c>
       <c r="C22" s="1">
         <v>1009.104553</v>
@@ -74343,10 +74343,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23877</v>
+        <v>24273</v>
       </c>
       <c r="B23" t="s">
-        <v>23913</v>
+        <v>24309</v>
       </c>
       <c r="C23" s="1">
         <v>14453.336394300661</v>
@@ -74369,10 +74369,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23878</v>
+        <v>24266</v>
       </c>
       <c r="B24" t="s">
-        <v>23914</v>
+        <v>24302</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
@@ -74391,10 +74391,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23879</v>
+        <v>24274</v>
       </c>
       <c r="B25" t="s">
-        <v>23915</v>
+        <v>24310</v>
       </c>
       <c r="C25" s="1">
         <v>79087.001794051394</v>
@@ -74417,10 +74417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23880</v>
+        <v>24279</v>
       </c>
       <c r="B26" t="s">
-        <v>23916</v>
+        <v>24315</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -74435,10 +74435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23881</v>
+        <v>24280</v>
       </c>
       <c r="B27" t="s">
-        <v>23917</v>
+        <v>24316</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -74457,10 +74457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23882</v>
+        <v>24277</v>
       </c>
       <c r="B28" t="s">
-        <v>23918</v>
+        <v>24313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -74475,10 +74475,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23883</v>
+        <v>24278</v>
       </c>
       <c r="B29" t="s">
-        <v>23919</v>
+        <v>24314</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -74497,10 +74497,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23884</v>
+        <v>24279</v>
       </c>
       <c r="B30" t="s">
-        <v>23920</v>
+        <v>24315</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -74515,10 +74515,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23885</v>
+        <v>24280</v>
       </c>
       <c r="B31" t="s">
-        <v>23921</v>
+        <v>24316</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -74537,10 +74537,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23886</v>
+        <v>24281</v>
       </c>
       <c r="B32" t="s">
-        <v>23922</v>
+        <v>24317</v>
       </c>
       <c r="C32" s="1">
         <v>-13024.332907634191</v>
@@ -74555,10 +74555,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23887</v>
+        <v>24282</v>
       </c>
       <c r="B33" t="s">
-        <v>23923</v>
+        <v>24318</v>
       </c>
       <c r="C33" s="1">
         <v>181.0641172</v>
@@ -74581,25 +74581,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23888</v>
+        <v>24283</v>
       </c>
       <c r="B34" t="s">
-        <v>23924</v>
+        <v>24319</v>
       </c>
       <c r="C34" s="1">
         <v>-14574.43484844782</v>
       </c>
       <c r="D34" s="1">
-        <v>-14574.43484844782</v>
+        <v>-14574.434848447811</v>
       </c>
       <c r="E34" s="1">
         <v>-66950.582658753847</v>
       </c>
       <c r="F34" s="1">
-        <v>-66950.582658753847</v>
+        <v>-66950.582658753861</v>
       </c>
       <c r="G34" s="1">
-        <v>55330.055140544151</v>
+        <v>55330.055140544697</v>
       </c>
       <c r="H34" s="1">
         <v>55330.055140544697</v>
@@ -74607,25 +74607,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23888</v>
+        <v>24283</v>
       </c>
       <c r="B35" t="s">
-        <v>23924</v>
+        <v>24319</v>
       </c>
       <c r="C35" s="1">
         <v>-14574.434848447811</v>
       </c>
       <c r="D35" s="1">
-        <v>-14574.434848447811</v>
+        <v>-14574.43484844782</v>
       </c>
       <c r="E35" s="1">
         <v>-66950.582658753861</v>
       </c>
       <c r="F35" s="1">
-        <v>-66950.582658753861</v>
+        <v>-66950.582658753847</v>
       </c>
       <c r="G35" s="1">
-        <v>55330.055140544697</v>
+        <v>55330.055140544151</v>
       </c>
       <c r="H35" s="1">
         <v>55330.055140544151</v>
@@ -74633,10 +74633,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23889</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>23925</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -74653,35 +74653,35 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23890</v>
+        <v>24284</v>
       </c>
       <c r="B37" t="s">
-        <v>23926</v>
+        <v>24320</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>147042.35994689999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>147042.21094677999</v>
-      </c>
+        <v>1410.7265588499999</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23891</v>
+        <v>24286</v>
       </c>
       <c r="B38" t="s">
-        <v>23927</v>
+        <v>24322</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1410.7265588499999</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>147042.35994689999</v>
+      </c>
+      <c r="F38" s="1">
+        <v>147042.21094677999</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -74696,36 +74696,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>23934</v>
+        <v>24250</v>
       </c>
       <c r="B1" t="s">
-        <v>23971</v>
+        <v>24287</v>
       </c>
       <c r="C1" t="s">
-        <v>24007</v>
+        <v>24323</v>
       </c>
       <c r="D1" t="s">
-        <v>24008</v>
+        <v>24324</v>
       </c>
       <c r="E1" t="s">
-        <v>24009</v>
+        <v>24325</v>
       </c>
       <c r="F1" t="s">
-        <v>24010</v>
+        <v>24326</v>
       </c>
       <c r="G1" t="s">
-        <v>24011</v>
+        <v>24327</v>
       </c>
       <c r="H1" t="s">
-        <v>24012</v>
+        <v>24328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>23935</v>
+        <v>24251</v>
       </c>
       <c r="B2" t="s">
-        <v>23972</v>
+        <v>24288</v>
       </c>
       <c r="C2" s="1">
         <v>-102236.23721409201</v>
@@ -74740,10 +74740,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>23936</v>
+        <v>24252</v>
       </c>
       <c r="B3" t="s">
-        <v>23973</v>
+        <v>24289</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -74762,10 +74762,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23937</v>
+        <v>24253</v>
       </c>
       <c r="B4" t="s">
-        <v>23974</v>
+        <v>24290</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -74782,10 +74782,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23938</v>
+        <v>24254</v>
       </c>
       <c r="B5" t="s">
-        <v>23975</v>
+        <v>24291</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -74798,10 +74798,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23939</v>
+        <v>24255</v>
       </c>
       <c r="B6" t="s">
-        <v>23976</v>
+        <v>24292</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -74818,10 +74818,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>23940</v>
+        <v>24256</v>
       </c>
       <c r="B7" t="s">
-        <v>23977</v>
+        <v>24293</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -74834,10 +74834,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>23941</v>
+        <v>24257</v>
       </c>
       <c r="B8" t="s">
-        <v>23977</v>
+        <v>24293</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -74850,10 +74850,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>23942</v>
+        <v>24258</v>
       </c>
       <c r="B9" t="s">
-        <v>23978</v>
+        <v>24294</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -74866,10 +74866,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23943</v>
+        <v>24259</v>
       </c>
       <c r="B10" t="s">
-        <v>23979</v>
+        <v>24295</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -74884,10 +74884,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23944</v>
+        <v>24260</v>
       </c>
       <c r="B11" t="s">
-        <v>23980</v>
+        <v>24296</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -74906,10 +74906,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>23945</v>
+        <v>24261</v>
       </c>
       <c r="B12" t="s">
-        <v>23981</v>
+        <v>24297</v>
       </c>
       <c r="C12" s="1">
         <v>-83.070126027215935</v>
@@ -74928,10 +74928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23946</v>
+        <v>24262</v>
       </c>
       <c r="B13" t="s">
-        <v>23982</v>
+        <v>24298</v>
       </c>
       <c r="C13" s="1">
         <v>144279.01796396461</v>
@@ -74954,10 +74954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23947</v>
+        <v>24263</v>
       </c>
       <c r="B14" t="s">
-        <v>23983</v>
+        <v>24299</v>
       </c>
       <c r="C14" s="1">
         <v>32414.538114762661</v>
@@ -74980,10 +74980,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23948</v>
+        <v>24264</v>
       </c>
       <c r="B15" t="s">
-        <v>23984</v>
+        <v>24300</v>
       </c>
       <c r="C15" s="1">
         <v>111864.47984920201</v>
@@ -75004,10 +75004,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>23949</v>
+        <v>24265</v>
       </c>
       <c r="B16" t="s">
-        <v>23985</v>
+        <v>24301</v>
       </c>
       <c r="C16" s="1">
         <v>101315.1098362044</v>
@@ -75030,10 +75030,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>23950</v>
+        <v>24266</v>
       </c>
       <c r="B17" t="s">
-        <v>23986</v>
+        <v>24302</v>
       </c>
       <c r="C17" s="1">
         <v>526.84154559200761</v>
@@ -75054,10 +75054,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>23951</v>
+        <v>24267</v>
       </c>
       <c r="B18" t="s">
-        <v>23987</v>
+        <v>24303</v>
       </c>
       <c r="C18" s="1">
         <v>1300.503467</v>
@@ -75078,10 +75078,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>23952</v>
+        <v>24268</v>
       </c>
       <c r="B19" t="s">
-        <v>23988</v>
+        <v>24304</v>
       </c>
       <c r="C19" s="1">
         <v>1300.503467</v>
@@ -75100,10 +75100,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>23953</v>
+        <v>24269</v>
       </c>
       <c r="B20" t="s">
-        <v>23989</v>
+        <v>24305</v>
       </c>
       <c r="C20" s="1">
         <v>16387.63379557012</v>
@@ -75126,10 +75126,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>23954</v>
+        <v>24270</v>
       </c>
       <c r="B21" t="s">
-        <v>23990</v>
+        <v>24306</v>
       </c>
       <c r="C21" s="1">
         <v>97.490238000000005</v>
@@ -75148,10 +75148,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23955</v>
+        <v>24271</v>
       </c>
       <c r="B22" t="s">
-        <v>23991</v>
+        <v>24307</v>
       </c>
       <c r="C22" s="1">
         <v>1386.9169386399999</v>
@@ -75168,10 +75168,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>23956</v>
+        <v>24272</v>
       </c>
       <c r="B23" t="s">
-        <v>23992</v>
+        <v>24308</v>
       </c>
       <c r="C23" s="1">
         <v>1117.864241</v>
@@ -75190,10 +75190,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>23957</v>
+        <v>24273</v>
       </c>
       <c r="B24" t="s">
-        <v>23993</v>
+        <v>24309</v>
       </c>
       <c r="C24" s="1">
         <v>13785.36237793012</v>
@@ -75216,10 +75216,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>23958</v>
+        <v>24274</v>
       </c>
       <c r="B25" t="s">
-        <v>23994</v>
+        <v>24310</v>
       </c>
       <c r="C25" s="1">
         <v>98850.343655568271</v>
@@ -75242,10 +75242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>23959</v>
+        <v>24279</v>
       </c>
       <c r="B26" t="s">
-        <v>23995</v>
+        <v>24315</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -75260,18 +75260,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>23960</v>
+        <v>24280</v>
       </c>
       <c r="B27" t="s">
-        <v>23996</v>
+        <v>24316</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
+        <v>-25017.388782343201</v>
+      </c>
+      <c r="F27" s="1">
         <v>-25017.38878234318</v>
-      </c>
-      <c r="F27" s="1">
-        <v>-25017.388782343201</v>
       </c>
       <c r="G27" s="1">
         <v>118456.4656790759</v>
@@ -75282,10 +75282,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>23961</v>
+        <v>24277</v>
       </c>
       <c r="B28" t="s">
-        <v>23997</v>
+        <v>24313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -75300,10 +75300,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>23962</v>
+        <v>24278</v>
       </c>
       <c r="B29" t="s">
-        <v>23998</v>
+        <v>24314</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -75322,10 +75322,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>23963</v>
+        <v>24279</v>
       </c>
       <c r="B30" t="s">
-        <v>23999</v>
+        <v>24315</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -75340,18 +75340,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>23964</v>
+        <v>24280</v>
       </c>
       <c r="B31" t="s">
-        <v>24000</v>
+        <v>24316</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
+        <v>-25017.38878234318</v>
+      </c>
+      <c r="F31" s="1">
         <v>-25017.388782343201</v>
-      </c>
-      <c r="F31" s="1">
-        <v>-25017.38878234318</v>
       </c>
       <c r="G31" s="1">
         <v>118456.4656790759</v>
@@ -75362,10 +75362,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>23965</v>
+        <v>24281</v>
       </c>
       <c r="B32" t="s">
-        <v>24001</v>
+        <v>24317</v>
       </c>
       <c r="C32" s="1">
         <v>-3385.8935585237782</v>
@@ -75380,10 +75380,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>23966</v>
+        <v>24282</v>
       </c>
       <c r="B33" t="s">
-        <v>24002</v>
+        <v>24318</v>
       </c>
       <c r="C33" s="1">
         <v>0.27703699999999998</v>
@@ -75406,25 +75406,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>23967</v>
+        <v>24283</v>
       </c>
       <c r="B34" t="s">
-        <v>24003</v>
+        <v>24319</v>
       </c>
       <c r="C34" s="1">
         <v>-4009.0753441289771</v>
       </c>
       <c r="D34" s="1">
-        <v>-4009.0753441289712</v>
+        <v>-4009.0753441289771</v>
       </c>
       <c r="E34" s="1">
-        <v>-63565.818181042087</v>
+        <v>-63565.770979082881</v>
       </c>
       <c r="F34" s="1">
-        <v>-63565.818181042087</v>
+        <v>-63565.770979082881</v>
       </c>
       <c r="G34" s="1">
-        <v>43782.161676834643</v>
+        <v>43782.161676835007</v>
       </c>
       <c r="H34" s="1">
         <v>43782.161676835007</v>
@@ -75432,25 +75432,25 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>23967</v>
+        <v>24283</v>
       </c>
       <c r="B35" t="s">
-        <v>24003</v>
+        <v>24319</v>
       </c>
       <c r="C35" s="1">
         <v>-4009.0753441289712</v>
       </c>
       <c r="D35" s="1">
-        <v>-4009.0753441289771</v>
+        <v>-4009.0753441289712</v>
       </c>
       <c r="E35" s="1">
-        <v>-63565.770979082881</v>
+        <v>-63565.818181042087</v>
       </c>
       <c r="F35" s="1">
-        <v>-63565.770979082881</v>
+        <v>-63565.818181042087</v>
       </c>
       <c r="G35" s="1">
-        <v>43782.161676835007</v>
+        <v>43782.161676834643</v>
       </c>
       <c r="H35" s="1">
         <v>43782.161676834643</v>
@@ -75458,10 +75458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>23968</v>
+        <v>24286</v>
       </c>
       <c r="B36" t="s">
-        <v>24004</v>
+        <v>24322</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -75476,10 +75476,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>23969</v>
+        <v>24285</v>
       </c>
       <c r="B37" t="s">
-        <v>24005</v>
+        <v>24321</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -75496,10 +75496,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>23970</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>24006</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -75521,36 +75521,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>24013</v>
+        <v>24250</v>
       </c>
       <c r="B1" t="s">
-        <v>24050</v>
+        <v>24287</v>
       </c>
       <c r="C1" t="s">
-        <v>24086</v>
+        <v>24323</v>
       </c>
       <c r="D1" t="s">
-        <v>24087</v>
+        <v>24324</v>
       </c>
       <c r="E1" t="s">
-        <v>24088</v>
+        <v>24325</v>
       </c>
       <c r="F1" t="s">
-        <v>24089</v>
+        <v>24326</v>
       </c>
       <c r="G1" t="s">
-        <v>24090</v>
+        <v>24327</v>
       </c>
       <c r="H1" t="s">
-        <v>24091</v>
+        <v>24328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24014</v>
+        <v>24251</v>
       </c>
       <c r="B2" t="s">
-        <v>24051</v>
+        <v>24288</v>
       </c>
       <c r="C2" s="1">
         <v>-101427.2938489076</v>
@@ -75565,10 +75565,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24015</v>
+        <v>24252</v>
       </c>
       <c r="B3" t="s">
-        <v>24052</v>
+        <v>24289</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -75587,10 +75587,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24016</v>
+        <v>24253</v>
       </c>
       <c r="B4" t="s">
-        <v>24053</v>
+        <v>24290</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -75607,10 +75607,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24017</v>
+        <v>24254</v>
       </c>
       <c r="B5" t="s">
-        <v>24054</v>
+        <v>24291</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -75623,10 +75623,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24018</v>
+        <v>24255</v>
       </c>
       <c r="B6" t="s">
-        <v>24055</v>
+        <v>24292</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -75643,10 +75643,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24019</v>
+        <v>24256</v>
       </c>
       <c r="B7" t="s">
-        <v>24056</v>
+        <v>24293</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -75659,10 +75659,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24020</v>
+        <v>24257</v>
       </c>
       <c r="B8" t="s">
-        <v>24056</v>
+        <v>24293</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -75675,10 +75675,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24021</v>
+        <v>24258</v>
       </c>
       <c r="B9" t="s">
-        <v>24057</v>
+        <v>24294</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -75691,10 +75691,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24022</v>
+        <v>24259</v>
       </c>
       <c r="B10" t="s">
-        <v>24058</v>
+        <v>24295</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -75709,10 +75709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24023</v>
+        <v>24260</v>
       </c>
       <c r="B11" t="s">
-        <v>24059</v>
+        <v>24296</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -75731,10 +75731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24024</v>
+        <v>24261</v>
       </c>
       <c r="B12" t="s">
-        <v>24060</v>
+        <v>24297</v>
       </c>
       <c r="C12" s="1">
         <v>-92.934358778526615</v>
@@ -75753,10 +75753,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24025</v>
+        <v>24262</v>
       </c>
       <c r="B13" t="s">
-        <v>24061</v>
+        <v>24298</v>
       </c>
       <c r="C13" s="1">
         <v>162249.8021316196</v>
@@ -75779,10 +75779,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24026</v>
+        <v>24263</v>
       </c>
       <c r="B14" t="s">
-        <v>24062</v>
+        <v>24299</v>
       </c>
       <c r="C14" s="1">
         <v>43179.357846405859</v>
@@ -75805,10 +75805,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24027</v>
+        <v>24264</v>
       </c>
       <c r="B15" t="s">
-        <v>24063</v>
+        <v>24300</v>
       </c>
       <c r="C15" s="1">
         <v>119070.4442852137</v>
@@ -75829,10 +75829,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24028</v>
+        <v>24265</v>
       </c>
       <c r="B16" t="s">
-        <v>24064</v>
+        <v>24301</v>
       </c>
       <c r="C16" s="1">
         <v>111072.9372501466</v>
@@ -75855,10 +75855,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>24029</v>
+        <v>24266</v>
       </c>
       <c r="B17" t="s">
-        <v>24065</v>
+        <v>24302</v>
       </c>
       <c r="C17" s="1">
         <v>455.25087191519339</v>
@@ -75879,10 +75879,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24030</v>
+        <v>24267</v>
       </c>
       <c r="B18" t="s">
-        <v>24066</v>
+        <v>24303</v>
       </c>
       <c r="C18" s="1">
         <v>1486.8528134281901</v>
@@ -75903,10 +75903,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>24031</v>
+        <v>24268</v>
       </c>
       <c r="B19" t="s">
-        <v>24067</v>
+        <v>24304</v>
       </c>
       <c r="C19" s="1">
         <v>1486.8528134281901</v>
@@ -75925,10 +75925,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24032</v>
+        <v>24269</v>
       </c>
       <c r="B20" t="s">
-        <v>24068</v>
+        <v>24305</v>
       </c>
       <c r="C20" s="1">
         <v>19645.88621086465</v>
@@ -75951,10 +75951,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>24033</v>
+        <v>24270</v>
       </c>
       <c r="B21" t="s">
-        <v>24069</v>
+        <v>24306</v>
       </c>
       <c r="C21" s="1">
         <v>1.3780870000000001</v>
@@ -75973,10 +75973,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>24034</v>
+        <v>24271</v>
       </c>
       <c r="B22" t="s">
-        <v>24070</v>
+        <v>24307</v>
       </c>
       <c r="C22" s="1">
         <v>1680.6084285300001</v>
@@ -75993,10 +75993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>24035</v>
+        <v>24272</v>
       </c>
       <c r="B23" t="s">
-        <v>24071</v>
+        <v>24308</v>
       </c>
       <c r="C23" s="1">
         <v>1167.0419095569939</v>
@@ -76015,10 +76015,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>24036</v>
+        <v>24273</v>
       </c>
       <c r="B24" t="s">
-        <v>24072</v>
+        <v>24309</v>
       </c>
       <c r="C24" s="1">
         <v>16796.857785777662</v>
@@ -76041,10 +76041,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>24037</v>
+        <v>24274</v>
       </c>
       <c r="B25" t="s">
-        <v>24073</v>
+        <v>24310</v>
       </c>
       <c r="C25" s="1">
         <v>108339.94151571881</v>
@@ -76067,10 +76067,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>24038</v>
+        <v>24279</v>
       </c>
       <c r="B26" t="s">
-        <v>24074</v>
+        <v>24315</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -76083,10 +76083,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>24039</v>
+        <v>24280</v>
       </c>
       <c r="B27" t="s">
-        <v>24075</v>
+        <v>24316</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -76105,10 +76105,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>24040</v>
+        <v>24277</v>
       </c>
       <c r="B28" t="s">
-        <v>24076</v>
+        <v>24313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -76123,10 +76123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>24041</v>
+        <v>24278</v>
       </c>
       <c r="B29" t="s">
-        <v>24077</v>
+        <v>24314</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -76145,10 +76145,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>24042</v>
+        <v>24279</v>
       </c>
       <c r="B30" t="s">
-        <v>24078</v>
+        <v>24315</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -76161,10 +76161,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>24043</v>
+        <v>24280</v>
       </c>
       <c r="B31" t="s">
-        <v>24079</v>
+        <v>24316</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -76183,10 +76183,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>24044</v>
+        <v>24281</v>
       </c>
       <c r="B32" t="s">
-        <v>24080</v>
+        <v>24317</v>
       </c>
       <c r="C32" s="1">
         <v>6912.6476668112009</v>
@@ -76201,10 +76201,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>24045</v>
+        <v>24282</v>
       </c>
       <c r="B33" t="s">
-        <v>24081</v>
+        <v>24239</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1">
@@ -76225,10 +76225,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>24046</v>
+        <v>24283</v>
       </c>
       <c r="B34" t="s">
-        <v>24082</v>
+        <v>24319</v>
       </c>
       <c r="C34" s="1">
         <v>5442.5976345336867</v>
@@ -76240,21 +76240,21 @@
         <v>-49773.892247342999</v>
       </c>
       <c r="F34" s="1">
-        <v>-49773.892247342999</v>
+        <v>-49773.892247343349</v>
       </c>
       <c r="G34" s="1">
+        <v>33283.712597372418</v>
+      </c>
+      <c r="H34" s="1">
         <v>33283.712597372112</v>
-      </c>
-      <c r="H34" s="1">
-        <v>33283.712597372418</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>24046</v>
+        <v>24283</v>
       </c>
       <c r="B35" t="s">
-        <v>24082</v>
+        <v>24319</v>
       </c>
       <c r="C35" s="1">
         <v>5442.5976345336967</v>
@@ -76266,21 +76266,21 @@
         <v>-49773.892247343349</v>
       </c>
       <c r="F35" s="1">
-        <v>-49773.892247343349</v>
+        <v>-49773.892247342999</v>
       </c>
       <c r="G35" s="1">
+        <v>33283.712597372112</v>
+      </c>
+      <c r="H35" s="1">
         <v>33283.712597372418</v>
-      </c>
-      <c r="H35" s="1">
-        <v>33283.712597372112</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24047</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>24083</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -76297,35 +76297,35 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24048</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24084</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>1640.019891895929</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>207169.67690947151</v>
+      </c>
+      <c r="F37" s="1">
+        <v>207169.67690947151</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24049</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>24085</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>207169.67690947151</v>
-      </c>
-      <c r="F38" s="1">
-        <v>207169.67690947151</v>
-      </c>
+        <v>1640.019891895929</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -76340,36 +76340,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>24092</v>
+        <v>24250</v>
       </c>
       <c r="B1" t="s">
-        <v>24129</v>
+        <v>24287</v>
       </c>
       <c r="C1" t="s">
-        <v>24165</v>
+        <v>24323</v>
       </c>
       <c r="D1" t="s">
-        <v>24166</v>
+        <v>24324</v>
       </c>
       <c r="E1" t="s">
-        <v>24167</v>
+        <v>24325</v>
       </c>
       <c r="F1" t="s">
-        <v>24168</v>
+        <v>24326</v>
       </c>
       <c r="G1" t="s">
-        <v>24169</v>
+        <v>24327</v>
       </c>
       <c r="H1" t="s">
-        <v>24170</v>
+        <v>24328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24093</v>
+        <v>24251</v>
       </c>
       <c r="B2" t="s">
-        <v>24130</v>
+        <v>24288</v>
       </c>
       <c r="C2" s="1">
         <v>-132325.81806931089</v>
@@ -76384,10 +76384,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24094</v>
+        <v>24252</v>
       </c>
       <c r="B3" t="s">
-        <v>24131</v>
+        <v>24289</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -76406,10 +76406,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24095</v>
+        <v>24253</v>
       </c>
       <c r="B4" t="s">
-        <v>24132</v>
+        <v>24290</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -76426,10 +76426,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24096</v>
+        <v>24254</v>
       </c>
       <c r="B5" t="s">
-        <v>24133</v>
+        <v>24291</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -76442,10 +76442,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24097</v>
+        <v>24255</v>
       </c>
       <c r="B6" t="s">
-        <v>24134</v>
+        <v>24292</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -76462,10 +76462,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24098</v>
+        <v>24256</v>
       </c>
       <c r="B7" t="s">
-        <v>24135</v>
+        <v>24293</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -76478,10 +76478,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24099</v>
+        <v>24257</v>
       </c>
       <c r="B8" t="s">
-        <v>24135</v>
+        <v>24293</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -76494,10 +76494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24100</v>
+        <v>24258</v>
       </c>
       <c r="B9" t="s">
-        <v>24136</v>
+        <v>24294</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -76510,10 +76510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24101</v>
+        <v>24259</v>
       </c>
       <c r="B10" t="s">
-        <v>24137</v>
+        <v>24295</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -76528,10 +76528,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24102</v>
+        <v>24260</v>
       </c>
       <c r="B11" t="s">
-        <v>24138</v>
+        <v>24296</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -76550,10 +76550,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24103</v>
+        <v>24261</v>
       </c>
       <c r="B12" t="s">
-        <v>24139</v>
+        <v>24297</v>
       </c>
       <c r="C12" s="1">
         <v>-111.3731775422125</v>
@@ -76572,10 +76572,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24104</v>
+        <v>24262</v>
       </c>
       <c r="B13" t="s">
-        <v>24140</v>
+        <v>24298</v>
       </c>
       <c r="C13" s="1">
         <v>160506.74429795379</v>
@@ -76598,10 +76598,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24105</v>
+        <v>24263</v>
       </c>
       <c r="B14" t="s">
-        <v>24141</v>
+        <v>24299</v>
       </c>
       <c r="C14" s="1">
         <v>47266.390163401513</v>
@@ -76624,10 +76624,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24106</v>
+        <v>24264</v>
       </c>
       <c r="B15" t="s">
-        <v>24142</v>
+        <v>24300</v>
       </c>
       <c r="C15" s="1">
         <v>113240.3541345523</v>
@@ -76648,10 +76648,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24107</v>
+        <v>24265</v>
       </c>
       <c r="B16" t="s">
-        <v>24143</v>
+        <v>24301</v>
       </c>
       <c r="C16" s="1">
         <v>106078.98298231589</v>
@@ -76674,10 +76674,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>24108</v>
+        <v>24266</v>
       </c>
       <c r="B17" t="s">
-        <v>24144</v>
+        <v>24302</v>
       </c>
       <c r="C17" s="1">
         <v>376.90302765656929</v>
@@ -76698,10 +76698,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24109</v>
+        <v>24267</v>
       </c>
       <c r="B18" t="s">
-        <v>24145</v>
+        <v>24303</v>
       </c>
       <c r="C18" s="1">
         <v>1655.657643517555</v>
@@ -76722,10 +76722,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>24110</v>
+        <v>24268</v>
       </c>
       <c r="B19" t="s">
-        <v>24146</v>
+        <v>24304</v>
       </c>
       <c r="C19" s="1">
         <v>1655.657643517555</v>
@@ -76744,10 +76744,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24111</v>
+        <v>24269</v>
       </c>
       <c r="B20" t="s">
-        <v>24147</v>
+        <v>24305</v>
       </c>
       <c r="C20" s="1">
         <v>22226.602795191338</v>
@@ -76770,10 +76770,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>24112</v>
+        <v>24270</v>
       </c>
       <c r="B21" t="s">
-        <v>24148</v>
+        <v>24306</v>
       </c>
       <c r="C21" s="1">
         <v>2.9676309999999999</v>
@@ -76792,10 +76792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>24113</v>
+        <v>24271</v>
       </c>
       <c r="B22" t="s">
-        <v>24149</v>
+        <v>24307</v>
       </c>
       <c r="C22" s="1">
         <v>2646.0630505200002</v>
@@ -76812,10 +76812,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>24114</v>
+        <v>24272</v>
       </c>
       <c r="B23" t="s">
-        <v>24150</v>
+        <v>24308</v>
       </c>
       <c r="C23" s="1">
         <v>1452.5266412882031</v>
@@ -76834,10 +76834,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>24115</v>
+        <v>24273</v>
       </c>
       <c r="B24" t="s">
-        <v>24151</v>
+        <v>24309</v>
       </c>
       <c r="C24" s="1">
         <v>18125.045472383139</v>
@@ -76860,10 +76860,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>24116</v>
+        <v>24274</v>
       </c>
       <c r="B25" t="s">
-        <v>24152</v>
+        <v>24310</v>
       </c>
       <c r="C25" s="1">
         <v>103687.46021795391</v>
@@ -76886,10 +76886,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>24117</v>
+        <v>24279</v>
       </c>
       <c r="B26" t="s">
-        <v>24153</v>
+        <v>24315</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -76902,18 +76902,18 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>24118</v>
+        <v>24280</v>
       </c>
       <c r="B27" t="s">
-        <v>24154</v>
+        <v>24316</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
+        <v>-47487.012322160823</v>
+      </c>
+      <c r="F27" s="1">
         <v>-47487.012322160852</v>
-      </c>
-      <c r="F27" s="1">
-        <v>-47487.012322160823</v>
       </c>
       <c r="G27" s="1">
         <v>137422.3722114753</v>
@@ -76924,10 +76924,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>24119</v>
+        <v>24277</v>
       </c>
       <c r="B28" t="s">
-        <v>24155</v>
+        <v>24313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -76942,10 +76942,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>24120</v>
+        <v>24278</v>
       </c>
       <c r="B29" t="s">
-        <v>24156</v>
+        <v>24314</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -76964,10 +76964,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>24121</v>
+        <v>24279</v>
       </c>
       <c r="B30" t="s">
-        <v>24157</v>
+        <v>24315</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -76980,18 +76980,18 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>24122</v>
+        <v>24280</v>
       </c>
       <c r="B31" t="s">
-        <v>24158</v>
+        <v>24316</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
+        <v>-47487.012322160852</v>
+      </c>
+      <c r="F31" s="1">
         <v>-47487.012322160823</v>
-      </c>
-      <c r="F31" s="1">
-        <v>-47487.012322160852</v>
       </c>
       <c r="G31" s="1">
         <v>137422.3722114753</v>
@@ -77002,10 +77002,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>24123</v>
+        <v>24281</v>
       </c>
       <c r="B32" t="s">
-        <v>24159</v>
+        <v>24317</v>
       </c>
       <c r="C32" s="1">
         <v>-28638.357851356981</v>
@@ -77020,10 +77020,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>24124</v>
+        <v>24282</v>
       </c>
       <c r="B33" t="s">
-        <v>24160</v>
+        <v>24318</v>
       </c>
       <c r="C33" s="1">
         <v>13.58729015431644</v>
@@ -77046,16 +77046,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>24125</v>
+        <v>24283</v>
       </c>
       <c r="B34" t="s">
-        <v>24161</v>
+        <v>24319</v>
       </c>
       <c r="C34" s="1">
         <v>-14516.140951382629</v>
       </c>
       <c r="D34" s="1">
-        <v>-14516.140951382629</v>
+        <v>-14516.15048177604</v>
       </c>
       <c r="E34" s="1">
         <v>-63947.039175029808</v>
@@ -77067,21 +77067,21 @@
         <v>39248.472782472993</v>
       </c>
       <c r="H34" s="1">
-        <v>39248.472782472993</v>
+        <v>39248.472782472847</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>24125</v>
+        <v>24283</v>
       </c>
       <c r="B35" t="s">
-        <v>24161</v>
+        <v>24319</v>
       </c>
       <c r="C35" s="1">
         <v>-14516.15048177604</v>
       </c>
       <c r="D35" s="1">
-        <v>-14516.15048177604</v>
+        <v>-14516.140951382629</v>
       </c>
       <c r="E35" s="1">
         <v>-63947.039175030113</v>
@@ -77093,62 +77093,62 @@
         <v>39248.472782472847</v>
       </c>
       <c r="H35" s="1">
-        <v>39248.472782472847</v>
+        <v>39248.472782472993</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24126</v>
+        <v>24284</v>
       </c>
       <c r="B36" t="s">
-        <v>24162</v>
+        <v>24320</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>239376.743428952</v>
+        <v>1691.532447066628</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>402.67289956090139</v>
-      </c>
-      <c r="H36" s="1">
-        <v>298520.24294644757</v>
-      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24127</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24163</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>1691.532447066628</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>200663.39336498949</v>
+      </c>
+      <c r="F37" s="1">
+        <v>200663.39336498949</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24128</v>
+        <v>24285</v>
       </c>
       <c r="B38" t="s">
-        <v>24164</v>
+        <v>24321</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>200663.39336498949</v>
-      </c>
-      <c r="F38" s="1">
-        <v>200663.39336498949</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+        <v>239376.743428952</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1">
+        <v>402.67289956090139</v>
+      </c>
+      <c r="H38" s="1">
+        <v>298520.24294644757</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -77161,36 +77161,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>24171</v>
+        <v>24250</v>
       </c>
       <c r="B1" t="s">
-        <v>24208</v>
+        <v>24287</v>
       </c>
       <c r="C1" t="s">
-        <v>24244</v>
+        <v>24323</v>
       </c>
       <c r="D1" t="s">
-        <v>24245</v>
+        <v>24324</v>
       </c>
       <c r="E1" t="s">
-        <v>24246</v>
+        <v>24325</v>
       </c>
       <c r="F1" t="s">
-        <v>24247</v>
+        <v>24326</v>
       </c>
       <c r="G1" t="s">
-        <v>24248</v>
+        <v>24327</v>
       </c>
       <c r="H1" t="s">
-        <v>24249</v>
+        <v>24328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>24172</v>
+        <v>24251</v>
       </c>
       <c r="B2" t="s">
-        <v>24209</v>
+        <v>24288</v>
       </c>
       <c r="C2" s="1">
         <v>-104514.67406784389</v>
@@ -77205,10 +77205,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>24173</v>
+        <v>24252</v>
       </c>
       <c r="B3" t="s">
-        <v>24210</v>
+        <v>24289</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -77227,10 +77227,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24174</v>
+        <v>24253</v>
       </c>
       <c r="B4" t="s">
-        <v>24211</v>
+        <v>24290</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -77247,10 +77247,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>24175</v>
+        <v>24254</v>
       </c>
       <c r="B5" t="s">
-        <v>24212</v>
+        <v>24291</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -77263,10 +77263,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>24176</v>
+        <v>24255</v>
       </c>
       <c r="B6" t="s">
-        <v>24213</v>
+        <v>24292</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -77283,10 +77283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>24177</v>
+        <v>24256</v>
       </c>
       <c r="B7" t="s">
-        <v>24214</v>
+        <v>24293</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -77299,10 +77299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>24178</v>
+        <v>24257</v>
       </c>
       <c r="B8" t="s">
-        <v>24214</v>
+        <v>24293</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -77315,10 +77315,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>24179</v>
+        <v>24258</v>
       </c>
       <c r="B9" t="s">
-        <v>24215</v>
+        <v>24294</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -77331,10 +77331,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24180</v>
+        <v>24259</v>
       </c>
       <c r="B10" t="s">
-        <v>24216</v>
+        <v>24295</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -77349,10 +77349,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>24181</v>
+        <v>24260</v>
       </c>
       <c r="B11" t="s">
-        <v>24217</v>
+        <v>24296</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -77371,10 +77371,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24182</v>
+        <v>24261</v>
       </c>
       <c r="B12" t="s">
-        <v>24218</v>
+        <v>24297</v>
       </c>
       <c r="C12" s="1">
         <v>-149.5741136579793</v>
@@ -77393,10 +77393,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>24183</v>
+        <v>24262</v>
       </c>
       <c r="B13" t="s">
-        <v>24219</v>
+        <v>24298</v>
       </c>
       <c r="C13" s="1">
         <v>151856.17438438139</v>
@@ -77419,10 +77419,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>24184</v>
+        <v>24263</v>
       </c>
       <c r="B14" t="s">
-        <v>24220</v>
+        <v>24299</v>
       </c>
       <c r="C14" s="1">
         <v>54754.723496312057</v>
@@ -77445,10 +77445,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24185</v>
+        <v>24264</v>
       </c>
       <c r="B15" t="s">
-        <v>24221</v>
+        <v>24300</v>
       </c>
       <c r="C15" s="1">
         <v>97101.450888069332</v>
@@ -77467,10 +77467,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24186</v>
+        <v>24265</v>
       </c>
       <c r="B16" t="s">
-        <v>24222</v>
+        <v>24301</v>
       </c>
       <c r="C16" s="1">
         <v>121151.1679762976</v>
@@ -77493,10 +77493,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>24187</v>
+        <v>24266</v>
       </c>
       <c r="B17" t="s">
-        <v>24223</v>
+        <v>24302</v>
       </c>
       <c r="C17" s="1">
         <v>829.94672213900139</v>
@@ -77517,10 +77517,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>24188</v>
+        <v>24267</v>
       </c>
       <c r="B18" t="s">
-        <v>24224</v>
+        <v>24303</v>
       </c>
       <c r="C18" s="1">
         <v>1851.55709250523</v>
@@ -77541,10 +77541,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>24189</v>
+        <v>24268</v>
       </c>
       <c r="B19" t="s">
-        <v>24225</v>
+        <v>24304</v>
       </c>
       <c r="C19" s="1">
         <v>1851.55709250523</v>
@@ -77563,10 +77563,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>24190</v>
+        <v>24269</v>
       </c>
       <c r="B20" t="s">
-        <v>24226</v>
+        <v>24305</v>
       </c>
       <c r="C20" s="1">
         <v>13110.58352570426</v>
@@ -77589,10 +77589,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>24191</v>
+        <v>24270</v>
       </c>
       <c r="B21" t="s">
-        <v>24227</v>
+        <v>24306</v>
       </c>
       <c r="C21" s="1">
         <v>1.421961</v>
@@ -77611,10 +77611,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>24192</v>
+        <v>24271</v>
       </c>
       <c r="B22" t="s">
-        <v>24228</v>
+        <v>24307</v>
       </c>
       <c r="C22" s="1">
         <v>2008.0292188799999</v>
@@ -77631,10 +77631,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>24193</v>
+        <v>24272</v>
       </c>
       <c r="B23" t="s">
-        <v>24229</v>
+        <v>24308</v>
       </c>
       <c r="C23" s="1">
         <v>728.95224428820325</v>
@@ -77653,10 +77653,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>24194</v>
+        <v>24273</v>
       </c>
       <c r="B24" t="s">
-        <v>24230</v>
+        <v>24309</v>
       </c>
       <c r="C24" s="1">
         <v>10372.18010153606</v>
@@ -77679,10 +77679,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>24195</v>
+        <v>24274</v>
       </c>
       <c r="B25" t="s">
-        <v>24231</v>
+        <v>24310</v>
       </c>
       <c r="C25" s="1">
         <v>117812.0378742148</v>
@@ -77705,10 +77705,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>24196</v>
+        <v>24279</v>
       </c>
       <c r="B26" t="s">
-        <v>24232</v>
+        <v>24315</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -77721,10 +77721,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>24197</v>
+        <v>24280</v>
       </c>
       <c r="B27" t="s">
-        <v>24233</v>
+        <v>24316</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -77743,10 +77743,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>24198</v>
+        <v>24277</v>
       </c>
       <c r="B28" t="s">
-        <v>24234</v>
+        <v>24313</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -77761,10 +77761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>24199</v>
+        <v>24278</v>
       </c>
       <c r="B29" t="s">
-        <v>24235</v>
+        <v>24314</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -77783,10 +77783,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>24200</v>
+        <v>24279</v>
       </c>
       <c r="B30" t="s">
-        <v>24236</v>
+        <v>24315</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -77799,10 +77799,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>24201</v>
+        <v>24280</v>
       </c>
       <c r="B31" t="s">
-        <v>24237</v>
+        <v>24316</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -77821,10 +77821,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>24202</v>
+        <v>24281</v>
       </c>
       <c r="B32" t="s">
-        <v>24238</v>
+        <v>24317</v>
       </c>
       <c r="C32" s="1">
         <v>13297.36380637088</v>
@@ -77839,7 +77839,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>24203</v>
+        <v>24282</v>
       </c>
       <c r="B33" t="s">
         <v>24239</v>
@@ -77863,16 +77863,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>24204</v>
+        <v>24283</v>
       </c>
       <c r="B34" t="s">
-        <v>24240</v>
+        <v>24319</v>
       </c>
       <c r="C34" s="1">
         <v>10171.468589380889</v>
       </c>
       <c r="D34" s="1">
-        <v>10171.468589380889</v>
+        <v>10171.459058987501</v>
       </c>
       <c r="E34" s="1">
         <v>-79545.106801385089</v>
@@ -77881,24 +77881,24 @@
         <v>-79545.106801385089</v>
       </c>
       <c r="G34" s="1">
-        <v>66059.10105946564</v>
+        <v>66058.729479423899</v>
       </c>
       <c r="H34" s="1">
-        <v>66059.10105946564</v>
+        <v>66058.729479423899</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>24204</v>
+        <v>24283</v>
       </c>
       <c r="B35" t="s">
-        <v>24240</v>
+        <v>24319</v>
       </c>
       <c r="C35" s="1">
         <v>10171.459058987501</v>
       </c>
       <c r="D35" s="1">
-        <v>10171.459058987501</v>
+        <v>10171.468589380889</v>
       </c>
       <c r="E35" s="1">
         <v>-79545.106801385089</v>
@@ -77907,18 +77907,18 @@
         <v>-79545.106801385089</v>
       </c>
       <c r="G35" s="1">
-        <v>66058.729479423899</v>
+        <v>66059.10105946564</v>
       </c>
       <c r="H35" s="1">
-        <v>66058.729479423899</v>
+        <v>66059.10105946564</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24205</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>24241</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -77935,10 +77935,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24206</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24242</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -77953,10 +77953,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24207</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>24243</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -78522,10 +78522,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>24275</v>
+        <v>24279</v>
       </c>
       <c r="B26" t="s">
-        <v>24311</v>
+        <v>24315</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -78538,10 +78538,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>24276</v>
+        <v>24280</v>
       </c>
       <c r="B27" t="s">
-        <v>24312</v>
+        <v>24316</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -78549,7 +78549,7 @@
         <v>-25100.98923128075</v>
       </c>
       <c r="F27" s="1">
-        <v>-25100.989231280721</v>
+        <v>-25100.98923128075</v>
       </c>
       <c r="G27" s="1">
         <v>147140.71535390709</v>
@@ -78627,7 +78627,7 @@
         <v>-25100.989231280721</v>
       </c>
       <c r="F31" s="1">
-        <v>-25100.98923128075</v>
+        <v>-25100.989231280721</v>
       </c>
       <c r="G31" s="1">
         <v>147140.71535390709</v>
@@ -78750,41 +78750,41 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>272538.25067318691</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1">
-        <v>456.40441621169998</v>
-      </c>
-      <c r="H37" s="1">
-        <v>335741.85541967727</v>
-      </c>
+        <v>264574.52162751998</v>
+      </c>
+      <c r="F37" s="1">
+        <v>264574.52162751998</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24286</v>
+        <v>24285</v>
       </c>
       <c r="B38" t="s">
-        <v>24322</v>
+        <v>24321</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>264574.52162751998</v>
-      </c>
-      <c r="F38" s="1">
-        <v>264574.52162751998</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+        <v>272538.25067318691</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1">
+        <v>456.40441621169998</v>
+      </c>
+      <c r="H38" s="1">
+        <v>335741.85541967727</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>

--- a/input_data/sna_country_data/URY/cei.xlsx
+++ b/input_data/sna_country_data/URY/cei.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42476" uniqueCount="24329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43050" uniqueCount="24329">
   <si>
     <t>code</t>
   </si>
@@ -73781,7 +73781,7 @@
         <v>25446.753598644849</v>
       </c>
       <c r="H34" s="1">
-        <v>25446.753598644718</v>
+        <v>25446.753598644849</v>
       </c>
     </row>
     <row r="35">
@@ -73807,24 +73807,22 @@
         <v>25446.753598644718</v>
       </c>
       <c r="H35" s="1">
-        <v>25446.753598644849</v>
+        <v>25446.753598644718</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24286</v>
+        <v>24284</v>
       </c>
       <c r="B36" t="s">
-        <v>24322</v>
+        <v>24320</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>79482.446760280014</v>
-      </c>
-      <c r="F36" s="1">
-        <v>79482.446760280014</v>
-      </c>
+        <v>926.5806651800001</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
@@ -73848,17 +73846,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24284</v>
+        <v>24286</v>
       </c>
       <c r="B38" t="s">
-        <v>24320</v>
+        <v>24322</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>926.5806651800001</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>79482.446760280014</v>
+      </c>
+      <c r="F38" s="1">
+        <v>79482.446760280014</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -74443,10 +74443,10 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
+        <v>-10570.43407502865</v>
+      </c>
+      <c r="F27" s="1">
         <v>-10570.434075028639</v>
-      </c>
-      <c r="F27" s="1">
-        <v>-10570.43407502865</v>
       </c>
       <c r="G27" s="1">
         <v>124508.5573505638</v>
@@ -74523,10 +74523,10 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
+        <v>-10570.434075028639</v>
+      </c>
+      <c r="F31" s="1">
         <v>-10570.43407502865</v>
-      </c>
-      <c r="F31" s="1">
-        <v>-10570.434075028639</v>
       </c>
       <c r="G31" s="1">
         <v>124508.5573505638</v>
@@ -74593,16 +74593,16 @@
         <v>-14574.434848447811</v>
       </c>
       <c r="E34" s="1">
+        <v>-66950.582658753861</v>
+      </c>
+      <c r="F34" s="1">
         <v>-66950.582658753847</v>
       </c>
-      <c r="F34" s="1">
-        <v>-66950.582658753861</v>
-      </c>
       <c r="G34" s="1">
-        <v>55330.055140544697</v>
+        <v>55330.055140544151</v>
       </c>
       <c r="H34" s="1">
-        <v>55330.055140544697</v>
+        <v>55330.055140544151</v>
       </c>
     </row>
     <row r="35">
@@ -74619,37 +74619,35 @@
         <v>-14574.43484844782</v>
       </c>
       <c r="E35" s="1">
+        <v>-66950.582658753847</v>
+      </c>
+      <c r="F35" s="1">
         <v>-66950.582658753861</v>
       </c>
-      <c r="F35" s="1">
-        <v>-66950.582658753847</v>
-      </c>
       <c r="G35" s="1">
-        <v>55330.055140544151</v>
+        <v>55330.055140544697</v>
       </c>
       <c r="H35" s="1">
-        <v>55330.055140544151</v>
+        <v>55330.055140544697</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B36" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>181558.9914336357</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>310.92989817709997</v>
-      </c>
-      <c r="H36" s="1">
-        <v>223683.25268700649</v>
-      </c>
+        <v>147042.35994689999</v>
+      </c>
+      <c r="F36" s="1">
+        <v>147042.21094677999</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
@@ -74669,21 +74667,23 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24286</v>
+        <v>24285</v>
       </c>
       <c r="B38" t="s">
-        <v>24322</v>
+        <v>24321</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>147042.35994689999</v>
-      </c>
-      <c r="F38" s="1">
-        <v>147042.21094677999</v>
-      </c>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+        <v>181558.9914336357</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1">
+        <v>310.92989817709997</v>
+      </c>
+      <c r="H38" s="1">
+        <v>223683.25268700649</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
@@ -75271,7 +75271,7 @@
         <v>-25017.388782343201</v>
       </c>
       <c r="F27" s="1">
-        <v>-25017.38878234318</v>
+        <v>-25017.388782343201</v>
       </c>
       <c r="G27" s="1">
         <v>118456.4656790759</v>
@@ -75351,7 +75351,7 @@
         <v>-25017.38878234318</v>
       </c>
       <c r="F31" s="1">
-        <v>-25017.388782343201</v>
+        <v>-25017.38878234318</v>
       </c>
       <c r="G31" s="1">
         <v>118456.4656790759</v>
@@ -75421,13 +75421,13 @@
         <v>-63565.770979082881</v>
       </c>
       <c r="F34" s="1">
-        <v>-63565.770979082881</v>
+        <v>-63565.818181042087</v>
       </c>
       <c r="G34" s="1">
         <v>43782.161676835007</v>
       </c>
       <c r="H34" s="1">
-        <v>43782.161676835007</v>
+        <v>43782.161676834643</v>
       </c>
     </row>
     <row r="35">
@@ -75447,52 +75447,52 @@
         <v>-63565.818181042087</v>
       </c>
       <c r="F35" s="1">
-        <v>-63565.818181042087</v>
+        <v>-63565.770979082881</v>
       </c>
       <c r="G35" s="1">
         <v>43782.161676834643</v>
       </c>
       <c r="H35" s="1">
-        <v>43782.161676834643</v>
+        <v>43782.161676835007</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24286</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>24322</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="F36" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+        <v>201604.21968480741</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
+        <v>337.34758922499998</v>
+      </c>
+      <c r="H36" s="1">
+        <v>253381.7166756459</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>201604.21968480741</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1">
-        <v>337.34758922499998</v>
-      </c>
-      <c r="H37" s="1">
-        <v>253381.7166756459</v>
-      </c>
+        <v>170013.75605207999</v>
+      </c>
+      <c r="F37" s="1">
+        <v>170013.75605207999</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -76234,13 +76234,13 @@
         <v>5442.5976345336867</v>
       </c>
       <c r="D34" s="1">
-        <v>5442.5976345336967</v>
+        <v>5442.5976345336867</v>
       </c>
       <c r="E34" s="1">
+        <v>-49773.892247343349</v>
+      </c>
+      <c r="F34" s="1">
         <v>-49773.892247342999</v>
-      </c>
-      <c r="F34" s="1">
-        <v>-49773.892247343349</v>
       </c>
       <c r="G34" s="1">
         <v>33283.712597372418</v>
@@ -76260,13 +76260,13 @@
         <v>5442.5976345336967</v>
       </c>
       <c r="D35" s="1">
-        <v>5442.5976345336867</v>
+        <v>5442.5976345336967</v>
       </c>
       <c r="E35" s="1">
+        <v>-49773.892247342999</v>
+      </c>
+      <c r="F35" s="1">
         <v>-49773.892247343349</v>
-      </c>
-      <c r="F35" s="1">
-        <v>-49773.892247342999</v>
       </c>
       <c r="G35" s="1">
         <v>33283.712597372112</v>
@@ -76297,35 +76297,35 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24286</v>
+        <v>24284</v>
       </c>
       <c r="B37" t="s">
-        <v>24322</v>
+        <v>24320</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>207169.67690947151</v>
-      </c>
-      <c r="F37" s="1">
-        <v>207169.67690947151</v>
-      </c>
+        <v>1640.019891895929</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24284</v>
+        <v>24286</v>
       </c>
       <c r="B38" t="s">
-        <v>24320</v>
+        <v>24322</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1640.019891895929</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>207169.67690947151</v>
+      </c>
+      <c r="F38" s="1">
+        <v>207169.67690947151</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -76913,7 +76913,7 @@
         <v>-47487.012322160823</v>
       </c>
       <c r="F27" s="1">
-        <v>-47487.012322160852</v>
+        <v>-47487.012322160823</v>
       </c>
       <c r="G27" s="1">
         <v>137422.3722114753</v>
@@ -76991,7 +76991,7 @@
         <v>-47487.012322160852</v>
       </c>
       <c r="F31" s="1">
-        <v>-47487.012322160823</v>
+        <v>-47487.012322160852</v>
       </c>
       <c r="G31" s="1">
         <v>137422.3722114753</v>
@@ -77061,7 +77061,7 @@
         <v>-63947.039175029808</v>
       </c>
       <c r="F34" s="1">
-        <v>-63947.039175029808</v>
+        <v>-63947.039175030113</v>
       </c>
       <c r="G34" s="1">
         <v>39248.472782472993</v>
@@ -77087,7 +77087,7 @@
         <v>-63947.039175030113</v>
       </c>
       <c r="F35" s="1">
-        <v>-63947.039175030113</v>
+        <v>-63947.039175029808</v>
       </c>
       <c r="G35" s="1">
         <v>39248.472782472847</v>
@@ -77114,41 +77114,41 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24286</v>
+        <v>24285</v>
       </c>
       <c r="B37" t="s">
-        <v>24322</v>
+        <v>24321</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>200663.39336498949</v>
-      </c>
-      <c r="F37" s="1">
-        <v>200663.39336498949</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+        <v>239376.743428952</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>402.67289956090139</v>
+      </c>
+      <c r="H37" s="1">
+        <v>298520.24294644757</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B38" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>239376.743428952</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1">
-        <v>402.67289956090139</v>
-      </c>
-      <c r="H38" s="1">
-        <v>298520.24294644757</v>
-      </c>
+        <v>200663.39336498949</v>
+      </c>
+      <c r="F38" s="1">
+        <v>200663.39336498949</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -77872,7 +77872,7 @@
         <v>10171.468589380889</v>
       </c>
       <c r="D34" s="1">
-        <v>10171.459058987501</v>
+        <v>10171.468589380889</v>
       </c>
       <c r="E34" s="1">
         <v>-79545.106801385089</v>
@@ -77898,7 +77898,7 @@
         <v>10171.459058987501</v>
       </c>
       <c r="D35" s="1">
-        <v>10171.468589380889</v>
+        <v>10171.459058987501</v>
       </c>
       <c r="E35" s="1">
         <v>-79545.106801385089</v>
@@ -77935,35 +77935,35 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24286</v>
+        <v>24284</v>
       </c>
       <c r="B37" t="s">
-        <v>24322</v>
+        <v>24320</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>242248.42014405999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>242248.42014405999</v>
-      </c>
+        <v>1625.492093275358</v>
+      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24284</v>
+        <v>24286</v>
       </c>
       <c r="B38" t="s">
-        <v>24320</v>
+        <v>24322</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>1625.492093275358</v>
-      </c>
-      <c r="F38" s="1"/>
+        <v>242248.42014405999</v>
+      </c>
+      <c r="F38" s="1">
+        <v>242248.42014405999</v>
+      </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -78546,7 +78546,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-25100.98923128075</v>
+        <v>-25100.989231280721</v>
       </c>
       <c r="F27" s="1">
         <v>-25100.98923128075</v>
@@ -78624,7 +78624,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-25100.989231280721</v>
+        <v>-25100.98923128075</v>
       </c>
       <c r="F31" s="1">
         <v>-25100.989231280721</v>
@@ -78700,10 +78700,10 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G34" s="1">
+        <v>50492.474199901873</v>
+      </c>
+      <c r="H34" s="1">
         <v>50492.474199902237</v>
-      </c>
-      <c r="H34" s="1">
-        <v>50492.474199901873</v>
       </c>
     </row>
     <row r="35">
@@ -78726,10 +78726,10 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G35" s="1">
+        <v>50492.474199902237</v>
+      </c>
+      <c r="H35" s="1">
         <v>50492.474199901873</v>
-      </c>
-      <c r="H35" s="1">
-        <v>50492.474199902237</v>
       </c>
     </row>
     <row r="36">
@@ -78750,41 +78750,41 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24286</v>
+        <v>24285</v>
       </c>
       <c r="B37" t="s">
-        <v>24322</v>
+        <v>24321</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>264574.52162751998</v>
-      </c>
-      <c r="F37" s="1">
-        <v>264574.52162751998</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+        <v>272538.25067318691</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>456.40441621169998</v>
+      </c>
+      <c r="H37" s="1">
+        <v>335741.85541967727</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B38" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>272538.25067318691</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1">
-        <v>456.40441621169998</v>
-      </c>
-      <c r="H38" s="1">
-        <v>335741.85541967727</v>
-      </c>
+        <v>264574.52162751998</v>
+      </c>
+      <c r="F38" s="1">
+        <v>264574.52162751998</v>
+      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
     </row>
   </sheetData>
 </worksheet>

--- a/input_data/sna_country_data/URY/cei.xlsx
+++ b/input_data/sna_country_data/URY/cei.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43050" uniqueCount="24329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44772" uniqueCount="24329">
   <si>
     <t>code</t>
   </si>
@@ -73624,10 +73624,10 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-3264.8749993161441</v>
+        <v>-3264.8749993161591</v>
       </c>
       <c r="F27" s="1">
-        <v>-3264.8749993161441</v>
+        <v>-3264.8749993161591</v>
       </c>
       <c r="G27" s="1">
         <v>65128.014697722727</v>
@@ -73704,10 +73704,10 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-3264.8749993161591</v>
+        <v>-3264.8749993161441</v>
       </c>
       <c r="F31" s="1">
-        <v>-3264.8749993161591</v>
+        <v>-3264.8749993161441</v>
       </c>
       <c r="G31" s="1">
         <v>65128.014697722727</v>
@@ -73781,7 +73781,7 @@
         <v>25446.753598644849</v>
       </c>
       <c r="H34" s="1">
-        <v>25446.753598644849</v>
+        <v>25446.753598644718</v>
       </c>
     </row>
     <row r="35">
@@ -73807,42 +73807,42 @@
         <v>25446.753598644718</v>
       </c>
       <c r="H35" s="1">
-        <v>25446.753598644718</v>
+        <v>25446.753598644849</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24284</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>24320</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>926.5806651800001</v>
+        <v>113976.0975413</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="H36" s="1">
+        <v>137582.86030768359</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24285</v>
+        <v>24284</v>
       </c>
       <c r="B37" t="s">
-        <v>24321</v>
+        <v>24320</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>113976.0975413</v>
+        <v>926.5806651800001</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="1">
-        <v>137582.86030768359</v>
-      </c>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -74446,7 +74446,7 @@
         <v>-10570.43407502865</v>
       </c>
       <c r="F27" s="1">
-        <v>-10570.434075028639</v>
+        <v>-10570.43407502865</v>
       </c>
       <c r="G27" s="1">
         <v>124508.5573505638</v>
@@ -74526,7 +74526,7 @@
         <v>-10570.434075028639</v>
       </c>
       <c r="F31" s="1">
-        <v>-10570.43407502865</v>
+        <v>-10570.434075028639</v>
       </c>
       <c r="G31" s="1">
         <v>124508.5573505638</v>
@@ -74599,7 +74599,7 @@
         <v>-66950.582658753847</v>
       </c>
       <c r="G34" s="1">
-        <v>55330.055140544151</v>
+        <v>55330.055140544697</v>
       </c>
       <c r="H34" s="1">
         <v>55330.055140544151</v>
@@ -74625,7 +74625,7 @@
         <v>-66950.582658753861</v>
       </c>
       <c r="G35" s="1">
-        <v>55330.055140544697</v>
+        <v>55330.055140544151</v>
       </c>
       <c r="H35" s="1">
         <v>55330.055140544697</v>
@@ -74633,57 +74633,57 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24286</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>24322</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>147042.35994689999</v>
-      </c>
-      <c r="F36" s="1">
-        <v>147042.21094677999</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+        <v>181558.9914336357</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1">
+        <v>310.92989817709997</v>
+      </c>
+      <c r="H36" s="1">
+        <v>223683.25268700649</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24284</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24320</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>1410.7265588499999</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>147042.35994689999</v>
+      </c>
+      <c r="F37" s="1">
+        <v>147042.21094677999</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24285</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>24321</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>181558.9914336357</v>
+        <v>1410.7265588499999</v>
       </c>
       <c r="F38" s="1"/>
-      <c r="G38" s="1">
-        <v>310.92989817709997</v>
-      </c>
-      <c r="H38" s="1">
-        <v>223683.25268700649</v>
-      </c>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
     </row>
   </sheetData>
 </worksheet>
@@ -75271,7 +75271,7 @@
         <v>-25017.388782343201</v>
       </c>
       <c r="F27" s="1">
-        <v>-25017.388782343201</v>
+        <v>-25017.38878234318</v>
       </c>
       <c r="G27" s="1">
         <v>118456.4656790759</v>
@@ -75351,7 +75351,7 @@
         <v>-25017.38878234318</v>
       </c>
       <c r="F31" s="1">
-        <v>-25017.38878234318</v>
+        <v>-25017.388782343201</v>
       </c>
       <c r="G31" s="1">
         <v>118456.4656790759</v>
@@ -75415,19 +75415,19 @@
         <v>-4009.0753441289771</v>
       </c>
       <c r="D34" s="1">
-        <v>-4009.0753441289771</v>
+        <v>-4009.0753441289712</v>
       </c>
       <c r="E34" s="1">
-        <v>-63565.770979082881</v>
+        <v>-63565.818181042087</v>
       </c>
       <c r="F34" s="1">
         <v>-63565.818181042087</v>
       </c>
       <c r="G34" s="1">
+        <v>43782.161676834643</v>
+      </c>
+      <c r="H34" s="1">
         <v>43782.161676835007</v>
-      </c>
-      <c r="H34" s="1">
-        <v>43782.161676834643</v>
       </c>
     </row>
     <row r="35">
@@ -75441,58 +75441,58 @@
         <v>-4009.0753441289712</v>
       </c>
       <c r="D35" s="1">
-        <v>-4009.0753441289712</v>
+        <v>-4009.0753441289771</v>
       </c>
       <c r="E35" s="1">
-        <v>-63565.818181042087</v>
+        <v>-63565.770979082881</v>
       </c>
       <c r="F35" s="1">
         <v>-63565.770979082881</v>
       </c>
       <c r="G35" s="1">
+        <v>43782.161676835007</v>
+      </c>
+      <c r="H35" s="1">
         <v>43782.161676834643</v>
-      </c>
-      <c r="H35" s="1">
-        <v>43782.161676835007</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B36" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>201604.21968480741</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>337.34758922499998</v>
-      </c>
-      <c r="H36" s="1">
-        <v>253381.7166756459</v>
-      </c>
+        <v>170013.75605207999</v>
+      </c>
+      <c r="F36" s="1">
+        <v>170013.75605207999</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24286</v>
+        <v>24285</v>
       </c>
       <c r="B37" t="s">
-        <v>24322</v>
+        <v>24321</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="F37" s="1">
-        <v>170013.75605207999</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+        <v>201604.21968480741</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1">
+        <v>337.34758922499998</v>
+      </c>
+      <c r="H37" s="1">
+        <v>253381.7166756459</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
@@ -76246,7 +76246,7 @@
         <v>33283.712597372418</v>
       </c>
       <c r="H34" s="1">
-        <v>33283.712597372112</v>
+        <v>33283.712597372418</v>
       </c>
     </row>
     <row r="35">
@@ -76272,7 +76272,7 @@
         <v>33283.712597372112</v>
       </c>
       <c r="H35" s="1">
-        <v>33283.712597372418</v>
+        <v>33283.712597372112</v>
       </c>
     </row>
     <row r="36">
@@ -76297,35 +76297,35 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24284</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24320</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>1640.019891895929</v>
-      </c>
-      <c r="F37" s="1"/>
+        <v>207169.67690947151</v>
+      </c>
+      <c r="F37" s="1">
+        <v>207169.67690947151</v>
+      </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24286</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>24322</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>207169.67690947151</v>
-      </c>
-      <c r="F38" s="1">
-        <v>207169.67690947151</v>
-      </c>
+        <v>1640.019891895929</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -76913,7 +76913,7 @@
         <v>-47487.012322160823</v>
       </c>
       <c r="F27" s="1">
-        <v>-47487.012322160823</v>
+        <v>-47487.012322160852</v>
       </c>
       <c r="G27" s="1">
         <v>137422.3722114753</v>
@@ -76991,7 +76991,7 @@
         <v>-47487.012322160852</v>
       </c>
       <c r="F31" s="1">
-        <v>-47487.012322160852</v>
+        <v>-47487.012322160823</v>
       </c>
       <c r="G31" s="1">
         <v>137422.3722114753</v>
@@ -77055,7 +77055,7 @@
         <v>-14516.140951382629</v>
       </c>
       <c r="D34" s="1">
-        <v>-14516.15048177604</v>
+        <v>-14516.140951382629</v>
       </c>
       <c r="E34" s="1">
         <v>-63947.039175029808</v>
@@ -77064,7 +77064,7 @@
         <v>-63947.039175030113</v>
       </c>
       <c r="G34" s="1">
-        <v>39248.472782472993</v>
+        <v>39248.472782472847</v>
       </c>
       <c r="H34" s="1">
         <v>39248.472782472847</v>
@@ -77081,7 +77081,7 @@
         <v>-14516.15048177604</v>
       </c>
       <c r="D35" s="1">
-        <v>-14516.140951382629</v>
+        <v>-14516.15048177604</v>
       </c>
       <c r="E35" s="1">
         <v>-63947.039175030113</v>
@@ -77090,7 +77090,7 @@
         <v>-63947.039175029808</v>
       </c>
       <c r="G35" s="1">
-        <v>39248.472782472847</v>
+        <v>39248.472782472993</v>
       </c>
       <c r="H35" s="1">
         <v>39248.472782472993</v>
@@ -77098,55 +77098,55 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24284</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>24320</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>1691.532447066628</v>
+        <v>239376.743428952</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="G36" s="1">
+        <v>402.67289956090139</v>
+      </c>
+      <c r="H36" s="1">
+        <v>298520.24294644757</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B37" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>239376.743428952</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1">
-        <v>402.67289956090139</v>
-      </c>
-      <c r="H37" s="1">
-        <v>298520.24294644757</v>
-      </c>
+        <v>200663.39336498949</v>
+      </c>
+      <c r="F37" s="1">
+        <v>200663.39336498949</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24286</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>24322</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>200663.39336498949</v>
-      </c>
-      <c r="F38" s="1">
-        <v>200663.39336498949</v>
-      </c>
+        <v>1691.532447066628</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -77872,7 +77872,7 @@
         <v>10171.468589380889</v>
       </c>
       <c r="D34" s="1">
-        <v>10171.468589380889</v>
+        <v>10171.459058987501</v>
       </c>
       <c r="E34" s="1">
         <v>-79545.106801385089</v>
@@ -77884,7 +77884,7 @@
         <v>66058.729479423899</v>
       </c>
       <c r="H34" s="1">
-        <v>66058.729479423899</v>
+        <v>66059.10105946564</v>
       </c>
     </row>
     <row r="35">
@@ -77898,7 +77898,7 @@
         <v>10171.459058987501</v>
       </c>
       <c r="D35" s="1">
-        <v>10171.459058987501</v>
+        <v>10171.468589380889</v>
       </c>
       <c r="E35" s="1">
         <v>-79545.106801385089</v>
@@ -77910,60 +77910,60 @@
         <v>66059.10105946564</v>
       </c>
       <c r="H35" s="1">
-        <v>66059.10105946564</v>
+        <v>66058.729479423899</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24285</v>
+        <v>24286</v>
       </c>
       <c r="B36" t="s">
-        <v>24321</v>
+        <v>24322</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>250754.8245620098</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1">
-        <v>442.30808405340002</v>
-      </c>
-      <c r="H36" s="1">
-        <v>313181.58741649322</v>
-      </c>
+        <v>242248.42014405999</v>
+      </c>
+      <c r="F36" s="1">
+        <v>242248.42014405999</v>
+      </c>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24284</v>
+        <v>24285</v>
       </c>
       <c r="B37" t="s">
-        <v>24320</v>
+        <v>24321</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>1625.492093275358</v>
+        <v>250754.8245620098</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="G37" s="1">
+        <v>442.30808405340002</v>
+      </c>
+      <c r="H37" s="1">
+        <v>313181.58741649322</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>24286</v>
+        <v>24284</v>
       </c>
       <c r="B38" t="s">
-        <v>24322</v>
+        <v>24320</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>242248.42014405999</v>
-      </c>
-      <c r="F38" s="1">
-        <v>242248.42014405999</v>
-      </c>
+        <v>1625.492093275358</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
     </row>
@@ -78546,7 +78546,7 @@
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
-        <v>-25100.989231280721</v>
+        <v>-25100.98923128075</v>
       </c>
       <c r="F27" s="1">
         <v>-25100.98923128075</v>
@@ -78624,7 +78624,7 @@
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
-        <v>-25100.98923128075</v>
+        <v>-25100.989231280721</v>
       </c>
       <c r="F31" s="1">
         <v>-25100.989231280721</v>
@@ -78691,7 +78691,7 @@
         <v>63134.524836636163</v>
       </c>
       <c r="D34" s="1">
-        <v>63134.524836636163</v>
+        <v>63134.515306242713</v>
       </c>
       <c r="E34" s="1">
         <v>-60032.164387225363</v>
@@ -78700,7 +78700,7 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G34" s="1">
-        <v>50492.474199901873</v>
+        <v>50492.474199902237</v>
       </c>
       <c r="H34" s="1">
         <v>50492.474199902237</v>
@@ -78717,7 +78717,7 @@
         <v>63134.515306242713</v>
       </c>
       <c r="D35" s="1">
-        <v>63134.515306242713</v>
+        <v>63134.524836636163</v>
       </c>
       <c r="E35" s="1">
         <v>-60032.164387225363</v>
@@ -78726,7 +78726,7 @@
         <v>-60032.164387225363</v>
       </c>
       <c r="G35" s="1">
-        <v>50492.474199902237</v>
+        <v>50492.474199901873</v>
       </c>
       <c r="H35" s="1">
         <v>50492.474199901873</v>
@@ -78734,39 +78734,39 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>24284</v>
+        <v>24285</v>
       </c>
       <c r="B36" t="s">
-        <v>24320</v>
+        <v>24321</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>1891.473003789004</v>
+        <v>272538.25067318691</v>
       </c>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="G36" s="1">
+        <v>456.40441621169998</v>
+      </c>
+      <c r="H36" s="1">
+        <v>335741.85541967727</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>24285</v>
+        <v>24284</v>
       </c>
       <c r="B37" t="s">
-        <v>24321</v>
+        <v>24320</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>272538.25067318691</v>
+        <v>1891.473003789004</v>
       </c>
       <c r="F37" s="1"/>
-      <c r="G37" s="1">
-        <v>456.40441621169998</v>
-      </c>
-      <c r="H37" s="1">
-        <v>335741.85541967727</v>
-      </c>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
